--- a/outputs/Block5B_Senate_Race_Attribution.xlsx
+++ b/outputs/Block5B_Senate_Race_Attribution.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="108">
   <si>
     <t>STATE</t>
   </si>
@@ -190,30 +190,30 @@
     <t>Mean Comparability Weight</t>
   </si>
   <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
     <t>Georgia</t>
   </si>
   <si>
-    <t>North Carolina</t>
-  </si>
-  <si>
     <t>New Hampshire</t>
   </si>
   <si>
+    <t>Ohio</t>
+  </si>
+  <si>
     <t>Michigan</t>
   </si>
   <si>
-    <t>Ohio</t>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>Texas</t>
   </si>
   <si>
     <t>Maine</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Texas</t>
-  </si>
-  <si>
     <t>Iowa</t>
   </si>
   <si>
@@ -223,30 +223,30 @@
     <t>Montana</t>
   </si>
   <si>
+    <t>R</t>
+  </si>
+  <si>
     <t>D</t>
   </si>
   <si>
-    <t>R</t>
+    <t>RSenLikPollLD (&gt;5%&lt;=10%)</t>
   </si>
   <si>
     <t>DSenLikPollH (&gt;5%&lt;=10%)</t>
   </si>
   <si>
-    <t>RSenLikPollLD (&gt;5%&lt;=10%)</t>
+    <t>RSenLeanPollLD (&gt;1&lt;=5%)</t>
   </si>
   <si>
     <t>DSenLeanPollH (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>RSenLeanPollLD (&gt;1&lt;=5%)</t>
+    <t>RSenTosPoll (&lt;=1%)</t>
   </si>
   <si>
     <t>RSenLeanPollH (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>RSenLikPollH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
     <t>RSenSafPollH (&gt;10%)</t>
   </si>
   <si>
@@ -256,12 +256,12 @@
     <t>D Lean</t>
   </si>
   <si>
+    <t>Toss-Up</t>
+  </si>
+  <si>
     <t>R Lean</t>
   </si>
   <si>
-    <t>R Likely</t>
-  </si>
-  <si>
     <t>R Safe</t>
   </si>
   <si>
@@ -274,18 +274,12 @@
     <t>Safe</t>
   </si>
   <si>
-    <t>D Safe</t>
-  </si>
-  <si>
-    <t>Toss-Up</t>
+    <t>Democratic Flip</t>
   </si>
   <si>
     <t>Democratic Hold</t>
   </si>
   <si>
-    <t>Democratic Flip</t>
-  </si>
-  <si>
     <t>Republican Hold</t>
   </si>
   <si>
@@ -298,43 +292,43 @@
     <t>D+2</t>
   </si>
   <si>
+    <t>R+5</t>
+  </si>
+  <si>
     <t>EVEN</t>
   </si>
   <si>
-    <t>R+5</t>
+    <t>R+6</t>
   </si>
   <si>
     <t>D+4</t>
   </si>
   <si>
-    <t>R+6</t>
-  </si>
-  <si>
     <t>R+10</t>
   </si>
   <si>
+    <t>48.69% R</t>
+  </si>
+  <si>
     <t>50.62% D</t>
   </si>
   <si>
-    <t>48.69% R</t>
-  </si>
-  <si>
     <t>56.64% D</t>
   </si>
   <si>
+    <t>Appointed (2025)[p]</t>
+  </si>
+  <si>
     <t>49.90% D</t>
   </si>
   <si>
-    <t>Appointed (2025)[p]</t>
+    <t>53.90% R</t>
+  </si>
+  <si>
+    <t>53.51% R</t>
   </si>
   <si>
     <t>50.98% R</t>
-  </si>
-  <si>
-    <t>53.90% R</t>
-  </si>
-  <si>
-    <t>53.51% R</t>
   </si>
   <si>
     <t>51.74% R</t>
@@ -888,13 +882,13 @@
         <v>69</v>
       </c>
       <c r="C2">
-        <v>51.28</v>
+        <v>49.92</v>
       </c>
       <c r="D2">
-        <v>43.48</v>
+        <v>41.4</v>
       </c>
       <c r="E2">
-        <v>7.8</v>
+        <v>8.52</v>
       </c>
       <c r="F2" t="s">
         <v>71</v>
@@ -906,22 +900,22 @@
         <v>83</v>
       </c>
       <c r="I2">
-        <v>54.12</v>
+        <v>54.67</v>
       </c>
       <c r="J2">
-        <v>45.88</v>
+        <v>45.33</v>
       </c>
       <c r="K2">
-        <v>8.23</v>
+        <v>9.33</v>
       </c>
       <c r="L2">
-        <v>2.1</v>
+        <v>-0.18</v>
       </c>
       <c r="M2">
-        <v>10.33</v>
+        <v>9.16</v>
       </c>
       <c r="N2">
-        <v>10.33</v>
+        <v>9.16</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -930,106 +924,106 @@
         <v>1</v>
       </c>
       <c r="Q2">
-        <v>55.17</v>
+        <v>54.58</v>
       </c>
       <c r="R2">
-        <v>44.83</v>
+        <v>45.42</v>
       </c>
       <c r="S2">
-        <v>2.1</v>
+        <v>-0.18</v>
       </c>
       <c r="T2">
-        <v>10.33</v>
+        <v>9.16</v>
       </c>
       <c r="U2">
-        <v>10.33</v>
+        <v>9.16</v>
       </c>
       <c r="V2">
-        <v>92.11</v>
+        <v>91.81</v>
       </c>
       <c r="W2">
-        <v>7.89</v>
+        <v>8.19</v>
       </c>
       <c r="X2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" t="s">
         <v>86</v>
       </c>
-      <c r="Y2" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>88</v>
-      </c>
       <c r="AA2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AC2">
-        <v>7.89</v>
+        <v>91.81</v>
       </c>
       <c r="AD2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AE2">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF2">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG2">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH2">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI2">
+        <v>3.51</v>
+      </c>
+      <c r="AJ2">
         <v>3.24</v>
       </c>
-      <c r="AJ2">
-        <v>-0.34</v>
-      </c>
       <c r="AK2">
         <v>0</v>
       </c>
       <c r="AL2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AM2">
         <v>-1</v>
       </c>
       <c r="AN2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AO2" t="s">
         <v>69</v>
       </c>
       <c r="AP2">
-        <v>0.5062</v>
+        <v>0.4869</v>
       </c>
       <c r="AQ2">
-        <v>1.239999999999995</v>
+        <v>2.620000000000005</v>
       </c>
       <c r="AR2">
-        <v>11.33409373772884</v>
+        <v>10.15789243716453</v>
       </c>
       <c r="AS2">
-        <v>9.094093737728848</v>
+        <v>6.53789243716453</v>
       </c>
       <c r="AT2">
-        <v>10.21409373772885</v>
+        <v>8.347892437164532</v>
       </c>
       <c r="AU2">
-        <v>2.553523434432211</v>
+        <v>2.086973109291133</v>
       </c>
       <c r="AV2">
-        <v>5.19</v>
+        <v>4.53</v>
       </c>
       <c r="AW2">
-        <v>6.63</v>
+        <v>5.8</v>
       </c>
       <c r="AX2">
-        <v>7.32</v>
+        <v>6.58</v>
       </c>
       <c r="AY2">
         <v>1.11</v>
@@ -1038,22 +1032,22 @@
         <v>3</v>
       </c>
       <c r="BA2">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="BB2">
-        <v>0.74</v>
+        <v>0.28</v>
       </c>
       <c r="BC2">
-        <v>5.21</v>
+        <v>2.95</v>
       </c>
       <c r="BD2">
-        <v>0</v>
+        <v>30.1</v>
       </c>
       <c r="BE2">
-        <v>44.34</v>
+        <v>30.1</v>
       </c>
       <c r="BF2">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:58">
@@ -1064,13 +1058,13 @@
         <v>70</v>
       </c>
       <c r="C3">
-        <v>51.45</v>
+        <v>51.22</v>
       </c>
       <c r="D3">
-        <v>43.42</v>
+        <v>43.62</v>
       </c>
       <c r="E3">
-        <v>8.02</v>
+        <v>7.6</v>
       </c>
       <c r="F3" t="s">
         <v>72</v>
@@ -1082,22 +1076,22 @@
         <v>83</v>
       </c>
       <c r="I3">
-        <v>54.23</v>
+        <v>54.01</v>
       </c>
       <c r="J3">
-        <v>45.77</v>
+        <v>45.99</v>
       </c>
       <c r="K3">
-        <v>8.460000000000001</v>
+        <v>8.01</v>
       </c>
       <c r="L3">
-        <v>-0.3</v>
+        <v>4.11</v>
       </c>
       <c r="M3">
-        <v>8.16</v>
+        <v>12.12</v>
       </c>
       <c r="N3">
-        <v>8.16</v>
+        <v>12.12</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1106,106 +1100,106 @@
         <v>1</v>
       </c>
       <c r="Q3">
-        <v>54.08</v>
+        <v>54.87</v>
       </c>
       <c r="R3">
-        <v>45.92</v>
+        <v>45.13</v>
       </c>
       <c r="S3">
-        <v>-0.3</v>
+        <v>4.11</v>
       </c>
       <c r="T3">
-        <v>8.16</v>
+        <v>12.12</v>
       </c>
       <c r="U3">
-        <v>8.16</v>
+        <v>9.74</v>
       </c>
       <c r="V3">
-        <v>89.66</v>
+        <v>90.34</v>
       </c>
       <c r="W3">
-        <v>10.34</v>
+        <v>9.66</v>
       </c>
       <c r="X3" t="s">
         <v>78</v>
       </c>
       <c r="Y3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC3">
+        <v>9.66</v>
+      </c>
+      <c r="AD3" t="s">
         <v>89</v>
       </c>
-      <c r="AA3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC3">
-        <v>89.66</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>91</v>
-      </c>
       <c r="AE3">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF3">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG3">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH3">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI3">
-        <v>3.24</v>
+        <v>3.51</v>
       </c>
       <c r="AJ3">
-        <v>2.9</v>
+        <v>-0.28</v>
       </c>
       <c r="AK3">
         <v>0</v>
       </c>
       <c r="AL3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AM3">
         <v>-1</v>
       </c>
       <c r="AN3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AO3" t="s">
         <v>70</v>
       </c>
       <c r="AP3">
-        <v>0.4869</v>
+        <v>0.5062</v>
       </c>
       <c r="AQ3">
-        <v>2.620000000000005</v>
+        <v>1.239999999999995</v>
       </c>
       <c r="AR3">
-        <v>9.15573551212689</v>
+        <v>13.11951692303765</v>
       </c>
       <c r="AS3">
-        <v>5.535735512126886</v>
+        <v>10.87951692303766</v>
       </c>
       <c r="AT3">
-        <v>7.345735512126888</v>
+        <v>11.99951692303765</v>
       </c>
       <c r="AU3">
-        <v>1.836433878031722</v>
+        <v>2.999879230759413</v>
       </c>
       <c r="AV3">
-        <v>4.53</v>
+        <v>5.19</v>
       </c>
       <c r="AW3">
-        <v>5.67</v>
+        <v>6.82</v>
       </c>
       <c r="AX3">
-        <v>6.46</v>
+        <v>7.48</v>
       </c>
       <c r="AY3">
         <v>1.11</v>
@@ -1214,22 +1208,22 @@
         <v>3</v>
       </c>
       <c r="BA3">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="BB3">
-        <v>0.28</v>
+        <v>0.74</v>
       </c>
       <c r="BC3">
-        <v>2.95</v>
+        <v>5.21</v>
       </c>
       <c r="BD3">
-        <v>30.1</v>
+        <v>0</v>
       </c>
       <c r="BE3">
-        <v>30.1</v>
+        <v>44.34</v>
       </c>
       <c r="BF3">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="4" spans="1:58">
@@ -1237,19 +1231,19 @@
         <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4">
-        <v>50.28</v>
+        <v>47.65</v>
       </c>
       <c r="D4">
-        <v>44.52</v>
+        <v>41.98</v>
       </c>
       <c r="E4">
-        <v>5.75</v>
+        <v>5.68</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G4" t="s">
         <v>78</v>
@@ -1258,22 +1252,22 @@
         <v>83</v>
       </c>
       <c r="I4">
-        <v>53.03</v>
+        <v>53.17</v>
       </c>
       <c r="J4">
-        <v>46.97</v>
+        <v>46.83</v>
       </c>
       <c r="K4">
-        <v>6.07</v>
+        <v>6.33</v>
       </c>
       <c r="L4">
-        <v>1.69</v>
+        <v>1.06</v>
       </c>
       <c r="M4">
-        <v>7.76</v>
+        <v>7.39</v>
       </c>
       <c r="N4">
-        <v>7.76</v>
+        <v>7.39</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1282,79 +1276,79 @@
         <v>1</v>
       </c>
       <c r="Q4">
-        <v>53.88</v>
+        <v>52.82</v>
       </c>
       <c r="R4">
-        <v>46.12</v>
+        <v>47.18</v>
       </c>
       <c r="S4">
-        <v>1.69</v>
+        <v>1.06</v>
       </c>
       <c r="T4">
-        <v>7.76</v>
+        <v>7.39</v>
       </c>
       <c r="U4">
-        <v>7.76</v>
+        <v>5.65</v>
       </c>
       <c r="V4">
-        <v>87.20999999999999</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="W4">
-        <v>12.79</v>
+        <v>20.49</v>
       </c>
       <c r="X4" t="s">
         <v>78</v>
       </c>
       <c r="Y4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AA4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AC4">
-        <v>12.79</v>
+        <v>20.49</v>
       </c>
       <c r="AD4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE4">
+        <v>7.86</v>
+      </c>
+      <c r="AF4">
+        <v>0.28</v>
+      </c>
+      <c r="AG4">
+        <v>3.24</v>
+      </c>
+      <c r="AH4">
+        <v>2.96</v>
+      </c>
+      <c r="AI4">
+        <v>3.51</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.28</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="s">
         <v>91</v>
-      </c>
-      <c r="AE4">
-        <v>7.27</v>
-      </c>
-      <c r="AF4">
-        <v>0.34</v>
-      </c>
-      <c r="AG4">
-        <v>2.9</v>
-      </c>
-      <c r="AH4">
-        <v>2.56</v>
-      </c>
-      <c r="AI4">
-        <v>3.24</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.34</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>93</v>
       </c>
       <c r="AM4">
         <v>2</v>
       </c>
       <c r="AN4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AO4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AP4">
         <v>0.5664</v>
@@ -1363,10 +1357,10 @@
         <v>13.28</v>
       </c>
       <c r="AR4">
-        <v>5.757545040113389</v>
+        <v>5.39330665909661</v>
       </c>
       <c r="AS4">
-        <v>5.522454959886612</v>
+        <v>5.886693340903391</v>
       </c>
       <c r="AT4">
         <v>5.640000000000001</v>
@@ -1378,10 +1372,10 @@
         <v>4.99</v>
       </c>
       <c r="AW4">
-        <v>6.09</v>
+        <v>6.11</v>
       </c>
       <c r="AX4">
-        <v>6.83</v>
+        <v>6.85</v>
       </c>
       <c r="AY4">
         <v>1.11</v>
@@ -1416,13 +1410,13 @@
         <v>69</v>
       </c>
       <c r="C5">
-        <v>47.92</v>
+        <v>48.4</v>
       </c>
       <c r="D5">
-        <v>44.95</v>
+        <v>44.82</v>
       </c>
       <c r="E5">
-        <v>2.97</v>
+        <v>3.58</v>
       </c>
       <c r="F5" t="s">
         <v>73</v>
@@ -1434,22 +1428,22 @@
         <v>84</v>
       </c>
       <c r="I5">
-        <v>51.6</v>
+        <v>51.92</v>
       </c>
       <c r="J5">
-        <v>48.4</v>
+        <v>48.08</v>
       </c>
       <c r="K5">
-        <v>3.2</v>
+        <v>3.83</v>
       </c>
       <c r="L5">
-        <v>0.12</v>
+        <v>-0.3</v>
       </c>
       <c r="M5">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="N5">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1458,130 +1452,118 @@
         <v>1</v>
       </c>
       <c r="Q5">
-        <v>51.66</v>
+        <v>51.77</v>
       </c>
       <c r="R5">
-        <v>48.34</v>
+        <v>48.23</v>
       </c>
       <c r="S5">
-        <v>0.12</v>
+        <v>-0.3</v>
       </c>
       <c r="T5">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="U5">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="V5">
-        <v>69.5</v>
+        <v>71.27</v>
       </c>
       <c r="W5">
-        <v>30.5</v>
+        <v>28.73</v>
       </c>
       <c r="X5" t="s">
         <v>79</v>
       </c>
       <c r="Y5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AA5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AB5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AC5">
-        <v>30.5</v>
+        <v>71.27</v>
       </c>
       <c r="AD5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AE5">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF5">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG5">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH5">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI5">
+        <v>3.51</v>
+      </c>
+      <c r="AJ5">
         <v>3.24</v>
       </c>
-      <c r="AJ5">
-        <v>-0.34</v>
-      </c>
       <c r="AK5">
         <v>0</v>
       </c>
       <c r="AL5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AN5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>69</v>
-      </c>
-      <c r="AP5">
-        <v>0.499</v>
-      </c>
-      <c r="AQ5">
-        <v>-0.2000000000000028</v>
+        <v>100</v>
       </c>
       <c r="AR5">
-        <v>3.322364192499973</v>
-      </c>
-      <c r="AS5">
-        <v>3.522364192499976</v>
+        <v>8.536611196062932</v>
       </c>
       <c r="AT5">
-        <v>3.422364192499974</v>
+        <v>8.536611196062932</v>
       </c>
       <c r="AU5">
-        <v>0.8555910481249935</v>
+        <v>2.134152799015733</v>
       </c>
       <c r="AV5">
-        <v>4.72</v>
+        <v>4.15</v>
       </c>
       <c r="AW5">
-        <v>5.73</v>
+        <v>5.49</v>
       </c>
       <c r="AX5">
-        <v>6.51</v>
+        <v>6.3</v>
       </c>
       <c r="AY5">
         <v>1.11</v>
       </c>
       <c r="AZ5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA5">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="BB5">
-        <v>-0.6899999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="BC5">
-        <v>1.19</v>
+        <v>2.96</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>17.49</v>
       </c>
       <c r="BE5">
         <v>0</v>
       </c>
       <c r="BF5">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="6" spans="1:58">
@@ -1592,13 +1574,13 @@
         <v>70</v>
       </c>
       <c r="C6">
-        <v>49.92</v>
+        <v>47.98</v>
       </c>
       <c r="D6">
-        <v>46.55</v>
+        <v>45.52</v>
       </c>
       <c r="E6">
-        <v>3.38</v>
+        <v>2.45</v>
       </c>
       <c r="F6" t="s">
         <v>74</v>
@@ -1610,22 +1592,22 @@
         <v>84</v>
       </c>
       <c r="I6">
-        <v>51.75</v>
+        <v>51.31</v>
       </c>
       <c r="J6">
-        <v>48.25</v>
+        <v>48.69</v>
       </c>
       <c r="K6">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="L6">
-        <v>-0.47</v>
+        <v>2.32</v>
       </c>
       <c r="M6">
-        <v>3.03</v>
+        <v>4.94</v>
       </c>
       <c r="N6">
-        <v>3.03</v>
+        <v>4.94</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1634,118 +1616,130 @@
         <v>1</v>
       </c>
       <c r="Q6">
-        <v>51.51</v>
+        <v>51.31</v>
       </c>
       <c r="R6">
-        <v>48.49</v>
+        <v>48.69</v>
       </c>
       <c r="S6">
-        <v>-0.47</v>
+        <v>2.32</v>
       </c>
       <c r="T6">
-        <v>3.03</v>
+        <v>4.94</v>
       </c>
       <c r="U6">
-        <v>3.03</v>
+        <v>2.62</v>
       </c>
       <c r="V6">
-        <v>68.7</v>
+        <v>65.48</v>
       </c>
       <c r="W6">
-        <v>31.3</v>
+        <v>34.52</v>
       </c>
       <c r="X6" t="s">
         <v>79</v>
       </c>
       <c r="Y6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC6">
+        <v>34.52</v>
+      </c>
+      <c r="AD6" t="s">
         <v>89</v>
       </c>
-      <c r="AA6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC6">
-        <v>68.7</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>91</v>
-      </c>
       <c r="AE6">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF6">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG6">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH6">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI6">
-        <v>3.24</v>
+        <v>3.51</v>
       </c>
       <c r="AJ6">
-        <v>2.9</v>
+        <v>-0.28</v>
       </c>
       <c r="AK6">
         <v>0</v>
       </c>
       <c r="AL6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AM6">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="s">
-        <v>103</v>
+        <v>101</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP6">
+        <v>0.499</v>
+      </c>
+      <c r="AQ6">
+        <v>-0.2000000000000028</v>
       </c>
       <c r="AR6">
-        <v>8.027335204854857</v>
+        <v>4.943406372496832</v>
+      </c>
+      <c r="AS6">
+        <v>5.143406372496835</v>
       </c>
       <c r="AT6">
-        <v>8.027335204854857</v>
+        <v>5.043406372496833</v>
       </c>
       <c r="AU6">
-        <v>2.006833801213714</v>
+        <v>1.260851593124208</v>
       </c>
       <c r="AV6">
-        <v>4.15</v>
+        <v>4.72</v>
       </c>
       <c r="AW6">
-        <v>5.39</v>
+        <v>5.81</v>
       </c>
       <c r="AX6">
-        <v>6.21</v>
+        <v>6.58</v>
       </c>
       <c r="AY6">
         <v>1.11</v>
       </c>
       <c r="AZ6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA6">
-        <v>2.8</v>
+        <v>1.93</v>
       </c>
       <c r="BB6">
-        <v>0.17</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="BC6">
-        <v>2.96</v>
+        <v>1.19</v>
       </c>
       <c r="BD6">
-        <v>17.49</v>
+        <v>0</v>
       </c>
       <c r="BE6">
         <v>0</v>
       </c>
       <c r="BF6">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:58">
@@ -1753,19 +1747,19 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7">
-        <v>49.4</v>
+        <v>50.15</v>
       </c>
       <c r="D7">
-        <v>47.7</v>
+        <v>48.38</v>
       </c>
       <c r="E7">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s">
         <v>79</v>
@@ -1774,22 +1768,22 @@
         <v>84</v>
       </c>
       <c r="I7">
-        <v>50.88</v>
+        <v>50.9</v>
       </c>
       <c r="J7">
-        <v>49.12</v>
+        <v>49.1</v>
       </c>
       <c r="K7">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="L7">
-        <v>-0.5</v>
+        <v>2.04</v>
       </c>
       <c r="M7">
-        <v>1.25</v>
+        <v>3.84</v>
       </c>
       <c r="N7">
-        <v>1.25</v>
+        <v>3.84</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1798,106 +1792,106 @@
         <v>1</v>
       </c>
       <c r="Q7">
-        <v>50.63</v>
+        <v>50.58</v>
       </c>
       <c r="R7">
-        <v>49.37</v>
+        <v>49.42</v>
       </c>
       <c r="S7">
-        <v>-0.5</v>
+        <v>2.04</v>
       </c>
       <c r="T7">
-        <v>1.25</v>
+        <v>3.84</v>
       </c>
       <c r="U7">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="V7">
-        <v>56.37</v>
+        <v>56.21</v>
       </c>
       <c r="W7">
-        <v>43.63</v>
+        <v>43.79</v>
       </c>
       <c r="X7" t="s">
         <v>79</v>
       </c>
       <c r="Y7" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC7">
+        <v>56.21</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE7">
+        <v>7.86</v>
+      </c>
+      <c r="AF7">
+        <v>0.28</v>
+      </c>
+      <c r="AG7">
+        <v>3.24</v>
+      </c>
+      <c r="AH7">
+        <v>2.96</v>
+      </c>
+      <c r="AI7">
+        <v>3.51</v>
+      </c>
+      <c r="AJ7">
+        <v>3.24</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM7">
+        <v>-6</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>102</v>
+      </c>
+      <c r="AO7" t="s">
         <v>69</v>
       </c>
-      <c r="Z7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC7">
-        <v>56.37</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE7">
-        <v>7.27</v>
-      </c>
-      <c r="AF7">
-        <v>0.34</v>
-      </c>
-      <c r="AG7">
-        <v>2.9</v>
-      </c>
-      <c r="AH7">
-        <v>2.56</v>
-      </c>
-      <c r="AI7">
-        <v>3.24</v>
-      </c>
-      <c r="AJ7">
-        <v>2.9</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM7">
-        <v>4</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>104</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>70</v>
-      </c>
       <c r="AP7">
-        <v>0.5097999999999999</v>
+        <v>0.539</v>
       </c>
       <c r="AQ7">
-        <v>-1.95999999999998</v>
+        <v>-7.800000000000011</v>
       </c>
       <c r="AR7">
-        <v>2.74770982501213</v>
+        <v>9.840986553974432</v>
       </c>
       <c r="AS7">
-        <v>3.212290174987849</v>
+        <v>11.64098655397444</v>
       </c>
       <c r="AT7">
-        <v>2.97999999999999</v>
+        <v>10.74098655397444</v>
       </c>
       <c r="AU7">
-        <v>0.7449999999999974</v>
+        <v>2.685246638493609</v>
       </c>
       <c r="AV7">
-        <v>6.17</v>
+        <v>5.31</v>
       </c>
       <c r="AW7">
-        <v>7.17</v>
+        <v>6.76</v>
       </c>
       <c r="AX7">
-        <v>7.8</v>
+        <v>7.43</v>
       </c>
       <c r="AY7">
         <v>1.11</v>
@@ -1906,22 +1900,22 @@
         <v>3</v>
       </c>
       <c r="BA7">
-        <v>1.88</v>
+        <v>1.54</v>
       </c>
       <c r="BB7">
-        <v>1.02</v>
+        <v>-4.01</v>
       </c>
       <c r="BC7">
-        <v>7.45</v>
+        <v>11.42</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>42.06</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>23.64</v>
       </c>
       <c r="BF7">
-        <v>0.92</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:58">
@@ -1929,19 +1923,19 @@
         <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8">
-        <v>50</v>
+        <v>48.42</v>
       </c>
       <c r="D8">
-        <v>48.52</v>
+        <v>45.85</v>
       </c>
       <c r="E8">
-        <v>1.48</v>
+        <v>2.58</v>
       </c>
       <c r="F8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s">
         <v>79</v>
@@ -1950,22 +1944,22 @@
         <v>84</v>
       </c>
       <c r="I8">
-        <v>50.75</v>
+        <v>51.37</v>
       </c>
       <c r="J8">
-        <v>49.25</v>
+        <v>48.63</v>
       </c>
       <c r="K8">
-        <v>1.5</v>
+        <v>2.73</v>
       </c>
       <c r="L8">
-        <v>0.19</v>
+        <v>0.02</v>
       </c>
       <c r="M8">
-        <v>1.69</v>
+        <v>2.76</v>
       </c>
       <c r="N8">
-        <v>1.69</v>
+        <v>2.76</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1974,106 +1968,106 @@
         <v>1</v>
       </c>
       <c r="Q8">
-        <v>50.32</v>
+        <v>50.19</v>
       </c>
       <c r="R8">
-        <v>49.68</v>
+        <v>49.81</v>
       </c>
       <c r="S8">
-        <v>0.19</v>
+        <v>0.02</v>
       </c>
       <c r="T8">
-        <v>1.69</v>
+        <v>2.76</v>
       </c>
       <c r="U8">
-        <v>0.64</v>
+        <v>0.37</v>
       </c>
       <c r="V8">
-        <v>53.53</v>
+        <v>52.35</v>
       </c>
       <c r="W8">
-        <v>46.47</v>
+        <v>47.65</v>
       </c>
       <c r="X8" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="Y8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z8" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC8">
+        <v>52.35</v>
+      </c>
+      <c r="AD8" t="s">
         <v>89</v>
       </c>
-      <c r="AA8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC8">
-        <v>53.53</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>91</v>
-      </c>
       <c r="AE8">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF8">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG8">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH8">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI8">
+        <v>3.51</v>
+      </c>
+      <c r="AJ8">
         <v>3.24</v>
       </c>
-      <c r="AJ8">
-        <v>2.9</v>
-      </c>
       <c r="AK8">
         <v>0</v>
       </c>
       <c r="AL8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AM8">
         <v>-6</v>
       </c>
       <c r="AN8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AO8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AP8">
-        <v>0.539</v>
+        <v>0.5351</v>
       </c>
       <c r="AQ8">
-        <v>-7.800000000000011</v>
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR8">
-        <v>7.686016982113116</v>
+        <v>8.755412717885292</v>
       </c>
       <c r="AS8">
-        <v>9.486016982113126</v>
+        <v>9.775412717885303</v>
       </c>
       <c r="AT8">
-        <v>8.58601698211312</v>
+        <v>9.265412717885297</v>
       </c>
       <c r="AU8">
-        <v>2.14650424552828</v>
+        <v>2.316353179471324</v>
       </c>
       <c r="AV8">
-        <v>5.31</v>
+        <v>4.14</v>
       </c>
       <c r="AW8">
-        <v>6.57</v>
+        <v>5.55</v>
       </c>
       <c r="AX8">
-        <v>7.26</v>
+        <v>6.35</v>
       </c>
       <c r="AY8">
         <v>1.11</v>
@@ -2082,22 +2076,22 @@
         <v>3</v>
       </c>
       <c r="BA8">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="BB8">
-        <v>-4.01</v>
+        <v>1.35</v>
       </c>
       <c r="BC8">
-        <v>11.42</v>
+        <v>5.75</v>
       </c>
       <c r="BD8">
-        <v>42.06</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>23.64</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>0.6899999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:58">
@@ -2105,19 +2099,19 @@
         <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9">
-        <v>47.32</v>
+        <v>48.32</v>
       </c>
       <c r="D9">
-        <v>45.6</v>
+        <v>46.18</v>
       </c>
       <c r="E9">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="F9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G9" t="s">
         <v>79</v>
@@ -2126,22 +2120,22 @@
         <v>84</v>
       </c>
       <c r="I9">
-        <v>50.93</v>
+        <v>51.14</v>
       </c>
       <c r="J9">
-        <v>49.07</v>
+        <v>48.86</v>
       </c>
       <c r="K9">
-        <v>1.86</v>
+        <v>2.28</v>
       </c>
       <c r="L9">
-        <v>-2.64</v>
+        <v>0.05</v>
       </c>
       <c r="M9">
-        <v>-0.78</v>
+        <v>2.32</v>
       </c>
       <c r="N9">
-        <v>-0.78</v>
+        <v>2.32</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -2150,106 +2144,106 @@
         <v>1</v>
       </c>
       <c r="Q9">
-        <v>49.61</v>
+        <v>49.98</v>
       </c>
       <c r="R9">
-        <v>50.39</v>
+        <v>50.02</v>
       </c>
       <c r="S9">
-        <v>-2.64</v>
+        <v>0.05</v>
       </c>
       <c r="T9">
-        <v>-0.78</v>
+        <v>2.32</v>
       </c>
       <c r="U9">
-        <v>-0.78</v>
+        <v>-0.05</v>
       </c>
       <c r="V9">
-        <v>44.91</v>
+        <v>49.76</v>
       </c>
       <c r="W9">
-        <v>55.09</v>
+        <v>50.24</v>
       </c>
       <c r="X9" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="Y9" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA9" t="s">
         <v>70</v>
       </c>
-      <c r="Z9" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA9" t="s">
+      <c r="AB9" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC9">
+        <v>49.76</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE9">
+        <v>7.86</v>
+      </c>
+      <c r="AF9">
+        <v>0.28</v>
+      </c>
+      <c r="AG9">
+        <v>3.24</v>
+      </c>
+      <c r="AH9">
+        <v>2.96</v>
+      </c>
+      <c r="AI9">
+        <v>3.51</v>
+      </c>
+      <c r="AJ9">
+        <v>3.24</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM9">
+        <v>4</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO9" t="s">
         <v>69</v>
       </c>
-      <c r="AB9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC9">
-        <v>44.91</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE9">
-        <v>7.27</v>
-      </c>
-      <c r="AF9">
-        <v>0.34</v>
-      </c>
-      <c r="AG9">
-        <v>2.9</v>
-      </c>
-      <c r="AH9">
-        <v>2.56</v>
-      </c>
-      <c r="AI9">
-        <v>3.24</v>
-      </c>
-      <c r="AJ9">
-        <v>2.9</v>
-      </c>
-      <c r="AK9">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>97</v>
-      </c>
-      <c r="AM9">
-        <v>-6</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>106</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>70</v>
-      </c>
       <c r="AP9">
-        <v>0.5351</v>
+        <v>0.5097999999999999</v>
       </c>
       <c r="AQ9">
-        <v>-7.02000000000001</v>
+        <v>-1.95999999999998</v>
       </c>
       <c r="AR9">
-        <v>5.215620294959367</v>
+        <v>1.675966859360293</v>
       </c>
       <c r="AS9">
-        <v>6.235620294959377</v>
+        <v>4.284033140639687</v>
       </c>
       <c r="AT9">
-        <v>5.725620294959372</v>
+        <v>2.97999999999999</v>
       </c>
       <c r="AU9">
-        <v>1.431405073739843</v>
+        <v>0.7449999999999974</v>
       </c>
       <c r="AV9">
-        <v>4.14</v>
+        <v>6.17</v>
       </c>
       <c r="AW9">
-        <v>5.29</v>
+        <v>7.2</v>
       </c>
       <c r="AX9">
-        <v>6.13</v>
+        <v>7.83</v>
       </c>
       <c r="AY9">
         <v>1.11</v>
@@ -2258,13 +2252,13 @@
         <v>3</v>
       </c>
       <c r="BA9">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="BB9">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="BC9">
-        <v>5.75</v>
+        <v>7.45</v>
       </c>
       <c r="BD9">
         <v>0</v>
@@ -2273,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="BF9">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="10" spans="1:58">
@@ -2281,16 +2275,16 @@
         <v>66</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10">
-        <v>46.05</v>
+        <v>45.4</v>
       </c>
       <c r="D10">
-        <v>48.32</v>
+        <v>46.12</v>
       </c>
       <c r="E10">
-        <v>-2.28</v>
+        <v>-0.73</v>
       </c>
       <c r="F10" t="s">
         <v>75</v>
@@ -2299,25 +2293,25 @@
         <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="I10">
-        <v>48.79</v>
+        <v>49.6</v>
       </c>
       <c r="J10">
-        <v>51.21</v>
+        <v>50.4</v>
       </c>
       <c r="K10">
-        <v>-2.41</v>
+        <v>-0.79</v>
       </c>
       <c r="L10">
-        <v>-1.72</v>
+        <v>-1.77</v>
       </c>
       <c r="M10">
-        <v>-4.13</v>
+        <v>-2.56</v>
       </c>
       <c r="N10">
-        <v>-4.13</v>
+        <v>-2.56</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -2326,79 +2320,79 @@
         <v>1</v>
       </c>
       <c r="Q10">
-        <v>47.93</v>
+        <v>48.72</v>
       </c>
       <c r="R10">
-        <v>52.07</v>
+        <v>51.28</v>
       </c>
       <c r="S10">
-        <v>-1.72</v>
+        <v>-1.77</v>
       </c>
       <c r="T10">
-        <v>-4.13</v>
+        <v>-2.56</v>
       </c>
       <c r="U10">
-        <v>-4.13</v>
+        <v>-2.56</v>
       </c>
       <c r="V10">
-        <v>28.76</v>
+        <v>36.52</v>
       </c>
       <c r="W10">
-        <v>71.23999999999999</v>
+        <v>63.48</v>
       </c>
       <c r="X10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Y10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Z10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AA10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AB10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AC10">
-        <v>28.76</v>
+        <v>36.52</v>
       </c>
       <c r="AD10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AE10">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF10">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG10">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH10">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI10">
+        <v>3.51</v>
+      </c>
+      <c r="AJ10">
         <v>3.24</v>
       </c>
-      <c r="AJ10">
-        <v>2.9</v>
-      </c>
       <c r="AK10">
         <v>0</v>
       </c>
       <c r="AL10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AM10">
         <v>-6</v>
       </c>
       <c r="AN10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AO10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AP10">
         <v>0.5174</v>
@@ -2407,25 +2401,25 @@
         <v>-3.47999999999999</v>
       </c>
       <c r="AR10">
-        <v>1.86896365369746</v>
+        <v>3.435838333780036</v>
       </c>
       <c r="AS10">
-        <v>0.6510363463025506</v>
+        <v>0.9158383337800258</v>
       </c>
       <c r="AT10">
-        <v>1.260000000000005</v>
+        <v>2.175838333780031</v>
       </c>
       <c r="AU10">
-        <v>0.3150000000000013</v>
+        <v>0.5439595834450077</v>
       </c>
       <c r="AV10">
         <v>5.7</v>
       </c>
       <c r="AW10">
-        <v>6.69</v>
+        <v>6.77</v>
       </c>
       <c r="AX10">
-        <v>7.37</v>
+        <v>7.44</v>
       </c>
       <c r="AY10">
         <v>1.11</v>
@@ -2457,16 +2451,16 @@
         <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C11">
-        <v>45.43</v>
+        <v>47.27</v>
       </c>
       <c r="D11">
-        <v>52.5</v>
+        <v>50.17</v>
       </c>
       <c r="E11">
-        <v>-7.07</v>
+        <v>-2.9</v>
       </c>
       <c r="F11" t="s">
         <v>76</v>
@@ -2475,25 +2469,25 @@
         <v>81</v>
       </c>
       <c r="H11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I11">
-        <v>46.39</v>
+        <v>48.51</v>
       </c>
       <c r="J11">
-        <v>53.61</v>
+        <v>51.49</v>
       </c>
       <c r="K11">
-        <v>-7.22</v>
+        <v>-2.98</v>
       </c>
       <c r="L11">
-        <v>1.2</v>
+        <v>1.78</v>
       </c>
       <c r="M11">
-        <v>-6.01</v>
+        <v>-1.2</v>
       </c>
       <c r="N11">
-        <v>-6.01</v>
+        <v>-1.2</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -2502,79 +2496,79 @@
         <v>1</v>
       </c>
       <c r="Q11">
-        <v>46.99</v>
+        <v>48.13</v>
       </c>
       <c r="R11">
-        <v>53.01</v>
+        <v>51.87</v>
       </c>
       <c r="S11">
-        <v>1.2</v>
+        <v>1.78</v>
       </c>
       <c r="T11">
-        <v>-6.01</v>
+        <v>-1.2</v>
       </c>
       <c r="U11">
-        <v>-6.01</v>
+        <v>-3.74</v>
       </c>
       <c r="V11">
-        <v>17.92</v>
+        <v>30.07</v>
       </c>
       <c r="W11">
-        <v>82.08</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="X11" t="s">
         <v>81</v>
       </c>
       <c r="Y11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Z11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AA11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AB11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AC11">
-        <v>17.92</v>
+        <v>30.07</v>
       </c>
       <c r="AD11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AE11">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF11">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG11">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH11">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI11">
+        <v>3.51</v>
+      </c>
+      <c r="AJ11">
         <v>3.24</v>
       </c>
-      <c r="AJ11">
-        <v>2.9</v>
-      </c>
       <c r="AK11">
         <v>0</v>
       </c>
       <c r="AL11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AM11">
         <v>-10</v>
       </c>
       <c r="AN11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AO11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AP11">
         <v>0.6258</v>
@@ -2583,25 +2577,25 @@
         <v>-25.16000000000001</v>
       </c>
       <c r="AR11">
-        <v>3.988358582490165</v>
+        <v>8.804477444369347</v>
       </c>
       <c r="AS11">
-        <v>19.14835858249018</v>
+        <v>23.96447744436936</v>
       </c>
       <c r="AT11">
-        <v>11.56835858249017</v>
+        <v>16.38447744436935</v>
       </c>
       <c r="AU11">
-        <v>2.892089645622542</v>
+        <v>4.096119361092338</v>
       </c>
       <c r="AV11">
         <v>4.13</v>
       </c>
       <c r="AW11">
-        <v>5.77</v>
+        <v>6.47</v>
       </c>
       <c r="AX11">
-        <v>6.55</v>
+        <v>7.17</v>
       </c>
       <c r="AY11">
         <v>1.11</v>
@@ -2633,16 +2627,16 @@
         <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12">
-        <v>30.1</v>
+        <v>27.05</v>
       </c>
       <c r="D12">
-        <v>46.97</v>
+        <v>44.9</v>
       </c>
       <c r="E12">
-        <v>-16.87</v>
+        <v>-17.85</v>
       </c>
       <c r="F12" t="s">
         <v>77</v>
@@ -2654,22 +2648,22 @@
         <v>85</v>
       </c>
       <c r="I12">
-        <v>39.06</v>
+        <v>37.6</v>
       </c>
       <c r="J12">
-        <v>60.94</v>
+        <v>62.4</v>
       </c>
       <c r="K12">
-        <v>-21.89</v>
+        <v>-24.81</v>
       </c>
       <c r="L12">
-        <v>-6.31</v>
+        <v>-6.51</v>
       </c>
       <c r="M12">
-        <v>-28.2</v>
+        <v>-31.32</v>
       </c>
       <c r="N12">
-        <v>-28.2</v>
+        <v>-31.32</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2678,19 +2672,19 @@
         <v>1</v>
       </c>
       <c r="Q12">
-        <v>35.9</v>
+        <v>34.34</v>
       </c>
       <c r="R12">
-        <v>64.09999999999999</v>
+        <v>65.66</v>
       </c>
       <c r="S12">
-        <v>-6.31</v>
+        <v>-6.51</v>
       </c>
       <c r="T12">
-        <v>-28.2</v>
+        <v>-31.32</v>
       </c>
       <c r="U12">
-        <v>-28.2</v>
+        <v>-31.32</v>
       </c>
       <c r="V12">
         <v>0.1</v>
@@ -2702,55 +2696,55 @@
         <v>82</v>
       </c>
       <c r="Y12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Z12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AA12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AB12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AC12">
         <v>0.1</v>
       </c>
       <c r="AD12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AE12">
-        <v>7.27</v>
+        <v>7.86</v>
       </c>
       <c r="AF12">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AG12">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH12">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AI12">
+        <v>3.51</v>
+      </c>
+      <c r="AJ12">
         <v>3.24</v>
       </c>
-      <c r="AJ12">
-        <v>2.9</v>
-      </c>
       <c r="AK12">
         <v>0</v>
       </c>
       <c r="AL12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AM12">
         <v>-10</v>
       </c>
       <c r="AN12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AO12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AP12">
         <v>0.5501</v>
@@ -2759,25 +2753,25 @@
         <v>-10.02000000000001</v>
       </c>
       <c r="AR12">
-        <v>18.19535625398524</v>
+        <v>21.32320758340596</v>
       </c>
       <c r="AS12">
-        <v>18.17535625398523</v>
+        <v>21.30320758340595</v>
       </c>
       <c r="AT12">
-        <v>18.18535625398524</v>
+        <v>21.31320758340595</v>
       </c>
       <c r="AU12">
-        <v>4.546339063496309</v>
+        <v>5.328301895851488</v>
       </c>
       <c r="AV12">
         <v>4.43</v>
       </c>
       <c r="AW12">
-        <v>7.29</v>
+        <v>7.92</v>
       </c>
       <c r="AX12">
-        <v>7.91</v>
+        <v>8.5</v>
       </c>
       <c r="AY12">
         <v>1.11</v>

--- a/outputs/Block5B_Senate_Race_Attribution.xlsx
+++ b/outputs/Block5B_Senate_Race_Attribution.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="112">
   <si>
     <t>STATE</t>
   </si>
@@ -190,27 +190,27 @@
     <t>Mean Comparability Weight</t>
   </si>
   <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
     <t>North Carolina</t>
   </si>
   <si>
-    <t>Georgia</t>
-  </si>
-  <si>
-    <t>New Hampshire</t>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>Texas</t>
   </si>
   <si>
     <t>Ohio</t>
   </si>
   <si>
-    <t>Michigan</t>
-  </si>
-  <si>
     <t>Alaska</t>
   </si>
   <si>
-    <t>Texas</t>
-  </si>
-  <si>
     <t>Maine</t>
   </si>
   <si>
@@ -220,27 +220,30 @@
     <t>Nebraska</t>
   </si>
   <si>
+    <t>Kansas</t>
+  </si>
+  <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>D</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
-    <t>D</t>
+    <t>DSenLikPollH (&gt;5%&lt;=10%)</t>
   </si>
   <si>
     <t>RSenLikPollLD (&gt;5%&lt;=10%)</t>
   </si>
   <si>
-    <t>DSenLikPollH (&gt;5%&lt;=10%)</t>
+    <t>DSenLeanPollH (&gt;1&lt;=5%)</t>
   </si>
   <si>
     <t>RSenLeanPollLD (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>DSenLeanPollH (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
     <t>RSenTosPoll (&lt;=1%)</t>
   </si>
   <si>
@@ -274,12 +277,15 @@
     <t>Safe</t>
   </si>
   <si>
+    <t>D Safe</t>
+  </si>
+  <si>
+    <t>Democratic Hold</t>
+  </si>
+  <si>
     <t>Democratic Flip</t>
   </si>
   <si>
-    <t>Democratic Hold</t>
-  </si>
-  <si>
     <t>Republican Hold</t>
   </si>
   <si>
@@ -292,42 +298,45 @@
     <t>D+2</t>
   </si>
   <si>
+    <t>EVEN</t>
+  </si>
+  <si>
+    <t>R+6</t>
+  </si>
+  <si>
     <t>R+5</t>
   </si>
   <si>
-    <t>EVEN</t>
-  </si>
-  <si>
-    <t>R+6</t>
-  </si>
-  <si>
     <t>D+4</t>
   </si>
   <si>
     <t>R+10</t>
   </si>
   <si>
+    <t>R+8</t>
+  </si>
+  <si>
+    <t>50.62% D</t>
+  </si>
+  <si>
+    <t>56.64% D</t>
+  </si>
+  <si>
     <t>48.69% R</t>
   </si>
   <si>
-    <t>50.62% D</t>
-  </si>
-  <si>
-    <t>56.64% D</t>
+    <t>49.90% D</t>
+  </si>
+  <si>
+    <t>53.51% R</t>
   </si>
   <si>
     <t>Appointed (2025)[p]</t>
   </si>
   <si>
-    <t>49.90% D</t>
-  </si>
-  <si>
     <t>53.90% R</t>
   </si>
   <si>
-    <t>53.51% R</t>
-  </si>
-  <si>
     <t>50.98% R</t>
   </si>
   <si>
@@ -335,6 +344,9 @@
   </si>
   <si>
     <t>62.58% R (2024 sp.)[o]</t>
+  </si>
+  <si>
+    <t>53.22% R</t>
   </si>
   <si>
     <t>55.01% R</t>
@@ -695,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BF12"/>
+  <dimension ref="A1:BF13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:58">
@@ -879,175 +891,175 @@
         <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2">
-        <v>49.92</v>
+        <v>51.87500000000001</v>
       </c>
       <c r="D2">
-        <v>41.4</v>
+        <v>43.4</v>
       </c>
       <c r="E2">
-        <v>8.52</v>
+        <v>8.475000000000001</v>
       </c>
       <c r="F2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I2">
-        <v>54.67</v>
+        <v>54.44765153503018</v>
       </c>
       <c r="J2">
-        <v>45.33</v>
+        <v>45.55234846496982</v>
       </c>
       <c r="K2">
-        <v>9.33</v>
+        <v>8.895303070060358</v>
       </c>
       <c r="L2">
-        <v>-0.18</v>
+        <v>4.259560104663242</v>
       </c>
       <c r="M2">
-        <v>9.16</v>
+        <v>13.1548631747236</v>
       </c>
       <c r="N2">
-        <v>9.16</v>
+        <v>13.1548631747236</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P2">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q2">
-        <v>54.58</v>
+        <v>56.04498657427889</v>
       </c>
       <c r="R2">
-        <v>45.42</v>
+        <v>43.95501342572111</v>
       </c>
       <c r="S2">
-        <v>-0.18</v>
+        <v>3.194670078497431</v>
       </c>
       <c r="T2">
-        <v>9.16</v>
+        <v>12.08997314855779</v>
       </c>
       <c r="U2">
-        <v>9.16</v>
+        <v>12.08997314855779</v>
       </c>
       <c r="V2">
-        <v>91.81</v>
+        <v>97.15805023929981</v>
       </c>
       <c r="W2">
-        <v>8.19</v>
+        <v>2.841949760700191</v>
       </c>
       <c r="X2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="Y2" t="s">
         <v>70</v>
       </c>
       <c r="Z2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA2" t="s">
         <v>70</v>
       </c>
       <c r="AB2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AC2">
-        <v>91.81</v>
+        <v>2.841949760700191</v>
       </c>
       <c r="AD2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AE2">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF2">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>3.24</v>
+        <v>-0</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.844443629792535</v>
       </c>
       <c r="AL2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AM2">
         <v>-1</v>
       </c>
       <c r="AN2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AO2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AP2">
-        <v>0.4869</v>
+        <v>0.5062</v>
       </c>
       <c r="AQ2">
-        <v>2.620000000000005</v>
+        <v>1.239999999999995</v>
       </c>
       <c r="AR2">
-        <v>10.15789243716453</v>
+        <v>13.08997314855779</v>
       </c>
       <c r="AS2">
-        <v>6.53789243716453</v>
+        <v>10.84997314855779</v>
       </c>
       <c r="AT2">
-        <v>8.347892437164532</v>
+        <v>11.96997314855779</v>
       </c>
       <c r="AU2">
-        <v>2.086973109291133</v>
+        <v>2.992493287139448</v>
       </c>
       <c r="AV2">
-        <v>4.53</v>
+        <v>5.482188815058572</v>
       </c>
       <c r="AW2">
-        <v>5.8</v>
+        <v>5.771015368998557</v>
       </c>
       <c r="AX2">
-        <v>6.58</v>
+        <v>6.34795245875231</v>
       </c>
       <c r="AY2">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ2">
         <v>3</v>
       </c>
       <c r="BA2">
-        <v>2.17</v>
+        <v>2.211929341045432</v>
       </c>
       <c r="BB2">
-        <v>0.28</v>
+        <v>0.7423884751670249</v>
       </c>
       <c r="BC2">
-        <v>2.95</v>
+        <v>5.209225288644337</v>
       </c>
       <c r="BD2">
-        <v>30.1</v>
+        <v>0</v>
       </c>
       <c r="BE2">
-        <v>30.1</v>
+        <v>44.3421030056761</v>
       </c>
       <c r="BF2">
-        <v>0.9399999999999999</v>
+        <v>0.9584693849829202</v>
       </c>
     </row>
     <row r="3" spans="1:58">
@@ -1058,172 +1070,172 @@
         <v>70</v>
       </c>
       <c r="C3">
-        <v>51.22</v>
+        <v>49.2</v>
       </c>
       <c r="D3">
-        <v>43.62</v>
+        <v>42.675</v>
       </c>
       <c r="E3">
-        <v>7.6</v>
+        <v>6.525</v>
       </c>
       <c r="F3" t="s">
         <v>72</v>
       </c>
       <c r="G3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I3">
-        <v>54.01</v>
+        <v>53.55102040816327</v>
       </c>
       <c r="J3">
-        <v>45.99</v>
+        <v>46.44897959183673</v>
       </c>
       <c r="K3">
-        <v>8.01</v>
+        <v>7.102040816326536</v>
       </c>
       <c r="L3">
-        <v>4.11</v>
+        <v>2.101444859661521</v>
       </c>
       <c r="M3">
-        <v>12.12</v>
+        <v>9.203485675988057</v>
       </c>
       <c r="N3">
-        <v>12.12</v>
+        <v>9.203485675988057</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P3">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q3">
-        <v>54.87</v>
+        <v>54.33906223053634</v>
       </c>
       <c r="R3">
-        <v>45.13</v>
+        <v>45.66093776946366</v>
       </c>
       <c r="S3">
-        <v>4.11</v>
+        <v>1.576083644746141</v>
       </c>
       <c r="T3">
-        <v>12.12</v>
+        <v>8.678124461072677</v>
       </c>
       <c r="U3">
-        <v>9.74</v>
+        <v>8.678124461072677</v>
       </c>
       <c r="V3">
-        <v>90.34</v>
+        <v>94.84509234166477</v>
       </c>
       <c r="W3">
-        <v>9.66</v>
+        <v>5.154907658335239</v>
       </c>
       <c r="X3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y3" t="s">
         <v>70</v>
       </c>
       <c r="Z3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AA3" t="s">
         <v>70</v>
       </c>
       <c r="AB3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AC3">
-        <v>9.66</v>
+        <v>5.154907658335239</v>
       </c>
       <c r="AD3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AE3">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF3">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.28</v>
+        <v>-0</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>0.909952316559551</v>
       </c>
       <c r="AL3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AO3" t="s">
         <v>70</v>
       </c>
       <c r="AP3">
-        <v>0.5062</v>
+        <v>0.5664</v>
       </c>
       <c r="AQ3">
-        <v>1.239999999999995</v>
+        <v>13.28</v>
       </c>
       <c r="AR3">
-        <v>13.11951692303765</v>
+        <v>6.678124461072677</v>
       </c>
       <c r="AS3">
-        <v>10.87951692303766</v>
+        <v>4.601875538927324</v>
       </c>
       <c r="AT3">
-        <v>11.99951692303765</v>
+        <v>5.640000000000001</v>
       </c>
       <c r="AU3">
-        <v>2.999879230759413</v>
+        <v>1.41</v>
       </c>
       <c r="AV3">
-        <v>5.19</v>
+        <v>5.112371008372736</v>
       </c>
       <c r="AW3">
-        <v>6.82</v>
+        <v>4.620884424478711</v>
       </c>
       <c r="AX3">
-        <v>7.48</v>
+        <v>5.323951060420438</v>
       </c>
       <c r="AY3">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ3">
         <v>3</v>
       </c>
       <c r="BA3">
-        <v>2.21</v>
+        <v>2.230264441281014</v>
       </c>
       <c r="BB3">
-        <v>0.74</v>
+        <v>0.8055665595386128</v>
       </c>
       <c r="BC3">
-        <v>5.21</v>
+        <v>5.981300614496139</v>
       </c>
       <c r="BD3">
         <v>0</v>
       </c>
       <c r="BE3">
-        <v>44.34</v>
+        <v>0</v>
       </c>
       <c r="BF3">
-        <v>0.96</v>
+        <v>0.9698252308898075</v>
       </c>
     </row>
     <row r="4" spans="1:58">
@@ -1231,175 +1243,175 @@
         <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4">
-        <v>47.65</v>
+        <v>50.34999999999999</v>
       </c>
       <c r="D4">
-        <v>41.98</v>
+        <v>42.25</v>
       </c>
       <c r="E4">
-        <v>5.68</v>
+        <v>8.1</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I4">
-        <v>53.17</v>
+        <v>54.37365010799135</v>
       </c>
       <c r="J4">
-        <v>46.83</v>
+        <v>45.62634989200864</v>
       </c>
       <c r="K4">
-        <v>6.33</v>
+        <v>8.747300215982712</v>
       </c>
       <c r="L4">
-        <v>1.06</v>
+        <v>-1.321479089073864</v>
       </c>
       <c r="M4">
-        <v>7.39</v>
+        <v>7.425821126908847</v>
       </c>
       <c r="N4">
-        <v>7.39</v>
+        <v>7.425821126908847</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P4">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q4">
-        <v>52.82</v>
+        <v>53.87809544958866</v>
       </c>
       <c r="R4">
-        <v>47.18</v>
+        <v>46.12190455041134</v>
       </c>
       <c r="S4">
-        <v>1.06</v>
+        <v>-0.9911093168053986</v>
       </c>
       <c r="T4">
-        <v>7.39</v>
+        <v>7.756190899177313</v>
       </c>
       <c r="U4">
-        <v>5.65</v>
+        <v>7.756190899177313</v>
       </c>
       <c r="V4">
-        <v>79.51000000000001</v>
+        <v>93.22560446351913</v>
       </c>
       <c r="W4">
-        <v>20.49</v>
+        <v>6.774395536480871</v>
       </c>
       <c r="X4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y4" t="s">
         <v>70</v>
       </c>
       <c r="Z4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AA4" t="s">
         <v>70</v>
       </c>
       <c r="AB4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC4">
-        <v>20.49</v>
+        <v>93.22560446351913</v>
       </c>
       <c r="AD4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AE4">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF4">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>0.5722172308539429</v>
       </c>
       <c r="AL4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AM4">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AN4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AO4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AP4">
-        <v>0.5664</v>
+        <v>0.4869</v>
       </c>
       <c r="AQ4">
-        <v>13.28</v>
+        <v>2.620000000000005</v>
       </c>
       <c r="AR4">
-        <v>5.39330665909661</v>
+        <v>8.756190899177312</v>
       </c>
       <c r="AS4">
-        <v>5.886693340903391</v>
+        <v>5.136190899177309</v>
       </c>
       <c r="AT4">
-        <v>5.640000000000001</v>
+        <v>6.94619089917731</v>
       </c>
       <c r="AU4">
-        <v>1.41</v>
+        <v>1.736547724794328</v>
       </c>
       <c r="AV4">
-        <v>4.99</v>
+        <v>4.808352845952818</v>
       </c>
       <c r="AW4">
-        <v>6.11</v>
+        <v>4.472531501293391</v>
       </c>
       <c r="AX4">
-        <v>6.85</v>
+        <v>5.195711699028696</v>
       </c>
       <c r="AY4">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ4">
         <v>3</v>
       </c>
       <c r="BA4">
-        <v>2.23</v>
+        <v>2.170415722150866</v>
       </c>
       <c r="BB4">
-        <v>0.8100000000000001</v>
+        <v>0.275052926652725</v>
       </c>
       <c r="BC4">
-        <v>5.98</v>
+        <v>2.954610092474855</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>30.09640135085562</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>30.09640135085562</v>
       </c>
       <c r="BF4">
-        <v>0.97</v>
+        <v>0.9401657373535796</v>
       </c>
     </row>
     <row r="5" spans="1:58">
@@ -1407,70 +1419,70 @@
         <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5">
-        <v>48.4</v>
+        <v>48.175</v>
       </c>
       <c r="D5">
-        <v>44.82</v>
+        <v>45</v>
       </c>
       <c r="E5">
-        <v>3.58</v>
+        <v>3.175</v>
       </c>
       <c r="F5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5">
-        <v>51.92</v>
+        <v>51.70378320364904</v>
       </c>
       <c r="J5">
-        <v>48.08</v>
+        <v>48.29621679635095</v>
       </c>
       <c r="K5">
-        <v>3.83</v>
+        <v>3.407566407298091</v>
       </c>
       <c r="L5">
-        <v>-0.3</v>
+        <v>2.219283990383333</v>
       </c>
       <c r="M5">
-        <v>3.54</v>
+        <v>5.626850397681425</v>
       </c>
       <c r="N5">
-        <v>3.54</v>
+        <v>5.626850397681425</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q5">
-        <v>51.77</v>
+        <v>52.5360147000428</v>
       </c>
       <c r="R5">
-        <v>48.23</v>
+        <v>47.4639852999572</v>
       </c>
       <c r="S5">
-        <v>-0.3</v>
+        <v>1.664462992787501</v>
       </c>
       <c r="T5">
-        <v>3.54</v>
+        <v>5.072029400085592</v>
       </c>
       <c r="U5">
-        <v>3.54</v>
+        <v>5.072029400085592</v>
       </c>
       <c r="V5">
-        <v>71.27</v>
+        <v>83.72921551043582</v>
       </c>
       <c r="W5">
-        <v>28.73</v>
+        <v>16.27078448956417</v>
       </c>
       <c r="X5" t="s">
         <v>79</v>
@@ -1479,91 +1491,103 @@
         <v>70</v>
       </c>
       <c r="Z5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA5" t="s">
         <v>70</v>
       </c>
       <c r="AB5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AC5">
-        <v>71.27</v>
+        <v>16.27078448956417</v>
       </c>
       <c r="AD5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AE5">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF5">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>3.24</v>
+        <v>-0</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>0.9609781569420333</v>
       </c>
       <c r="AL5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AM5">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP5">
+        <v>0.499</v>
+      </c>
+      <c r="AQ5">
+        <v>-0.2000000000000028</v>
       </c>
       <c r="AR5">
-        <v>8.536611196062932</v>
+        <v>5.072029400085592</v>
+      </c>
+      <c r="AS5">
+        <v>5.272029400085595</v>
       </c>
       <c r="AT5">
-        <v>8.536611196062932</v>
+        <v>5.172029400085593</v>
       </c>
       <c r="AU5">
-        <v>2.134152799015733</v>
+        <v>1.293007350021398</v>
       </c>
       <c r="AV5">
-        <v>4.15</v>
+        <v>4.890566271054463</v>
       </c>
       <c r="AW5">
-        <v>5.49</v>
+        <v>4.428317085264829</v>
       </c>
       <c r="AX5">
-        <v>6.3</v>
+        <v>5.157700479575209</v>
       </c>
       <c r="AY5">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA5">
-        <v>2.8</v>
+        <v>1.928319091839648</v>
       </c>
       <c r="BB5">
-        <v>0.17</v>
+        <v>-0.6920346275003579</v>
       </c>
       <c r="BC5">
-        <v>2.96</v>
+        <v>1.192072171556674</v>
       </c>
       <c r="BD5">
-        <v>17.49</v>
+        <v>0</v>
       </c>
       <c r="BE5">
         <v>0</v>
       </c>
       <c r="BF5">
-        <v>0.96</v>
+        <v>0.9413992011197729</v>
       </c>
     </row>
     <row r="6" spans="1:58">
@@ -1571,166 +1595,166 @@
         <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6">
-        <v>47.98</v>
+        <v>48.675</v>
       </c>
       <c r="D6">
-        <v>45.52</v>
+        <v>45.65</v>
       </c>
       <c r="E6">
-        <v>2.45</v>
+        <v>3.025</v>
       </c>
       <c r="F6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I6">
-        <v>51.31</v>
+        <v>51.60349854227405</v>
       </c>
       <c r="J6">
-        <v>48.69</v>
+        <v>48.39650145772595</v>
       </c>
       <c r="K6">
-        <v>2.62</v>
+        <v>3.206997084548107</v>
       </c>
       <c r="L6">
-        <v>2.32</v>
+        <v>-1.2681457739171</v>
       </c>
       <c r="M6">
-        <v>4.94</v>
+        <v>1.938851310631006</v>
       </c>
       <c r="N6">
-        <v>4.94</v>
+        <v>1.938851310631006</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P6">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q6">
-        <v>51.31</v>
+        <v>51.12794387705514</v>
       </c>
       <c r="R6">
-        <v>48.69</v>
+        <v>48.87205612294486</v>
       </c>
       <c r="S6">
-        <v>2.32</v>
+        <v>-0.9511093304378253</v>
       </c>
       <c r="T6">
-        <v>4.94</v>
+        <v>2.255887754110281</v>
       </c>
       <c r="U6">
-        <v>2.62</v>
+        <v>2.255887754110281</v>
       </c>
       <c r="V6">
-        <v>65.48</v>
+        <v>67.08308487070286</v>
       </c>
       <c r="W6">
-        <v>34.52</v>
+        <v>32.91691512929713</v>
       </c>
       <c r="X6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y6" t="s">
         <v>70</v>
       </c>
       <c r="Z6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AA6" t="s">
         <v>70</v>
       </c>
       <c r="AB6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC6">
-        <v>34.52</v>
+        <v>67.08308487070286</v>
       </c>
       <c r="AD6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AE6">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF6">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>0.549123227957043</v>
       </c>
       <c r="AL6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AN6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AO6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AP6">
-        <v>0.499</v>
+        <v>0.5351</v>
       </c>
       <c r="AQ6">
-        <v>-0.2000000000000028</v>
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR6">
-        <v>4.943406372496832</v>
+        <v>8.255887754110281</v>
       </c>
       <c r="AS6">
-        <v>5.143406372496835</v>
+        <v>9.275887754110292</v>
       </c>
       <c r="AT6">
-        <v>5.043406372496833</v>
+        <v>8.765887754110286</v>
       </c>
       <c r="AU6">
-        <v>1.260851593124208</v>
+        <v>2.191471938527572</v>
       </c>
       <c r="AV6">
-        <v>4.72</v>
+        <v>4.345503062353619</v>
       </c>
       <c r="AW6">
-        <v>5.81</v>
+        <v>4.362627316035638</v>
       </c>
       <c r="AX6">
-        <v>6.58</v>
+        <v>5.101411483891715</v>
       </c>
       <c r="AY6">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ6">
         <v>3</v>
       </c>
       <c r="BA6">
-        <v>1.93</v>
+        <v>1.930645252303767</v>
       </c>
       <c r="BB6">
-        <v>-0.6899999999999999</v>
+        <v>1.354753062157686</v>
       </c>
       <c r="BC6">
-        <v>1.19</v>
+        <v>5.754964092348529</v>
       </c>
       <c r="BD6">
         <v>0</v>
@@ -1739,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="BF6">
-        <v>0.9399999999999999</v>
+        <v>0.9442145399410329</v>
       </c>
     </row>
     <row r="7" spans="1:58">
@@ -1747,175 +1771,163 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7">
-        <v>50.15</v>
+        <v>48.225</v>
       </c>
       <c r="D7">
-        <v>48.38</v>
+        <v>45.1</v>
       </c>
       <c r="E7">
-        <v>1.78</v>
+        <v>3.125</v>
       </c>
       <c r="F7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I7">
-        <v>50.9</v>
+        <v>51.67425663005626</v>
       </c>
       <c r="J7">
-        <v>49.1</v>
+        <v>48.32574336994374</v>
       </c>
       <c r="K7">
-        <v>1.8</v>
+        <v>3.348513260112512</v>
       </c>
       <c r="L7">
-        <v>2.04</v>
+        <v>-1.794861267366732</v>
       </c>
       <c r="M7">
-        <v>3.84</v>
+        <v>1.553651992745779</v>
       </c>
       <c r="N7">
-        <v>3.84</v>
+        <v>1.553651992745779</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q7">
-        <v>50.58</v>
+        <v>51.00118365479373</v>
       </c>
       <c r="R7">
-        <v>49.42</v>
+        <v>48.99881634520627</v>
       </c>
       <c r="S7">
-        <v>2.04</v>
+        <v>-1.346145950525049</v>
       </c>
       <c r="T7">
-        <v>3.84</v>
+        <v>2.002367309587462</v>
       </c>
       <c r="U7">
-        <v>1.16</v>
+        <v>2.002367309587462</v>
       </c>
       <c r="V7">
-        <v>56.21</v>
+        <v>65.26388699510164</v>
       </c>
       <c r="W7">
-        <v>43.79</v>
+        <v>34.73611300489836</v>
       </c>
       <c r="X7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y7" t="s">
         <v>70</v>
       </c>
       <c r="Z7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AA7" t="s">
         <v>70</v>
       </c>
       <c r="AB7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AC7">
-        <v>56.21</v>
+        <v>65.26388699510164</v>
       </c>
       <c r="AD7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AE7">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF7">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH7">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>0.7771977269041618</v>
       </c>
       <c r="AL7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AM7">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AN7" t="s">
-        <v>102</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AP7">
-        <v>0.539</v>
-      </c>
-      <c r="AQ7">
-        <v>-7.800000000000011</v>
+        <v>105</v>
       </c>
       <c r="AR7">
-        <v>9.840986553974432</v>
-      </c>
-      <c r="AS7">
-        <v>11.64098655397444</v>
+        <v>7.002367309587463</v>
       </c>
       <c r="AT7">
-        <v>10.74098655397444</v>
+        <v>7.002367309587463</v>
       </c>
       <c r="AU7">
-        <v>2.685246638493609</v>
+        <v>1.750591827396866</v>
       </c>
       <c r="AV7">
-        <v>5.31</v>
+        <v>4.567515257270437</v>
       </c>
       <c r="AW7">
-        <v>6.76</v>
+        <v>4.363504132448985</v>
       </c>
       <c r="AX7">
-        <v>7.43</v>
+        <v>5.102161340379323</v>
       </c>
       <c r="AY7">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA7">
-        <v>1.54</v>
+        <v>2.797261014127842</v>
       </c>
       <c r="BB7">
-        <v>-4.01</v>
+        <v>0.1730167113317724</v>
       </c>
       <c r="BC7">
-        <v>11.42</v>
+        <v>2.956526743070407</v>
       </c>
       <c r="BD7">
-        <v>42.06</v>
+        <v>17.4915896825486</v>
       </c>
       <c r="BE7">
-        <v>23.64</v>
+        <v>0</v>
       </c>
       <c r="BF7">
-        <v>0.6899999999999999</v>
+        <v>0.956231216651788</v>
       </c>
     </row>
     <row r="8" spans="1:58">
@@ -1923,70 +1935,70 @@
         <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C8">
-        <v>48.42</v>
+        <v>49.325</v>
       </c>
       <c r="D8">
-        <v>45.85</v>
+        <v>47.475</v>
       </c>
       <c r="E8">
-        <v>2.58</v>
+        <v>1.85</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I8">
-        <v>51.37</v>
+        <v>50.95557851239669</v>
       </c>
       <c r="J8">
-        <v>48.63</v>
+        <v>49.0444214876033</v>
       </c>
       <c r="K8">
-        <v>2.73</v>
+        <v>1.91115702479339</v>
       </c>
       <c r="L8">
-        <v>0.02</v>
+        <v>-0.1172224213495152</v>
       </c>
       <c r="M8">
-        <v>2.76</v>
+        <v>1.793934603443875</v>
       </c>
       <c r="N8">
-        <v>2.76</v>
+        <v>1.793934603443875</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P8">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q8">
-        <v>50.19</v>
+        <v>50.91162010439063</v>
       </c>
       <c r="R8">
-        <v>49.81</v>
+        <v>49.08837989560937</v>
       </c>
       <c r="S8">
-        <v>0.02</v>
+        <v>-0.08791681601213641</v>
       </c>
       <c r="T8">
-        <v>2.76</v>
+        <v>1.823240208781253</v>
       </c>
       <c r="U8">
-        <v>0.37</v>
+        <v>1.823240208781253</v>
       </c>
       <c r="V8">
-        <v>52.35</v>
+        <v>61.79014903031504</v>
       </c>
       <c r="W8">
-        <v>47.65</v>
+        <v>38.20985096968496</v>
       </c>
       <c r="X8" t="s">
         <v>80</v>
@@ -1995,103 +2007,103 @@
         <v>70</v>
       </c>
       <c r="Z8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AA8" t="s">
         <v>70</v>
       </c>
       <c r="AB8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AC8">
-        <v>52.35</v>
+        <v>61.79014903031504</v>
       </c>
       <c r="AD8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AE8">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF8">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>0.05075879739090176</v>
       </c>
       <c r="AL8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AM8">
         <v>-6</v>
       </c>
       <c r="AN8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AO8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AP8">
-        <v>0.5351</v>
+        <v>0.539</v>
       </c>
       <c r="AQ8">
-        <v>-7.02000000000001</v>
+        <v>-7.800000000000011</v>
       </c>
       <c r="AR8">
-        <v>8.755412717885292</v>
+        <v>7.823240208781254</v>
       </c>
       <c r="AS8">
-        <v>9.775412717885303</v>
+        <v>9.623240208781265</v>
       </c>
       <c r="AT8">
-        <v>9.265412717885297</v>
+        <v>8.723240208781259</v>
       </c>
       <c r="AU8">
-        <v>2.316353179471324</v>
+        <v>2.180810052195315</v>
       </c>
       <c r="AV8">
-        <v>4.14</v>
+        <v>5.898436507750732</v>
       </c>
       <c r="AW8">
-        <v>5.55</v>
+        <v>5.472672171724974</v>
       </c>
       <c r="AX8">
-        <v>6.35</v>
+        <v>6.077994959568073</v>
       </c>
       <c r="AY8">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ8">
         <v>3</v>
       </c>
       <c r="BA8">
-        <v>1.93</v>
+        <v>1.541161542643699</v>
       </c>
       <c r="BB8">
-        <v>1.35</v>
+        <v>-4.006524474852094</v>
       </c>
       <c r="BC8">
-        <v>5.75</v>
+        <v>11.41694912221213</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>42.06393827345702</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>23.63541255450272</v>
       </c>
       <c r="BF8">
-        <v>0.9399999999999999</v>
+        <v>0.6873186760847522</v>
       </c>
     </row>
     <row r="9" spans="1:58">
@@ -2099,124 +2111,124 @@
         <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9">
-        <v>48.32</v>
+        <v>48.25</v>
       </c>
       <c r="D9">
-        <v>46.18</v>
+        <v>46.575</v>
       </c>
       <c r="E9">
-        <v>2.15</v>
+        <v>1.675</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I9">
-        <v>51.14</v>
+        <v>50.8832059056156</v>
       </c>
       <c r="J9">
-        <v>48.86</v>
+        <v>49.11679409438439</v>
       </c>
       <c r="K9">
-        <v>2.28</v>
+        <v>1.766411811231215</v>
       </c>
       <c r="L9">
-        <v>0.05</v>
+        <v>-1.225993544904167</v>
       </c>
       <c r="M9">
-        <v>2.32</v>
+        <v>0.5404182663270487</v>
       </c>
       <c r="N9">
-        <v>2.32</v>
+        <v>0.5404182663270487</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P9">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q9">
-        <v>49.98</v>
+        <v>50.42345832627655</v>
       </c>
       <c r="R9">
-        <v>50.02</v>
+        <v>49.57654167372345</v>
       </c>
       <c r="S9">
-        <v>0.05</v>
+        <v>-0.9194951586781249</v>
       </c>
       <c r="T9">
-        <v>2.32</v>
+        <v>0.8469166525530903</v>
       </c>
       <c r="U9">
-        <v>-0.05</v>
+        <v>0.8469166525530903</v>
       </c>
       <c r="V9">
-        <v>49.76</v>
+        <v>55.65418073718285</v>
       </c>
       <c r="W9">
-        <v>50.24</v>
+        <v>44.34581926281715</v>
       </c>
       <c r="X9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Y9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA9" t="s">
         <v>70</v>
       </c>
       <c r="AB9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AC9">
-        <v>49.76</v>
+        <v>55.65418073718285</v>
       </c>
       <c r="AD9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AE9">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF9">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>0.530870777381373</v>
       </c>
       <c r="AL9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AM9">
         <v>4</v>
       </c>
       <c r="AN9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="AO9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AP9">
         <v>0.5097999999999999</v>
@@ -2225,10 +2237,10 @@
         <v>-1.95999999999998</v>
       </c>
       <c r="AR9">
-        <v>1.675966859360293</v>
+        <v>3.15308334744691</v>
       </c>
       <c r="AS9">
-        <v>4.284033140639687</v>
+        <v>2.80691665255307</v>
       </c>
       <c r="AT9">
         <v>2.97999999999999</v>
@@ -2237,28 +2249,28 @@
         <v>0.7449999999999974</v>
       </c>
       <c r="AV9">
-        <v>6.17</v>
+        <v>6.166256775636249</v>
       </c>
       <c r="AW9">
-        <v>7.2</v>
+        <v>5.33631557212084</v>
       </c>
       <c r="AX9">
-        <v>7.83</v>
+        <v>5.955513908523875</v>
       </c>
       <c r="AY9">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ9">
         <v>3</v>
       </c>
       <c r="BA9">
-        <v>1.88</v>
+        <v>1.878161728442779</v>
       </c>
       <c r="BB9">
-        <v>1.02</v>
+        <v>1.021885173756878</v>
       </c>
       <c r="BC9">
-        <v>7.45</v>
+        <v>7.445671083211828</v>
       </c>
       <c r="BD9">
         <v>0</v>
@@ -2267,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="BF9">
-        <v>0.92</v>
+        <v>0.9207631564477893</v>
       </c>
     </row>
     <row r="10" spans="1:58">
@@ -2275,124 +2287,124 @@
         <v>66</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10">
-        <v>45.4</v>
+        <v>46.075</v>
       </c>
       <c r="D10">
-        <v>46.12</v>
+        <v>46.2</v>
       </c>
       <c r="E10">
-        <v>-0.73</v>
+        <v>-0.125</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I10">
-        <v>49.6</v>
+        <v>49.932267678136</v>
       </c>
       <c r="J10">
-        <v>50.4</v>
+        <v>50.06773232186399</v>
       </c>
       <c r="K10">
-        <v>-0.79</v>
+        <v>-0.1354646437279925</v>
       </c>
       <c r="L10">
-        <v>-1.77</v>
+        <v>-2.883221219172162</v>
       </c>
       <c r="M10">
-        <v>-2.56</v>
+        <v>-3.018685862900155</v>
       </c>
       <c r="N10">
-        <v>-2.56</v>
+        <v>-3.018685862900155</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P10">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q10">
-        <v>48.72</v>
+        <v>48.85105972094644</v>
       </c>
       <c r="R10">
-        <v>51.28</v>
+        <v>51.14894027905356</v>
       </c>
       <c r="S10">
-        <v>-1.77</v>
+        <v>-2.162415914379122</v>
       </c>
       <c r="T10">
-        <v>-2.56</v>
+        <v>-2.297880558107114</v>
       </c>
       <c r="U10">
-        <v>-2.56</v>
+        <v>-2.297880558107114</v>
       </c>
       <c r="V10">
-        <v>36.52</v>
+        <v>34.57168958828296</v>
       </c>
       <c r="W10">
-        <v>63.48</v>
+        <v>65.42831041171704</v>
       </c>
       <c r="X10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Z10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AA10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AB10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AC10">
-        <v>36.52</v>
+        <v>34.57168958828296</v>
       </c>
       <c r="AD10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AE10">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF10">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.248471410266716</v>
       </c>
       <c r="AL10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AM10">
         <v>-6</v>
       </c>
       <c r="AN10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="AO10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AP10">
         <v>0.5174</v>
@@ -2401,49 +2413,49 @@
         <v>-3.47999999999999</v>
       </c>
       <c r="AR10">
-        <v>3.435838333780036</v>
+        <v>3.702119441892886</v>
       </c>
       <c r="AS10">
-        <v>0.9158383337800258</v>
+        <v>1.182119441892876</v>
       </c>
       <c r="AT10">
-        <v>2.175838333780031</v>
+        <v>2.442119441892881</v>
       </c>
       <c r="AU10">
-        <v>0.5439595834450077</v>
+        <v>0.6105298604732202</v>
       </c>
       <c r="AV10">
-        <v>5.7</v>
+        <v>5.775280601260435</v>
       </c>
       <c r="AW10">
-        <v>6.77</v>
+        <v>5.150295879788892</v>
       </c>
       <c r="AX10">
-        <v>7.44</v>
+        <v>5.789423950509446</v>
       </c>
       <c r="AY10">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ10">
         <v>3</v>
       </c>
       <c r="BA10">
-        <v>2.19</v>
+        <v>2.193175026846863</v>
       </c>
       <c r="BB10">
-        <v>-2.89</v>
+        <v>-2.886112316484782</v>
       </c>
       <c r="BC10">
-        <v>6.84</v>
+        <v>6.837360120673064</v>
       </c>
       <c r="BD10">
-        <v>30.49</v>
+        <v>30.49114883433812</v>
       </c>
       <c r="BE10">
         <v>0</v>
       </c>
       <c r="BF10">
-        <v>0.95</v>
+        <v>0.9513390040572299</v>
       </c>
     </row>
     <row r="11" spans="1:58">
@@ -2451,124 +2463,124 @@
         <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C11">
-        <v>47.27</v>
+        <v>47.3</v>
       </c>
       <c r="D11">
-        <v>50.17</v>
+        <v>50.16666667000001</v>
       </c>
       <c r="E11">
-        <v>-2.9</v>
+        <v>-2.866666667</v>
       </c>
       <c r="F11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I11">
-        <v>48.51</v>
+        <v>48.52941176304619</v>
       </c>
       <c r="J11">
-        <v>51.49</v>
+        <v>51.47058823695382</v>
       </c>
       <c r="K11">
-        <v>-2.98</v>
+        <v>-2.941176473907625</v>
       </c>
       <c r="L11">
-        <v>1.78</v>
+        <v>0.5792673114617315</v>
       </c>
       <c r="M11">
-        <v>-1.2</v>
+        <v>-2.361909162445893</v>
       </c>
       <c r="N11">
-        <v>-1.2</v>
+        <v>-2.361909162445893</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P11">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q11">
-        <v>48.13</v>
+        <v>48.74663700484434</v>
       </c>
       <c r="R11">
-        <v>51.87</v>
+        <v>51.25336299515566</v>
       </c>
       <c r="S11">
-        <v>1.78</v>
+        <v>0.434450483596299</v>
       </c>
       <c r="T11">
-        <v>-1.2</v>
+        <v>-2.506725990311326</v>
       </c>
       <c r="U11">
-        <v>-3.74</v>
+        <v>-2.506725990311326</v>
       </c>
       <c r="V11">
-        <v>30.07</v>
+        <v>33.66396774649345</v>
       </c>
       <c r="W11">
-        <v>69.93000000000001</v>
+        <v>66.33603225350654</v>
       </c>
       <c r="X11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Z11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AA11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AB11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AC11">
-        <v>30.07</v>
+        <v>33.66396774649345</v>
       </c>
       <c r="AD11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AE11">
-        <v>7.86</v>
+        <v>8.73527450544567</v>
       </c>
       <c r="AF11">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>0.2508301036538862</v>
       </c>
       <c r="AL11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AM11">
         <v>-10</v>
       </c>
       <c r="AN11" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="AO11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AP11">
         <v>0.6258</v>
@@ -2577,40 +2589,40 @@
         <v>-25.16000000000001</v>
       </c>
       <c r="AR11">
-        <v>8.804477444369347</v>
+        <v>7.493274009688674</v>
       </c>
       <c r="AS11">
-        <v>23.96447744436936</v>
+        <v>22.65327400968869</v>
       </c>
       <c r="AT11">
-        <v>16.38447744436935</v>
+        <v>15.07327400968868</v>
       </c>
       <c r="AU11">
-        <v>4.096119361092338</v>
+        <v>3.76831850242217</v>
       </c>
       <c r="AV11">
-        <v>4.13</v>
+        <v>4.390437171606355</v>
       </c>
       <c r="AW11">
-        <v>6.47</v>
+        <v>5.324598663427484</v>
       </c>
       <c r="AX11">
-        <v>7.17</v>
+        <v>5.945017489960455</v>
       </c>
       <c r="AY11">
-        <v>1.11</v>
+        <v>0.8436468628413508</v>
       </c>
       <c r="AZ11">
         <v>3</v>
       </c>
       <c r="BA11">
-        <v>1.91</v>
+        <v>1.906296723190152</v>
       </c>
       <c r="BB11">
-        <v>-1.37</v>
+        <v>-1.372324784465838</v>
       </c>
       <c r="BC11">
-        <v>5.41</v>
+        <v>5.414780435479317</v>
       </c>
       <c r="BD11">
         <v>0</v>
@@ -2619,7 +2631,7 @@
         <v>0</v>
       </c>
       <c r="BF11">
-        <v>0.93</v>
+        <v>0.9325238981752073</v>
       </c>
     </row>
     <row r="12" spans="1:58">
@@ -2627,16 +2639,16 @@
         <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C12">
-        <v>27.05</v>
+        <v>45.875</v>
       </c>
       <c r="D12">
-        <v>44.9</v>
+        <v>49.675</v>
       </c>
       <c r="E12">
-        <v>-17.85</v>
+        <v>-3.8</v>
       </c>
       <c r="F12" t="s">
         <v>77</v>
@@ -2648,154 +2660,330 @@
         <v>85</v>
       </c>
       <c r="I12">
-        <v>37.6</v>
+        <v>48.01151229722657</v>
       </c>
       <c r="J12">
-        <v>62.4</v>
+        <v>51.98848770277341</v>
       </c>
       <c r="K12">
-        <v>-24.81</v>
+        <v>-3.976975405546838</v>
       </c>
       <c r="L12">
-        <v>-6.51</v>
+        <v>-0.2491280460552653</v>
       </c>
       <c r="M12">
-        <v>-31.32</v>
+        <v>-4.226103451602103</v>
       </c>
       <c r="N12">
-        <v>-31.32</v>
+        <v>-4.226103451602103</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P12">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q12">
-        <v>34.34</v>
+        <v>47.91808927995586</v>
       </c>
       <c r="R12">
-        <v>65.66</v>
+        <v>52.08191072004414</v>
       </c>
       <c r="S12">
-        <v>-6.51</v>
+        <v>-0.1868460345414489</v>
       </c>
       <c r="T12">
-        <v>-31.32</v>
+        <v>-4.163821440088287</v>
       </c>
       <c r="U12">
-        <v>-31.32</v>
+        <v>-4.163821440088287</v>
       </c>
       <c r="V12">
-        <v>0.1</v>
+        <v>21.63743754626992</v>
       </c>
       <c r="W12">
-        <v>99.90000000000001</v>
+        <v>78.36256245373008</v>
       </c>
       <c r="X12" t="s">
         <v>82</v>
       </c>
       <c r="Y12" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC12">
+        <v>21.63743754626992</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE12">
+        <v>8.73527450544567</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0.1078756083395196</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM12">
+        <v>-8</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>110</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>71</v>
+      </c>
+      <c r="AP12">
+        <v>0.5322</v>
+      </c>
+      <c r="AQ12">
+        <v>-6.439999999999998</v>
+      </c>
+      <c r="AR12">
+        <v>3.836178559911713</v>
+      </c>
+      <c r="AS12">
+        <v>2.276178559911711</v>
+      </c>
+      <c r="AT12">
+        <v>3.056178559911712</v>
+      </c>
+      <c r="AU12">
+        <v>0.7640446399779279</v>
+      </c>
+      <c r="AV12">
+        <v>5.314982794026658</v>
+      </c>
+      <c r="AW12">
+        <v>4.602075819872517</v>
+      </c>
+      <c r="AX12">
+        <v>5.307634490167654</v>
+      </c>
+      <c r="AY12">
+        <v>0.8436468628413508</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>-0.3706239798868902</v>
+      </c>
+      <c r="BC12">
+        <v>5.000892084631056</v>
+      </c>
+      <c r="BD12">
+        <v>17.64705882352941</v>
+      </c>
+      <c r="BE12">
+        <v>8.823529411764707</v>
+      </c>
+      <c r="BF12">
+        <v>0.9238036867710117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:58">
+      <c r="A13" t="s">
         <v>69</v>
       </c>
-      <c r="Z12" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC12">
+      <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13">
+        <v>17.175</v>
+      </c>
+      <c r="D13">
+        <v>44.8</v>
+      </c>
+      <c r="E13">
+        <v>-27.625</v>
+      </c>
+      <c r="F13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" t="s">
+        <v>86</v>
+      </c>
+      <c r="I13">
+        <v>27.71278741427995</v>
+      </c>
+      <c r="J13">
+        <v>72.28721258572004</v>
+      </c>
+      <c r="K13">
+        <v>-44.5744251714401</v>
+      </c>
+      <c r="L13">
+        <v>-9.884364997571231</v>
+      </c>
+      <c r="M13">
+        <v>-54.45879016901133</v>
+      </c>
+      <c r="N13">
+        <v>-54.45879016901133</v>
+      </c>
+      <c r="O13">
+        <v>0.25</v>
+      </c>
+      <c r="P13">
+        <v>0.75</v>
+      </c>
+      <c r="Q13">
+        <v>24.00615054019074</v>
+      </c>
+      <c r="R13">
+        <v>75.99384945980927</v>
+      </c>
+      <c r="S13">
+        <v>-7.413273748178426</v>
+      </c>
+      <c r="T13">
+        <v>-51.98769891961852</v>
+      </c>
+      <c r="U13">
+        <v>-51.98769891961852</v>
+      </c>
+      <c r="V13">
         <v>0.1</v>
       </c>
-      <c r="AD12" t="s">
-        <v>89</v>
-      </c>
-      <c r="AE12">
-        <v>7.86</v>
-      </c>
-      <c r="AF12">
-        <v>0.28</v>
-      </c>
-      <c r="AG12">
-        <v>3.24</v>
-      </c>
-      <c r="AH12">
-        <v>2.96</v>
-      </c>
-      <c r="AI12">
-        <v>3.51</v>
-      </c>
-      <c r="AJ12">
-        <v>3.24</v>
-      </c>
-      <c r="AK12">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM12">
+      <c r="W13">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="X13" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC13">
+        <v>0.1</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE13">
+        <v>8.73527450544567</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>4.280055594087199</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM13">
         <v>-10</v>
       </c>
-      <c r="AN12" t="s">
-        <v>107</v>
-      </c>
-      <c r="AO12" t="s">
-        <v>69</v>
-      </c>
-      <c r="AP12">
+      <c r="AN13" t="s">
+        <v>111</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>71</v>
+      </c>
+      <c r="AP13">
         <v>0.5501</v>
       </c>
-      <c r="AQ12">
+      <c r="AQ13">
         <v>-10.02000000000001</v>
       </c>
-      <c r="AR12">
-        <v>21.32320758340596</v>
-      </c>
-      <c r="AS12">
-        <v>21.30320758340595</v>
-      </c>
-      <c r="AT12">
-        <v>21.31320758340595</v>
-      </c>
-      <c r="AU12">
-        <v>5.328301895851488</v>
-      </c>
-      <c r="AV12">
-        <v>4.43</v>
-      </c>
-      <c r="AW12">
-        <v>7.92</v>
-      </c>
-      <c r="AX12">
-        <v>8.5</v>
-      </c>
-      <c r="AY12">
-        <v>1.11</v>
-      </c>
-      <c r="AZ12">
+      <c r="AR13">
+        <v>41.98769891961852</v>
+      </c>
+      <c r="AS13">
+        <v>41.96769891961851</v>
+      </c>
+      <c r="AT13">
+        <v>41.97769891961852</v>
+      </c>
+      <c r="AU13">
+        <v>6</v>
+      </c>
+      <c r="AV13">
+        <v>4.808765205332268</v>
+      </c>
+      <c r="AW13">
+        <v>8.329220566311957</v>
+      </c>
+      <c r="AX13">
+        <v>8.738867047371532</v>
+      </c>
+      <c r="AY13">
+        <v>0.8436468628413508</v>
+      </c>
+      <c r="AZ13">
         <v>3</v>
       </c>
-      <c r="BA12">
-        <v>1.94</v>
-      </c>
-      <c r="BB12">
-        <v>0.1</v>
-      </c>
-      <c r="BC12">
-        <v>1.96</v>
-      </c>
-      <c r="BD12">
-        <v>58.22</v>
-      </c>
-      <c r="BE12">
-        <v>0</v>
-      </c>
-      <c r="BF12">
-        <v>0.95</v>
+      <c r="BA13">
+        <v>1.939183370917788</v>
+      </c>
+      <c r="BB13">
+        <v>0.1011860990595696</v>
+      </c>
+      <c r="BC13">
+        <v>1.960814204790223</v>
+      </c>
+      <c r="BD13">
+        <v>58.22371654759336</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0.9487813321503221</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block5B_Senate_Race_Attribution.xlsx
+++ b/outputs/Block5B_Senate_Race_Attribution.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="113">
   <si>
     <t>STATE</t>
   </si>
@@ -277,7 +277,10 @@
     <t>Safe</t>
   </si>
   <si>
-    <t>D Safe</t>
+    <t>D Tilt</t>
+  </si>
+  <si>
+    <t>R Tilt</t>
   </si>
   <si>
     <t>Democratic Hold</t>
@@ -957,25 +960,25 @@
         <v>2.841949760700191</v>
       </c>
       <c r="X2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="Y2" t="s">
         <v>70</v>
       </c>
       <c r="Z2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA2" t="s">
         <v>70</v>
       </c>
       <c r="AB2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AC2">
         <v>2.841949760700191</v>
       </c>
       <c r="AD2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE2">
         <v>8.73527450544567</v>
@@ -999,13 +1002,13 @@
         <v>1.844443629792535</v>
       </c>
       <c r="AL2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AM2">
         <v>-1</v>
       </c>
       <c r="AN2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AO2" t="s">
         <v>70</v>
@@ -1139,19 +1142,19 @@
         <v>70</v>
       </c>
       <c r="Z3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA3" t="s">
         <v>70</v>
       </c>
       <c r="AB3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AC3">
         <v>5.154907658335239</v>
       </c>
       <c r="AD3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE3">
         <v>8.73527450544567</v>
@@ -1175,13 +1178,13 @@
         <v>0.909952316559551</v>
       </c>
       <c r="AL3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AM3">
         <v>2</v>
       </c>
       <c r="AN3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO3" t="s">
         <v>70</v>
@@ -1315,19 +1318,19 @@
         <v>70</v>
       </c>
       <c r="Z4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA4" t="s">
         <v>70</v>
       </c>
       <c r="AB4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AC4">
         <v>93.22560446351913</v>
       </c>
       <c r="AD4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE4">
         <v>8.73527450544567</v>
@@ -1351,13 +1354,13 @@
         <v>0.5722172308539429</v>
       </c>
       <c r="AL4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AM4">
         <v>-1</v>
       </c>
       <c r="AN4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AO4" t="s">
         <v>71</v>
@@ -1485,25 +1488,25 @@
         <v>16.27078448956417</v>
       </c>
       <c r="X5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y5" t="s">
         <v>70</v>
       </c>
       <c r="Z5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA5" t="s">
         <v>70</v>
       </c>
       <c r="AB5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AC5">
         <v>16.27078448956417</v>
       </c>
       <c r="AD5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE5">
         <v>8.73527450544567</v>
@@ -1527,13 +1530,13 @@
         <v>0.9609781569420333</v>
       </c>
       <c r="AL5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AM5">
         <v>0</v>
       </c>
       <c r="AN5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO5" t="s">
         <v>70</v>
@@ -1661,25 +1664,25 @@
         <v>32.91691512929713</v>
       </c>
       <c r="X6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="Y6" t="s">
         <v>70</v>
       </c>
       <c r="Z6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA6" t="s">
         <v>70</v>
       </c>
       <c r="AB6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AC6">
         <v>67.08308487070286</v>
       </c>
       <c r="AD6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE6">
         <v>8.73527450544567</v>
@@ -1703,13 +1706,13 @@
         <v>0.549123227957043</v>
       </c>
       <c r="AL6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AM6">
         <v>-6</v>
       </c>
       <c r="AN6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AO6" t="s">
         <v>71</v>
@@ -1837,25 +1840,25 @@
         <v>34.73611300489836</v>
       </c>
       <c r="X7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="Y7" t="s">
         <v>70</v>
       </c>
       <c r="Z7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA7" t="s">
         <v>70</v>
       </c>
       <c r="AB7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AC7">
         <v>65.26388699510164</v>
       </c>
       <c r="AD7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE7">
         <v>8.73527450544567</v>
@@ -1879,13 +1882,13 @@
         <v>0.7771977269041618</v>
       </c>
       <c r="AL7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AM7">
         <v>-5</v>
       </c>
       <c r="AN7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AR7">
         <v>7.002367309587463</v>
@@ -2001,25 +2004,25 @@
         <v>38.20985096968496</v>
       </c>
       <c r="X8" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="Y8" t="s">
         <v>70</v>
       </c>
       <c r="Z8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA8" t="s">
         <v>70</v>
       </c>
       <c r="AB8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AC8">
         <v>61.79014903031504</v>
       </c>
       <c r="AD8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE8">
         <v>8.73527450544567</v>
@@ -2043,13 +2046,13 @@
         <v>0.05075879739090176</v>
       </c>
       <c r="AL8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AM8">
         <v>-6</v>
       </c>
       <c r="AN8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AO8" t="s">
         <v>71</v>
@@ -2183,19 +2186,19 @@
         <v>70</v>
       </c>
       <c r="Z9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA9" t="s">
         <v>70</v>
       </c>
       <c r="AB9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AC9">
         <v>55.65418073718285</v>
       </c>
       <c r="AD9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE9">
         <v>8.73527450544567</v>
@@ -2219,13 +2222,13 @@
         <v>0.530870777381373</v>
       </c>
       <c r="AL9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AM9">
         <v>4</v>
       </c>
       <c r="AN9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO9" t="s">
         <v>71</v>
@@ -2353,25 +2356,25 @@
         <v>65.42831041171704</v>
       </c>
       <c r="X10" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="Y10" t="s">
         <v>71</v>
       </c>
       <c r="Z10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AA10" t="s">
         <v>71</v>
       </c>
       <c r="AB10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AC10">
         <v>34.57168958828296</v>
       </c>
       <c r="AD10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE10">
         <v>8.73527450544567</v>
@@ -2395,13 +2398,13 @@
         <v>1.248471410266716</v>
       </c>
       <c r="AL10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AM10">
         <v>-6</v>
       </c>
       <c r="AN10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO10" t="s">
         <v>71</v>
@@ -2529,25 +2532,25 @@
         <v>66.33603225350654</v>
       </c>
       <c r="X11" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="Y11" t="s">
         <v>71</v>
       </c>
       <c r="Z11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AA11" t="s">
         <v>71</v>
       </c>
       <c r="AB11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AC11">
         <v>33.66396774649345</v>
       </c>
       <c r="AD11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE11">
         <v>8.73527450544567</v>
@@ -2571,13 +2574,13 @@
         <v>0.2508301036538862</v>
       </c>
       <c r="AL11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AM11">
         <v>-10</v>
       </c>
       <c r="AN11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AO11" t="s">
         <v>71</v>
@@ -2711,19 +2714,19 @@
         <v>71</v>
       </c>
       <c r="Z12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AA12" t="s">
         <v>71</v>
       </c>
       <c r="AB12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AC12">
         <v>21.63743754626992</v>
       </c>
       <c r="AD12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE12">
         <v>8.73527450544567</v>
@@ -2747,13 +2750,13 @@
         <v>0.1078756083395196</v>
       </c>
       <c r="AL12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AM12">
         <v>-8</v>
       </c>
       <c r="AN12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO12" t="s">
         <v>71</v>
@@ -2887,19 +2890,19 @@
         <v>71</v>
       </c>
       <c r="Z13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AA13" t="s">
         <v>71</v>
       </c>
       <c r="AB13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AC13">
         <v>0.1</v>
       </c>
       <c r="AD13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE13">
         <v>8.73527450544567</v>
@@ -2923,13 +2926,13 @@
         <v>4.280055594087199</v>
       </c>
       <c r="AL13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AM13">
         <v>-10</v>
       </c>
       <c r="AN13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AO13" t="s">
         <v>71</v>

--- a/outputs/Block5B_Senate_Race_Attribution.xlsx
+++ b/outputs/Block5B_Senate_Race_Attribution.xlsx
@@ -202,27 +202,27 @@
     <t>Michigan</t>
   </si>
   <si>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
     <t>Texas</t>
   </si>
   <si>
-    <t>Ohio</t>
-  </si>
-  <si>
-    <t>Alaska</t>
-  </si>
-  <si>
     <t>Maine</t>
   </si>
   <si>
     <t>Iowa</t>
   </si>
   <si>
+    <t>Kansas</t>
+  </si>
+  <si>
     <t>Nebraska</t>
   </si>
   <si>
-    <t>Kansas</t>
-  </si>
-  <si>
     <t>Montana</t>
   </si>
   <si>
@@ -313,12 +313,12 @@
     <t>D+4</t>
   </si>
   <si>
+    <t>R+8</t>
+  </si>
+  <si>
     <t>R+10</t>
   </si>
   <si>
-    <t>R+8</t>
-  </si>
-  <si>
     <t>50.62% D</t>
   </si>
   <si>
@@ -331,25 +331,25 @@
     <t>49.90% D</t>
   </si>
   <si>
+    <t>53.90% R</t>
+  </si>
+  <si>
+    <t>Appointed (2025)[p]</t>
+  </si>
+  <si>
     <t>53.51% R</t>
   </si>
   <si>
-    <t>Appointed (2025)[p]</t>
-  </si>
-  <si>
-    <t>53.90% R</t>
-  </si>
-  <si>
     <t>50.98% R</t>
   </si>
   <si>
     <t>51.74% R</t>
   </si>
   <si>
+    <t>53.22% R</t>
+  </si>
+  <si>
     <t>62.58% R (2024 sp.)[o]</t>
-  </si>
-  <si>
-    <t>53.22% R</t>
   </si>
   <si>
     <t>55.01% R</t>
@@ -897,13 +897,13 @@
         <v>70</v>
       </c>
       <c r="C2">
-        <v>51.87500000000001</v>
+        <v>51.9</v>
       </c>
       <c r="D2">
-        <v>43.4</v>
+        <v>43.375</v>
       </c>
       <c r="E2">
-        <v>8.475000000000001</v>
+        <v>8.525</v>
       </c>
       <c r="F2" t="s">
         <v>72</v>
@@ -915,22 +915,22 @@
         <v>84</v>
       </c>
       <c r="I2">
-        <v>54.44765153503018</v>
+        <v>54.47389136709525</v>
       </c>
       <c r="J2">
-        <v>45.55234846496982</v>
+        <v>45.52610863290474</v>
       </c>
       <c r="K2">
-        <v>8.895303070060358</v>
+        <v>8.947782734190504</v>
       </c>
       <c r="L2">
-        <v>4.259560104663242</v>
+        <v>4.265768337051614</v>
       </c>
       <c r="M2">
-        <v>13.1548631747236</v>
+        <v>13.21355107124212</v>
       </c>
       <c r="N2">
-        <v>13.1548631747236</v>
+        <v>13.21355107124212</v>
       </c>
       <c r="O2">
         <v>0.25</v>
@@ -939,25 +939,25 @@
         <v>0.75</v>
       </c>
       <c r="Q2">
-        <v>56.04498657427889</v>
+        <v>56.07355449348961</v>
       </c>
       <c r="R2">
-        <v>43.95501342572111</v>
+        <v>43.92644550651039</v>
       </c>
       <c r="S2">
-        <v>3.194670078497431</v>
+        <v>3.19932625278871</v>
       </c>
       <c r="T2">
-        <v>12.08997314855779</v>
+        <v>12.14710898697921</v>
       </c>
       <c r="U2">
-        <v>12.08997314855779</v>
+        <v>12.14710898697921</v>
       </c>
       <c r="V2">
-        <v>97.15805023929981</v>
+        <v>97.20159014526948</v>
       </c>
       <c r="W2">
-        <v>2.841949760700191</v>
+        <v>2.798409854730521</v>
       </c>
       <c r="X2" t="s">
         <v>79</v>
@@ -975,13 +975,13 @@
         <v>89</v>
       </c>
       <c r="AC2">
-        <v>2.841949760700191</v>
+        <v>2.798409854730521</v>
       </c>
       <c r="AD2" t="s">
         <v>92</v>
       </c>
       <c r="AE2">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -999,7 +999,7 @@
         <v>-0</v>
       </c>
       <c r="AK2">
-        <v>1.844443629792535</v>
+        <v>1.847131873272999</v>
       </c>
       <c r="AL2" t="s">
         <v>93</v>
@@ -1020,25 +1020,25 @@
         <v>1.239999999999995</v>
       </c>
       <c r="AR2">
-        <v>13.08997314855779</v>
+        <v>13.14710898697921</v>
       </c>
       <c r="AS2">
-        <v>10.84997314855779</v>
+        <v>10.90710898697922</v>
       </c>
       <c r="AT2">
-        <v>11.96997314855779</v>
+        <v>12.02710898697922</v>
       </c>
       <c r="AU2">
-        <v>2.992493287139448</v>
+        <v>3.006777246744804</v>
       </c>
       <c r="AV2">
         <v>5.482188815058572</v>
       </c>
       <c r="AW2">
-        <v>5.771015368998557</v>
+        <v>5.779286853475976</v>
       </c>
       <c r="AX2">
-        <v>6.34795245875231</v>
+        <v>6.355473118826183</v>
       </c>
       <c r="AY2">
         <v>0.8436468628413508</v>
@@ -1073,13 +1073,13 @@
         <v>70</v>
       </c>
       <c r="C3">
-        <v>49.2</v>
+        <v>49.375</v>
       </c>
       <c r="D3">
-        <v>42.675</v>
+        <v>42.475</v>
       </c>
       <c r="E3">
-        <v>6.525</v>
+        <v>6.9</v>
       </c>
       <c r="F3" t="s">
         <v>72</v>
@@ -1091,22 +1091,22 @@
         <v>84</v>
       </c>
       <c r="I3">
-        <v>53.55102040816327</v>
+        <v>53.75612411540556</v>
       </c>
       <c r="J3">
-        <v>46.44897959183673</v>
+        <v>46.24387588459445</v>
       </c>
       <c r="K3">
-        <v>7.102040816326536</v>
+        <v>7.512248230811103</v>
       </c>
       <c r="L3">
-        <v>2.101444859661521</v>
+        <v>2.15168128687088</v>
       </c>
       <c r="M3">
-        <v>9.203485675988057</v>
+        <v>9.663929517681982</v>
       </c>
       <c r="N3">
-        <v>9.203485675988057</v>
+        <v>9.663929517681982</v>
       </c>
       <c r="O3">
         <v>0.25</v>
@@ -1115,25 +1115,25 @@
         <v>0.75</v>
       </c>
       <c r="Q3">
-        <v>54.33906223053634</v>
+        <v>54.56300459798213</v>
       </c>
       <c r="R3">
-        <v>45.66093776946366</v>
+        <v>45.43699540201787</v>
       </c>
       <c r="S3">
-        <v>1.576083644746141</v>
+        <v>1.613760965153158</v>
       </c>
       <c r="T3">
-        <v>8.678124461072677</v>
+        <v>9.126009195964262</v>
       </c>
       <c r="U3">
-        <v>8.678124461072677</v>
+        <v>9.126009195964262</v>
       </c>
       <c r="V3">
-        <v>94.84509234166477</v>
+        <v>95.66726197064992</v>
       </c>
       <c r="W3">
-        <v>5.154907658335239</v>
+        <v>4.332738029350081</v>
       </c>
       <c r="X3" t="s">
         <v>79</v>
@@ -1151,13 +1151,13 @@
         <v>89</v>
       </c>
       <c r="AC3">
-        <v>5.154907658335239</v>
+        <v>4.332738029350081</v>
       </c>
       <c r="AD3" t="s">
         <v>92</v>
       </c>
       <c r="AE3">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -1175,7 +1175,7 @@
         <v>-0</v>
       </c>
       <c r="AK3">
-        <v>0.909952316559551</v>
+        <v>0.9317053276388867</v>
       </c>
       <c r="AL3" t="s">
         <v>94</v>
@@ -1196,10 +1196,10 @@
         <v>13.28</v>
       </c>
       <c r="AR3">
-        <v>6.678124461072677</v>
+        <v>7.126009195964262</v>
       </c>
       <c r="AS3">
-        <v>4.601875538927324</v>
+        <v>4.15399080403574</v>
       </c>
       <c r="AT3">
         <v>5.640000000000001</v>
@@ -1211,10 +1211,10 @@
         <v>5.112371008372736</v>
       </c>
       <c r="AW3">
-        <v>4.620884424478711</v>
+        <v>4.623848774507894</v>
       </c>
       <c r="AX3">
-        <v>5.323951060420438</v>
+        <v>5.326524149844822</v>
       </c>
       <c r="AY3">
         <v>0.8436468628413508</v>
@@ -1249,13 +1249,13 @@
         <v>71</v>
       </c>
       <c r="C4">
-        <v>50.34999999999999</v>
+        <v>50.675</v>
       </c>
       <c r="D4">
-        <v>42.25</v>
+        <v>41.45</v>
       </c>
       <c r="E4">
-        <v>8.1</v>
+        <v>9.225</v>
       </c>
       <c r="F4" t="s">
         <v>73</v>
@@ -1267,22 +1267,22 @@
         <v>84</v>
       </c>
       <c r="I4">
-        <v>54.37365010799135</v>
+        <v>55.0067842605156</v>
       </c>
       <c r="J4">
-        <v>45.62634989200864</v>
+        <v>44.9932157394844</v>
       </c>
       <c r="K4">
-        <v>8.747300215982712</v>
+        <v>10.0135685210312</v>
       </c>
       <c r="L4">
-        <v>-1.321479089073864</v>
+        <v>-1.380307966940977</v>
       </c>
       <c r="M4">
-        <v>7.425821126908847</v>
+        <v>8.633260554090226</v>
       </c>
       <c r="N4">
-        <v>7.425821126908847</v>
+        <v>8.633260554090226</v>
       </c>
       <c r="O4">
         <v>0.25</v>
@@ -1291,25 +1291,25 @@
         <v>0.75</v>
       </c>
       <c r="Q4">
-        <v>53.87809544958866</v>
+        <v>54.48916877291273</v>
       </c>
       <c r="R4">
-        <v>46.12190455041134</v>
+        <v>45.51083122708727</v>
       </c>
       <c r="S4">
-        <v>-0.9911093168053986</v>
+        <v>-1.035230975205733</v>
       </c>
       <c r="T4">
-        <v>7.756190899177313</v>
+        <v>8.97833754582547</v>
       </c>
       <c r="U4">
-        <v>7.756190899177313</v>
+        <v>8.97833754582547</v>
       </c>
       <c r="V4">
-        <v>93.22560446351913</v>
+        <v>95.47518279599674</v>
       </c>
       <c r="W4">
-        <v>6.774395536480871</v>
+        <v>4.52481720400325</v>
       </c>
       <c r="X4" t="s">
         <v>79</v>
@@ -1327,13 +1327,13 @@
         <v>90</v>
       </c>
       <c r="AC4">
-        <v>93.22560446351913</v>
+        <v>95.47518279599674</v>
       </c>
       <c r="AD4" t="s">
         <v>92</v>
       </c>
       <c r="AE4">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF4">
         <v>0</v>
@@ -1351,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>0.5722172308539429</v>
+        <v>0.5976908822084687</v>
       </c>
       <c r="AL4" t="s">
         <v>93</v>
@@ -1372,25 +1372,25 @@
         <v>2.620000000000005</v>
       </c>
       <c r="AR4">
-        <v>8.756190899177312</v>
+        <v>9.97833754582547</v>
       </c>
       <c r="AS4">
-        <v>5.136190899177309</v>
+        <v>6.358337545825465</v>
       </c>
       <c r="AT4">
-        <v>6.94619089917731</v>
+        <v>8.168337545825468</v>
       </c>
       <c r="AU4">
-        <v>1.736547724794328</v>
+        <v>2.042084386456367</v>
       </c>
       <c r="AV4">
         <v>4.808352845952818</v>
       </c>
       <c r="AW4">
-        <v>4.472531501293391</v>
+        <v>4.597750331251065</v>
       </c>
       <c r="AX4">
-        <v>5.195711699028696</v>
+        <v>5.303884438586613</v>
       </c>
       <c r="AY4">
         <v>0.8436468628413508</v>
@@ -1425,13 +1425,13 @@
         <v>70</v>
       </c>
       <c r="C5">
-        <v>48.175</v>
+        <v>48.825</v>
       </c>
       <c r="D5">
-        <v>45</v>
+        <v>45.275</v>
       </c>
       <c r="E5">
-        <v>3.175</v>
+        <v>3.55</v>
       </c>
       <c r="F5" t="s">
         <v>74</v>
@@ -1443,22 +1443,22 @@
         <v>85</v>
       </c>
       <c r="I5">
-        <v>51.70378320364904</v>
+        <v>51.88629117959618</v>
       </c>
       <c r="J5">
-        <v>48.29621679635095</v>
+        <v>48.11370882040383</v>
       </c>
       <c r="K5">
-        <v>3.407566407298091</v>
+        <v>3.772582359192349</v>
       </c>
       <c r="L5">
-        <v>2.219283990383333</v>
+        <v>2.784312428859241</v>
       </c>
       <c r="M5">
-        <v>5.626850397681425</v>
+        <v>6.55689478805159</v>
       </c>
       <c r="N5">
-        <v>5.626850397681425</v>
+        <v>6.55689478805159</v>
       </c>
       <c r="O5">
         <v>0.25</v>
@@ -1467,25 +1467,25 @@
         <v>0.75</v>
       </c>
       <c r="Q5">
-        <v>52.5360147000428</v>
+        <v>52.93040834041839</v>
       </c>
       <c r="R5">
-        <v>47.4639852999572</v>
+        <v>47.06959165958161</v>
       </c>
       <c r="S5">
-        <v>1.664462992787501</v>
+        <v>2.088234321644431</v>
       </c>
       <c r="T5">
-        <v>5.072029400085592</v>
+        <v>5.86081668083678</v>
       </c>
       <c r="U5">
-        <v>5.072029400085592</v>
+        <v>5.86081668083678</v>
       </c>
       <c r="V5">
-        <v>83.72921551043582</v>
+        <v>86.78566705347262</v>
       </c>
       <c r="W5">
-        <v>16.27078448956417</v>
+        <v>13.21433294652739</v>
       </c>
       <c r="X5" t="s">
         <v>80</v>
@@ -1503,13 +1503,13 @@
         <v>89</v>
       </c>
       <c r="AC5">
-        <v>16.27078448956417</v>
+        <v>13.21433294652739</v>
       </c>
       <c r="AD5" t="s">
         <v>92</v>
       </c>
       <c r="AE5">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>-0</v>
       </c>
       <c r="AK5">
-        <v>0.9609781569420333</v>
+        <v>1.205642647732428</v>
       </c>
       <c r="AL5" t="s">
         <v>95</v>
@@ -1548,25 +1548,25 @@
         <v>-0.2000000000000028</v>
       </c>
       <c r="AR5">
-        <v>5.072029400085592</v>
+        <v>5.86081668083678</v>
       </c>
       <c r="AS5">
-        <v>5.272029400085595</v>
+        <v>6.060816680836782</v>
       </c>
       <c r="AT5">
-        <v>5.172029400085593</v>
+        <v>5.960816680836781</v>
       </c>
       <c r="AU5">
-        <v>1.293007350021398</v>
+        <v>1.490204170209195</v>
       </c>
       <c r="AV5">
         <v>4.890566271054463</v>
       </c>
       <c r="AW5">
-        <v>4.428317085264829</v>
+        <v>4.535644811700211</v>
       </c>
       <c r="AX5">
-        <v>5.157700479575209</v>
+        <v>5.250138654099052</v>
       </c>
       <c r="AY5">
         <v>0.8436468628413508</v>
@@ -1601,13 +1601,13 @@
         <v>71</v>
       </c>
       <c r="C6">
-        <v>48.675</v>
+        <v>50.55</v>
       </c>
       <c r="D6">
-        <v>45.65</v>
+        <v>48.25</v>
       </c>
       <c r="E6">
-        <v>3.025</v>
+        <v>2.3</v>
       </c>
       <c r="F6" t="s">
         <v>75</v>
@@ -1619,22 +1619,22 @@
         <v>85</v>
       </c>
       <c r="I6">
-        <v>51.60349854227405</v>
+        <v>51.16396761133603</v>
       </c>
       <c r="J6">
-        <v>48.39650145772595</v>
+        <v>48.83603238866397</v>
       </c>
       <c r="K6">
-        <v>3.206997084548107</v>
+        <v>2.327935222672068</v>
       </c>
       <c r="L6">
-        <v>-1.2681457739171</v>
+        <v>1.046950541341876</v>
       </c>
       <c r="M6">
-        <v>1.938851310631006</v>
+        <v>3.374885764013944</v>
       </c>
       <c r="N6">
-        <v>1.938851310631006</v>
+        <v>3.374885764013944</v>
       </c>
       <c r="O6">
         <v>0.25</v>
@@ -1643,28 +1643,28 @@
         <v>0.75</v>
       </c>
       <c r="Q6">
-        <v>51.12794387705514</v>
+        <v>51.55657406433924</v>
       </c>
       <c r="R6">
-        <v>48.87205612294486</v>
+        <v>48.44342593566076</v>
       </c>
       <c r="S6">
-        <v>-0.9511093304378253</v>
+        <v>0.7852129060064073</v>
       </c>
       <c r="T6">
-        <v>2.255887754110281</v>
+        <v>3.113148128678475</v>
       </c>
       <c r="U6">
-        <v>2.255887754110281</v>
+        <v>3.113148128678475</v>
       </c>
       <c r="V6">
-        <v>67.08308487070286</v>
+        <v>69.21939506969498</v>
       </c>
       <c r="W6">
-        <v>32.91691512929713</v>
+        <v>30.78060493030502</v>
       </c>
       <c r="X6" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="Y6" t="s">
         <v>70</v>
@@ -1679,13 +1679,13 @@
         <v>90</v>
       </c>
       <c r="AC6">
-        <v>67.08308487070286</v>
+        <v>69.21939506969498</v>
       </c>
       <c r="AD6" t="s">
         <v>92</v>
       </c>
       <c r="AE6">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="AK6">
-        <v>0.549123227957043</v>
+        <v>0.4533428826539674</v>
       </c>
       <c r="AL6" t="s">
         <v>96</v>
@@ -1718,31 +1718,31 @@
         <v>71</v>
       </c>
       <c r="AP6">
-        <v>0.5351</v>
+        <v>0.539</v>
       </c>
       <c r="AQ6">
-        <v>-7.02000000000001</v>
+        <v>-7.800000000000011</v>
       </c>
       <c r="AR6">
-        <v>8.255887754110281</v>
+        <v>9.113148128678475</v>
       </c>
       <c r="AS6">
-        <v>9.275887754110292</v>
+        <v>10.91314812867849</v>
       </c>
       <c r="AT6">
-        <v>8.765887754110286</v>
+        <v>10.01314812867848</v>
       </c>
       <c r="AU6">
-        <v>2.191471938527572</v>
+        <v>2.50328703216962</v>
       </c>
       <c r="AV6">
-        <v>4.345503062353619</v>
+        <v>5.898436507750732</v>
       </c>
       <c r="AW6">
-        <v>4.362627316035638</v>
+        <v>5.60843385395642</v>
       </c>
       <c r="AX6">
-        <v>5.101411483891715</v>
+        <v>6.200517101304247</v>
       </c>
       <c r="AY6">
         <v>0.8436468628413508</v>
@@ -1751,22 +1751,22 @@
         <v>3</v>
       </c>
       <c r="BA6">
-        <v>1.930645252303767</v>
+        <v>1.541161542643699</v>
       </c>
       <c r="BB6">
-        <v>1.354753062157686</v>
+        <v>-4.006524474852094</v>
       </c>
       <c r="BC6">
-        <v>5.754964092348529</v>
+        <v>11.41694912221213</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>42.06393827345702</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>23.63541255450272</v>
       </c>
       <c r="BF6">
-        <v>0.9442145399410329</v>
+        <v>0.6873186760847522</v>
       </c>
     </row>
     <row r="7" spans="1:58">
@@ -1777,13 +1777,13 @@
         <v>71</v>
       </c>
       <c r="C7">
-        <v>48.225</v>
+        <v>47.8</v>
       </c>
       <c r="D7">
-        <v>45.1</v>
+        <v>43.7</v>
       </c>
       <c r="E7">
-        <v>3.125</v>
+        <v>4.100000000000001</v>
       </c>
       <c r="F7" t="s">
         <v>75</v>
@@ -1795,22 +1795,22 @@
         <v>85</v>
       </c>
       <c r="I7">
-        <v>51.67425663005626</v>
+        <v>52.24043715846994</v>
       </c>
       <c r="J7">
-        <v>48.32574336994374</v>
+        <v>47.75956284153006</v>
       </c>
       <c r="K7">
-        <v>3.348513260112512</v>
+        <v>4.480874316939889</v>
       </c>
       <c r="L7">
-        <v>-1.794861267366732</v>
+        <v>-2.617231028609809</v>
       </c>
       <c r="M7">
-        <v>1.553651992745779</v>
+        <v>1.86364328833008</v>
       </c>
       <c r="N7">
-        <v>1.553651992745779</v>
+        <v>1.86364328833008</v>
       </c>
       <c r="O7">
         <v>0.25</v>
@@ -1819,25 +1819,25 @@
         <v>0.75</v>
       </c>
       <c r="Q7">
-        <v>51.00118365479373</v>
+        <v>51.25897552274127</v>
       </c>
       <c r="R7">
-        <v>48.99881634520627</v>
+        <v>48.74102447725873</v>
       </c>
       <c r="S7">
-        <v>-1.346145950525049</v>
+        <v>-1.962923271457357</v>
       </c>
       <c r="T7">
-        <v>2.002367309587462</v>
+        <v>2.517951045482532</v>
       </c>
       <c r="U7">
-        <v>2.002367309587462</v>
+        <v>2.517951045482532</v>
       </c>
       <c r="V7">
-        <v>65.26388699510164</v>
+        <v>68.55458229868631</v>
       </c>
       <c r="W7">
-        <v>34.73611300489836</v>
+        <v>31.44541770131368</v>
       </c>
       <c r="X7" t="s">
         <v>87</v>
@@ -1855,13 +1855,13 @@
         <v>90</v>
       </c>
       <c r="AC7">
-        <v>65.26388699510164</v>
+        <v>68.55458229868631</v>
       </c>
       <c r="AD7" t="s">
         <v>92</v>
       </c>
       <c r="AE7">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF7">
         <v>0</v>
@@ -1879,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="AK7">
-        <v>0.7771977269041618</v>
+        <v>1.133294279174486</v>
       </c>
       <c r="AL7" t="s">
         <v>97</v>
@@ -1891,22 +1891,22 @@
         <v>106</v>
       </c>
       <c r="AR7">
-        <v>7.002367309587463</v>
+        <v>7.517951045482532</v>
       </c>
       <c r="AT7">
-        <v>7.002367309587463</v>
+        <v>7.517951045482532</v>
       </c>
       <c r="AU7">
-        <v>1.750591827396866</v>
+        <v>1.879487761370633</v>
       </c>
       <c r="AV7">
         <v>4.567515257270437</v>
       </c>
       <c r="AW7">
-        <v>4.363504132448985</v>
+        <v>4.489472846184185</v>
       </c>
       <c r="AX7">
-        <v>5.102161340379323</v>
+        <v>5.210302147283503</v>
       </c>
       <c r="AY7">
         <v>0.8436468628413508</v>
@@ -1941,13 +1941,13 @@
         <v>71</v>
       </c>
       <c r="C8">
-        <v>49.325</v>
+        <v>48.675</v>
       </c>
       <c r="D8">
-        <v>47.475</v>
+        <v>46.1</v>
       </c>
       <c r="E8">
-        <v>1.85</v>
+        <v>2.575</v>
       </c>
       <c r="F8" t="s">
         <v>75</v>
@@ -1959,22 +1959,22 @@
         <v>85</v>
       </c>
       <c r="I8">
-        <v>50.95557851239669</v>
+        <v>51.35848061197573</v>
       </c>
       <c r="J8">
-        <v>49.0444214876033</v>
+        <v>48.64151938802426</v>
       </c>
       <c r="K8">
-        <v>1.91115702479339</v>
+        <v>2.716961223951465</v>
       </c>
       <c r="L8">
-        <v>-0.1172224213495152</v>
+        <v>-1.102239597745279</v>
       </c>
       <c r="M8">
-        <v>1.793934603443875</v>
+        <v>1.614721626206186</v>
       </c>
       <c r="N8">
-        <v>1.793934603443875</v>
+        <v>1.614721626206186</v>
       </c>
       <c r="O8">
         <v>0.25</v>
@@ -1983,25 +1983,25 @@
         <v>0.75</v>
       </c>
       <c r="Q8">
-        <v>50.91162010439063</v>
+        <v>50.94514076282125</v>
       </c>
       <c r="R8">
-        <v>49.08837989560937</v>
+        <v>49.05485923717875</v>
       </c>
       <c r="S8">
-        <v>-0.08791681601213641</v>
+        <v>-0.8266796983089593</v>
       </c>
       <c r="T8">
-        <v>1.823240208781253</v>
+        <v>1.890281525642506</v>
       </c>
       <c r="U8">
-        <v>1.823240208781253</v>
+        <v>1.890281525642506</v>
       </c>
       <c r="V8">
-        <v>61.79014903031504</v>
+        <v>64.5725196739622</v>
       </c>
       <c r="W8">
-        <v>38.20985096968496</v>
+        <v>35.4274803260378</v>
       </c>
       <c r="X8" t="s">
         <v>87</v>
@@ -2019,13 +2019,13 @@
         <v>90</v>
       </c>
       <c r="AC8">
-        <v>61.79014903031504</v>
+        <v>64.5725196739622</v>
       </c>
       <c r="AD8" t="s">
         <v>92</v>
       </c>
       <c r="AE8">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF8">
         <v>0</v>
@@ -2043,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="AK8">
-        <v>0.05075879739090176</v>
+        <v>0.4772837463522762</v>
       </c>
       <c r="AL8" t="s">
         <v>96</v>
@@ -2058,31 +2058,31 @@
         <v>71</v>
       </c>
       <c r="AP8">
-        <v>0.539</v>
+        <v>0.5351</v>
       </c>
       <c r="AQ8">
-        <v>-7.800000000000011</v>
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR8">
-        <v>7.823240208781254</v>
+        <v>7.890281525642505</v>
       </c>
       <c r="AS8">
-        <v>9.623240208781265</v>
+        <v>8.910281525642516</v>
       </c>
       <c r="AT8">
-        <v>8.723240208781259</v>
+        <v>8.400281525642511</v>
       </c>
       <c r="AU8">
-        <v>2.180810052195315</v>
+        <v>2.100070381410628</v>
       </c>
       <c r="AV8">
-        <v>5.898436507750732</v>
+        <v>4.345503062353619</v>
       </c>
       <c r="AW8">
-        <v>5.472672171724974</v>
+        <v>4.310457345837744</v>
       </c>
       <c r="AX8">
-        <v>6.077994959568073</v>
+        <v>5.056869047112899</v>
       </c>
       <c r="AY8">
         <v>0.8436468628413508</v>
@@ -2091,22 +2091,22 @@
         <v>3</v>
       </c>
       <c r="BA8">
-        <v>1.541161542643699</v>
+        <v>1.930645252303767</v>
       </c>
       <c r="BB8">
-        <v>-4.006524474852094</v>
+        <v>1.354753062157686</v>
       </c>
       <c r="BC8">
-        <v>11.41694912221213</v>
+        <v>5.754964092348529</v>
       </c>
       <c r="BD8">
-        <v>42.06393827345702</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>23.63541255450272</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>0.6873186760847522</v>
+        <v>0.9442145399410329</v>
       </c>
     </row>
     <row r="9" spans="1:58">
@@ -2117,13 +2117,13 @@
         <v>71</v>
       </c>
       <c r="C9">
-        <v>48.25</v>
+        <v>48.825</v>
       </c>
       <c r="D9">
-        <v>46.575</v>
+        <v>47.5</v>
       </c>
       <c r="E9">
-        <v>1.675</v>
+        <v>1.325</v>
       </c>
       <c r="F9" t="s">
         <v>75</v>
@@ -2135,22 +2135,22 @@
         <v>85</v>
       </c>
       <c r="I9">
-        <v>50.8832059056156</v>
+        <v>50.68777575914871</v>
       </c>
       <c r="J9">
-        <v>49.11679409438439</v>
+        <v>49.31222424085129</v>
       </c>
       <c r="K9">
-        <v>1.766411811231215</v>
+        <v>1.375551518297428</v>
       </c>
       <c r="L9">
-        <v>-1.225993544904167</v>
+        <v>-0.4670255429338032</v>
       </c>
       <c r="M9">
-        <v>0.5404182663270487</v>
+        <v>0.9085259753636247</v>
       </c>
       <c r="N9">
-        <v>0.5404182663270487</v>
+        <v>0.9085259753636247</v>
       </c>
       <c r="O9">
         <v>0.25</v>
@@ -2159,28 +2159,28 @@
         <v>0.75</v>
       </c>
       <c r="Q9">
-        <v>50.42345832627655</v>
+        <v>50.51264118054853</v>
       </c>
       <c r="R9">
-        <v>49.57654167372345</v>
+        <v>49.48735881945147</v>
       </c>
       <c r="S9">
-        <v>-0.9194951586781249</v>
+        <v>-0.3502691572003522</v>
       </c>
       <c r="T9">
-        <v>0.8469166525530903</v>
+        <v>1.025282361097076</v>
       </c>
       <c r="U9">
-        <v>0.8469166525530903</v>
+        <v>1.025282361097076</v>
       </c>
       <c r="V9">
-        <v>55.65418073718285</v>
+        <v>56.86396059822987</v>
       </c>
       <c r="W9">
-        <v>44.34581926281715</v>
+        <v>43.13603940177013</v>
       </c>
       <c r="X9" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="Y9" t="s">
         <v>70</v>
@@ -2195,13 +2195,13 @@
         <v>90</v>
       </c>
       <c r="AC9">
-        <v>55.65418073718285</v>
+        <v>56.86396059822987</v>
       </c>
       <c r="AD9" t="s">
         <v>92</v>
       </c>
       <c r="AE9">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF9">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AK9">
-        <v>0.530870777381373</v>
+        <v>0.2022279921984468</v>
       </c>
       <c r="AL9" t="s">
         <v>98</v>
@@ -2240,10 +2240,10 @@
         <v>-1.95999999999998</v>
       </c>
       <c r="AR9">
-        <v>3.15308334744691</v>
+        <v>2.974717638902924</v>
       </c>
       <c r="AS9">
-        <v>2.80691665255307</v>
+        <v>2.985282361097055</v>
       </c>
       <c r="AT9">
         <v>2.97999999999999</v>
@@ -2255,10 +2255,10 @@
         <v>6.166256775636249</v>
       </c>
       <c r="AW9">
-        <v>5.33631557212084</v>
+        <v>5.307280945654573</v>
       </c>
       <c r="AX9">
-        <v>5.955513908523875</v>
+        <v>5.929512042779748</v>
       </c>
       <c r="AY9">
         <v>0.8436468628413508</v>
@@ -2293,13 +2293,13 @@
         <v>71</v>
       </c>
       <c r="C10">
-        <v>46.075</v>
+        <v>47.025</v>
       </c>
       <c r="D10">
-        <v>46.2</v>
+        <v>46.55</v>
       </c>
       <c r="E10">
-        <v>-0.125</v>
+        <v>0.475</v>
       </c>
       <c r="F10" t="s">
         <v>76</v>
@@ -2311,22 +2311,22 @@
         <v>81</v>
       </c>
       <c r="I10">
-        <v>49.932267678136</v>
+        <v>50.25380710659898</v>
       </c>
       <c r="J10">
-        <v>50.06773232186399</v>
+        <v>49.74619289340102</v>
       </c>
       <c r="K10">
-        <v>-0.1354646437279925</v>
+        <v>0.507614213197968</v>
       </c>
       <c r="L10">
-        <v>-2.883221219172162</v>
+        <v>-2.118496098593954</v>
       </c>
       <c r="M10">
-        <v>-3.018685862900155</v>
+        <v>-1.610881885395986</v>
       </c>
       <c r="N10">
-        <v>-3.018685862900155</v>
+        <v>-1.610881885395986</v>
       </c>
       <c r="O10">
         <v>0.25</v>
@@ -2335,25 +2335,25 @@
         <v>0.75</v>
       </c>
       <c r="Q10">
-        <v>48.85105972094644</v>
+        <v>49.45937106962625</v>
       </c>
       <c r="R10">
-        <v>51.14894027905356</v>
+        <v>50.54062893037375</v>
       </c>
       <c r="S10">
-        <v>-2.162415914379122</v>
+        <v>-1.588872073945465</v>
       </c>
       <c r="T10">
-        <v>-2.297880558107114</v>
+        <v>-1.081257860747497</v>
       </c>
       <c r="U10">
-        <v>-2.297880558107114</v>
+        <v>-1.081257860747497</v>
       </c>
       <c r="V10">
-        <v>34.57168958828296</v>
+        <v>42.55353044592097</v>
       </c>
       <c r="W10">
-        <v>65.42831041171704</v>
+        <v>57.44646955407903</v>
       </c>
       <c r="X10" t="s">
         <v>88</v>
@@ -2365,19 +2365,19 @@
         <v>91</v>
       </c>
       <c r="AA10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AB10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AC10">
-        <v>34.57168958828296</v>
+        <v>42.55353044592097</v>
       </c>
       <c r="AD10" t="s">
         <v>92</v>
       </c>
       <c r="AE10">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF10">
         <v>0</v>
@@ -2395,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="AK10">
-        <v>1.248471410266716</v>
+        <v>0.9173357196002934</v>
       </c>
       <c r="AL10" t="s">
         <v>96</v>
@@ -2416,25 +2416,25 @@
         <v>-3.47999999999999</v>
       </c>
       <c r="AR10">
-        <v>3.702119441892886</v>
+        <v>4.918742139252503</v>
       </c>
       <c r="AS10">
-        <v>1.182119441892876</v>
+        <v>2.398742139252493</v>
       </c>
       <c r="AT10">
-        <v>2.442119441892881</v>
+        <v>3.658742139252498</v>
       </c>
       <c r="AU10">
-        <v>0.6105298604732202</v>
+        <v>0.9146855348131244</v>
       </c>
       <c r="AV10">
         <v>5.775280601260435</v>
       </c>
       <c r="AW10">
-        <v>5.150295879788892</v>
+        <v>5.116017109818188</v>
       </c>
       <c r="AX10">
-        <v>5.789423950509446</v>
+        <v>5.758950694120796</v>
       </c>
       <c r="AY10">
         <v>0.8436468628413508</v>
@@ -2469,13 +2469,13 @@
         <v>71</v>
       </c>
       <c r="C11">
-        <v>47.3</v>
+        <v>46.025</v>
       </c>
       <c r="D11">
-        <v>50.16666667000001</v>
+        <v>49.52500000000001</v>
       </c>
       <c r="E11">
-        <v>-2.866666667</v>
+        <v>-3.5</v>
       </c>
       <c r="F11" t="s">
         <v>77</v>
@@ -2487,22 +2487,22 @@
         <v>85</v>
       </c>
       <c r="I11">
-        <v>48.52941176304619</v>
+        <v>48.16849816849816</v>
       </c>
       <c r="J11">
-        <v>51.47058823695382</v>
+        <v>51.83150183150183</v>
       </c>
       <c r="K11">
-        <v>-2.941176473907625</v>
+        <v>-3.663003663003671</v>
       </c>
       <c r="L11">
-        <v>0.5792673114617315</v>
+        <v>-0.319579423669317</v>
       </c>
       <c r="M11">
-        <v>-2.361909162445893</v>
+        <v>-3.982583086672988</v>
       </c>
       <c r="N11">
-        <v>-2.361909162445893</v>
+        <v>-3.982583086672988</v>
       </c>
       <c r="O11">
         <v>0.25</v>
@@ -2511,28 +2511,28 @@
         <v>0.75</v>
       </c>
       <c r="Q11">
-        <v>48.74663700484434</v>
+        <v>48.04865588462217</v>
       </c>
       <c r="R11">
-        <v>51.25336299515566</v>
+        <v>51.95134411537783</v>
       </c>
       <c r="S11">
-        <v>0.434450483596299</v>
+        <v>-0.2396845677519877</v>
       </c>
       <c r="T11">
-        <v>-2.506725990311326</v>
+        <v>-3.902688230755659</v>
       </c>
       <c r="U11">
-        <v>-2.506725990311326</v>
+        <v>-3.902688230755659</v>
       </c>
       <c r="V11">
-        <v>33.66396774649345</v>
+        <v>23.15815969257593</v>
       </c>
       <c r="W11">
-        <v>66.33603225350654</v>
+        <v>76.84184030742406</v>
       </c>
       <c r="X11" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="Y11" t="s">
         <v>71</v>
@@ -2547,13 +2547,13 @@
         <v>91</v>
       </c>
       <c r="AC11">
-        <v>33.66396774649345</v>
+        <v>23.15815969257593</v>
       </c>
       <c r="AD11" t="s">
         <v>92</v>
       </c>
       <c r="AE11">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF11">
         <v>0</v>
@@ -2571,13 +2571,13 @@
         <v>0</v>
       </c>
       <c r="AK11">
-        <v>0.2508301036538862</v>
+        <v>0.1383819497122092</v>
       </c>
       <c r="AL11" t="s">
         <v>99</v>
       </c>
       <c r="AM11">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AN11" t="s">
         <v>110</v>
@@ -2586,55 +2586,55 @@
         <v>71</v>
       </c>
       <c r="AP11">
-        <v>0.6258</v>
+        <v>0.5322</v>
       </c>
       <c r="AQ11">
-        <v>-25.16000000000001</v>
+        <v>-6.439999999999998</v>
       </c>
       <c r="AR11">
-        <v>7.493274009688674</v>
+        <v>4.097311769244341</v>
       </c>
       <c r="AS11">
-        <v>22.65327400968869</v>
+        <v>2.537311769244339</v>
       </c>
       <c r="AT11">
-        <v>15.07327400968868</v>
+        <v>3.317311769244339</v>
       </c>
       <c r="AU11">
-        <v>3.76831850242217</v>
+        <v>0.8293279423110849</v>
       </c>
       <c r="AV11">
-        <v>4.390437171606355</v>
+        <v>5.314982794026658</v>
       </c>
       <c r="AW11">
-        <v>5.324598663427484</v>
+        <v>4.615828922128182</v>
       </c>
       <c r="AX11">
-        <v>5.945017489960455</v>
+        <v>5.319563766674573</v>
       </c>
       <c r="AY11">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA11">
-        <v>1.906296723190152</v>
+        <v>0</v>
       </c>
       <c r="BB11">
-        <v>-1.372324784465838</v>
+        <v>-0.3706239798868902</v>
       </c>
       <c r="BC11">
-        <v>5.414780435479317</v>
+        <v>5.000892084631056</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>8.823529411764707</v>
       </c>
       <c r="BF11">
-        <v>0.9325238981752073</v>
+        <v>0.9238036867710117</v>
       </c>
     </row>
     <row r="12" spans="1:58">
@@ -2645,13 +2645,13 @@
         <v>71</v>
       </c>
       <c r="C12">
-        <v>45.875</v>
+        <v>46.3</v>
       </c>
       <c r="D12">
-        <v>49.675</v>
+        <v>51.16666667000001</v>
       </c>
       <c r="E12">
-        <v>-3.8</v>
+        <v>-4.866666667</v>
       </c>
       <c r="F12" t="s">
         <v>77</v>
@@ -2663,22 +2663,22 @@
         <v>85</v>
       </c>
       <c r="I12">
-        <v>48.01151229722657</v>
+        <v>47.50341997101561</v>
       </c>
       <c r="J12">
-        <v>51.98848770277341</v>
+        <v>52.49658002898438</v>
       </c>
       <c r="K12">
-        <v>-3.976975405546838</v>
+        <v>-4.993160057968772</v>
       </c>
       <c r="L12">
-        <v>-0.2491280460552653</v>
+        <v>1.022628397888314</v>
       </c>
       <c r="M12">
-        <v>-4.226103451602103</v>
+        <v>-3.970531660080458</v>
       </c>
       <c r="N12">
-        <v>-4.226103451602103</v>
+        <v>-3.970531660080458</v>
       </c>
       <c r="O12">
         <v>0.25</v>
@@ -2687,25 +2687,25 @@
         <v>0.75</v>
       </c>
       <c r="Q12">
-        <v>47.91808927995586</v>
+        <v>47.88690562022373</v>
       </c>
       <c r="R12">
-        <v>52.08191072004414</v>
+        <v>52.11309437977627</v>
       </c>
       <c r="S12">
-        <v>-0.1868460345414489</v>
+        <v>0.7669712984162356</v>
       </c>
       <c r="T12">
-        <v>-4.163821440088287</v>
+        <v>-4.226188759552537</v>
       </c>
       <c r="U12">
-        <v>-4.163821440088287</v>
+        <v>-4.226188759552537</v>
       </c>
       <c r="V12">
-        <v>21.63743754626992</v>
+        <v>22.86059118815288</v>
       </c>
       <c r="W12">
-        <v>78.36256245373008</v>
+        <v>77.13940881184712</v>
       </c>
       <c r="X12" t="s">
         <v>82</v>
@@ -2723,13 +2723,13 @@
         <v>91</v>
       </c>
       <c r="AC12">
-        <v>21.63743754626992</v>
+        <v>22.86059118815288</v>
       </c>
       <c r="AD12" t="s">
         <v>92</v>
       </c>
       <c r="AE12">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF12">
         <v>0</v>
@@ -2747,13 +2747,13 @@
         <v>0</v>
       </c>
       <c r="AK12">
-        <v>0.1078756083395196</v>
+        <v>0.4428110856013305</v>
       </c>
       <c r="AL12" t="s">
         <v>100</v>
       </c>
       <c r="AM12">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="AN12" t="s">
         <v>111</v>
@@ -2762,55 +2762,55 @@
         <v>71</v>
       </c>
       <c r="AP12">
-        <v>0.5322</v>
+        <v>0.6258</v>
       </c>
       <c r="AQ12">
-        <v>-6.439999999999998</v>
+        <v>-25.16000000000001</v>
       </c>
       <c r="AR12">
-        <v>3.836178559911713</v>
+        <v>5.773811240447463</v>
       </c>
       <c r="AS12">
-        <v>2.276178559911711</v>
+        <v>20.93381124044748</v>
       </c>
       <c r="AT12">
-        <v>3.056178559911712</v>
+        <v>13.35381124044747</v>
       </c>
       <c r="AU12">
-        <v>0.7640446399779279</v>
+        <v>3.338452810111868</v>
       </c>
       <c r="AV12">
-        <v>5.314982794026658</v>
+        <v>4.390437171606355</v>
       </c>
       <c r="AW12">
-        <v>4.602075819872517</v>
+        <v>5.032171060126636</v>
       </c>
       <c r="AX12">
-        <v>5.307634490167654</v>
+        <v>5.684595641533177</v>
       </c>
       <c r="AY12">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.906296723190152</v>
       </c>
       <c r="BB12">
-        <v>-0.3706239798868902</v>
+        <v>-1.372324784465838</v>
       </c>
       <c r="BC12">
-        <v>5.000892084631056</v>
+        <v>5.414780435479317</v>
       </c>
       <c r="BD12">
-        <v>17.64705882352941</v>
+        <v>0</v>
       </c>
       <c r="BE12">
-        <v>8.823529411764707</v>
+        <v>0</v>
       </c>
       <c r="BF12">
-        <v>0.9238036867710117</v>
+        <v>0.9325238981752073</v>
       </c>
     </row>
     <row r="13" spans="1:58">
@@ -2821,13 +2821,13 @@
         <v>71</v>
       </c>
       <c r="C13">
-        <v>17.175</v>
+        <v>17.05</v>
       </c>
       <c r="D13">
-        <v>44.8</v>
+        <v>45.25</v>
       </c>
       <c r="E13">
-        <v>-27.625</v>
+        <v>-28.2</v>
       </c>
       <c r="F13" t="s">
         <v>78</v>
@@ -2839,22 +2839,22 @@
         <v>86</v>
       </c>
       <c r="I13">
-        <v>27.71278741427995</v>
+        <v>27.36757624398074</v>
       </c>
       <c r="J13">
-        <v>72.28721258572004</v>
+        <v>72.63242375601926</v>
       </c>
       <c r="K13">
-        <v>-44.5744251714401</v>
+        <v>-45.26484751203853</v>
       </c>
       <c r="L13">
-        <v>-9.884364997571231</v>
+        <v>-9.55808334289528</v>
       </c>
       <c r="M13">
-        <v>-54.45879016901133</v>
+        <v>-54.82293085493381</v>
       </c>
       <c r="N13">
-        <v>-54.45879016901133</v>
+        <v>-54.82293085493381</v>
       </c>
       <c r="O13">
         <v>0.25</v>
@@ -2863,19 +2863,19 @@
         <v>0.75</v>
       </c>
       <c r="Q13">
-        <v>24.00615054019074</v>
+        <v>23.78329499039501</v>
       </c>
       <c r="R13">
-        <v>75.99384945980927</v>
+        <v>76.21670500960499</v>
       </c>
       <c r="S13">
-        <v>-7.413273748178426</v>
+        <v>-7.168562507171458</v>
       </c>
       <c r="T13">
-        <v>-51.98769891961852</v>
+        <v>-52.43341001920999</v>
       </c>
       <c r="U13">
-        <v>-51.98769891961852</v>
+        <v>-52.43341001920999</v>
       </c>
       <c r="V13">
         <v>0.1</v>
@@ -2905,7 +2905,7 @@
         <v>92</v>
       </c>
       <c r="AE13">
-        <v>8.73527450544567</v>
+        <v>8.719769247836687</v>
       </c>
       <c r="AF13">
         <v>0</v>
@@ -2923,10 +2923,10 @@
         <v>0</v>
       </c>
       <c r="AK13">
-        <v>4.280055594087199</v>
+        <v>4.138771493218101</v>
       </c>
       <c r="AL13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AM13">
         <v>-10</v>
@@ -2944,13 +2944,13 @@
         <v>-10.02000000000001</v>
       </c>
       <c r="AR13">
-        <v>41.98769891961852</v>
+        <v>42.43341001920999</v>
       </c>
       <c r="AS13">
-        <v>41.96769891961851</v>
+        <v>42.41341001920998</v>
       </c>
       <c r="AT13">
-        <v>41.97769891961852</v>
+        <v>42.42341001920998</v>
       </c>
       <c r="AU13">
         <v>6</v>
@@ -2959,10 +2959,10 @@
         <v>4.808765205332268</v>
       </c>
       <c r="AW13">
-        <v>8.329220566311957</v>
+        <v>8.264248554060883</v>
       </c>
       <c r="AX13">
-        <v>8.738867047371532</v>
+        <v>8.676962959046175</v>
       </c>
       <c r="AY13">
         <v>0.8436468628413508</v>

--- a/outputs/Block5B_Senate_Race_Attribution.xlsx
+++ b/outputs/Block5B_Senate_Race_Attribution.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="115">
   <si>
     <t>STATE</t>
   </si>
@@ -193,24 +193,24 @@
     <t>Georgia</t>
   </si>
   <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
     <t>New Hampshire</t>
   </si>
   <si>
-    <t>North Carolina</t>
-  </si>
-  <si>
     <t>Michigan</t>
   </si>
   <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
     <t>Alaska</t>
   </si>
   <si>
-    <t>Ohio</t>
-  </si>
-  <si>
-    <t>Texas</t>
-  </si>
-  <si>
     <t>Maine</t>
   </si>
   <si>
@@ -250,6 +250,9 @@
     <t>RSenLeanPollH (&gt;1&lt;=5%)</t>
   </si>
   <si>
+    <t>RSenLikPollH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
     <t>RSenSafPollH (&gt;10%)</t>
   </si>
   <si>
@@ -265,6 +268,9 @@
     <t>R Lean</t>
   </si>
   <si>
+    <t>R Likely</t>
+  </si>
+  <si>
     <t>R Safe</t>
   </si>
   <si>
@@ -304,12 +310,12 @@
     <t>EVEN</t>
   </si>
   <si>
+    <t>R+5</t>
+  </si>
+  <si>
     <t>R+6</t>
   </si>
   <si>
-    <t>R+5</t>
-  </si>
-  <si>
     <t>D+4</t>
   </si>
   <si>
@@ -322,22 +328,22 @@
     <t>50.62% D</t>
   </si>
   <si>
+    <t>48.69% R</t>
+  </si>
+  <si>
     <t>56.64% D</t>
   </si>
   <si>
-    <t>48.69% R</t>
-  </si>
-  <si>
     <t>49.90% D</t>
   </si>
   <si>
+    <t>Appointed (2025)[p]</t>
+  </si>
+  <si>
+    <t>53.51% R</t>
+  </si>
+  <si>
     <t>53.90% R</t>
-  </si>
-  <si>
-    <t>Appointed (2025)[p]</t>
-  </si>
-  <si>
-    <t>53.51% R</t>
   </si>
   <si>
     <t>50.98% R</t>
@@ -897,40 +903,40 @@
         <v>70</v>
       </c>
       <c r="C2">
-        <v>51.9</v>
+        <v>52.6</v>
       </c>
       <c r="D2">
-        <v>43.375</v>
+        <v>43.775</v>
       </c>
       <c r="E2">
-        <v>8.525</v>
+        <v>8.824999999999999</v>
       </c>
       <c r="F2" t="s">
         <v>72</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I2">
-        <v>54.47389136709525</v>
+        <v>54.57846952010376</v>
       </c>
       <c r="J2">
-        <v>45.52610863290474</v>
+        <v>45.42153047989624</v>
       </c>
       <c r="K2">
-        <v>8.947782734190504</v>
+        <v>9.156939040207519</v>
       </c>
       <c r="L2">
-        <v>4.265768337051614</v>
+        <v>4.865057489990605</v>
       </c>
       <c r="M2">
-        <v>13.21355107124212</v>
+        <v>14.02199653019812</v>
       </c>
       <c r="N2">
-        <v>13.21355107124212</v>
+        <v>14.02199653019812</v>
       </c>
       <c r="O2">
         <v>0.25</v>
@@ -939,49 +945,49 @@
         <v>0.75</v>
       </c>
       <c r="Q2">
-        <v>56.07355449348961</v>
+        <v>56.40286607885024</v>
       </c>
       <c r="R2">
-        <v>43.92644550651039</v>
+        <v>43.59713392114976</v>
       </c>
       <c r="S2">
-        <v>3.19932625278871</v>
+        <v>3.648793117492954</v>
       </c>
       <c r="T2">
-        <v>12.14710898697921</v>
+        <v>12.80573215770047</v>
       </c>
       <c r="U2">
-        <v>12.14710898697921</v>
+        <v>12.80573215770047</v>
       </c>
       <c r="V2">
-        <v>97.20159014526948</v>
+        <v>97.54891845534584</v>
       </c>
       <c r="W2">
-        <v>2.798409854730521</v>
+        <v>2.451081544654166</v>
       </c>
       <c r="X2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y2" t="s">
         <v>70</v>
       </c>
       <c r="Z2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AA2" t="s">
         <v>70</v>
       </c>
       <c r="AB2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AC2">
-        <v>2.798409854730521</v>
+        <v>2.451081544654166</v>
       </c>
       <c r="AD2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AE2">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -999,16 +1005,16 @@
         <v>-0</v>
       </c>
       <c r="AK2">
-        <v>1.847131873272999</v>
+        <v>2.10663168860181</v>
       </c>
       <c r="AL2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AM2">
         <v>-1</v>
       </c>
       <c r="AN2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AO2" t="s">
         <v>70</v>
@@ -1020,25 +1026,25 @@
         <v>1.239999999999995</v>
       </c>
       <c r="AR2">
-        <v>13.14710898697921</v>
+        <v>13.80573215770047</v>
       </c>
       <c r="AS2">
-        <v>10.90710898697922</v>
+        <v>11.56573215770048</v>
       </c>
       <c r="AT2">
-        <v>12.02710898697922</v>
+        <v>12.68573215770047</v>
       </c>
       <c r="AU2">
-        <v>3.006777246744804</v>
+        <v>3.171433039425119</v>
       </c>
       <c r="AV2">
         <v>5.482188815058572</v>
       </c>
       <c r="AW2">
-        <v>5.779286853475976</v>
+        <v>5.944032352845992</v>
       </c>
       <c r="AX2">
-        <v>6.355473118826183</v>
+        <v>6.505643906719904</v>
       </c>
       <c r="AY2">
         <v>0.8436468628413508</v>
@@ -1070,43 +1076,43 @@
         <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3">
-        <v>49.375</v>
+        <v>50.74999999999999</v>
       </c>
       <c r="D3">
-        <v>42.475</v>
+        <v>41.375</v>
       </c>
       <c r="E3">
-        <v>6.9</v>
+        <v>9.375</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I3">
-        <v>53.75612411540556</v>
+        <v>55.08819538670284</v>
       </c>
       <c r="J3">
-        <v>46.24387588459445</v>
+        <v>44.91180461329715</v>
       </c>
       <c r="K3">
-        <v>7.512248230811103</v>
+        <v>10.17639077340569</v>
       </c>
       <c r="L3">
-        <v>2.15168128687088</v>
+        <v>-1.39302597381857</v>
       </c>
       <c r="M3">
-        <v>9.663929517681982</v>
+        <v>8.783364799587122</v>
       </c>
       <c r="N3">
-        <v>9.663929517681982</v>
+        <v>8.783364799587122</v>
       </c>
       <c r="O3">
         <v>0.25</v>
@@ -1115,49 +1121,49 @@
         <v>0.75</v>
       </c>
       <c r="Q3">
-        <v>54.56300459798213</v>
+        <v>54.56581064652088</v>
       </c>
       <c r="R3">
-        <v>45.43699540201787</v>
+        <v>45.43418935347912</v>
       </c>
       <c r="S3">
-        <v>1.613760965153158</v>
+        <v>-1.044769480363929</v>
       </c>
       <c r="T3">
-        <v>9.126009195964262</v>
+        <v>9.131621293041764</v>
       </c>
       <c r="U3">
-        <v>9.126009195964262</v>
+        <v>9.131621293041764</v>
       </c>
       <c r="V3">
-        <v>95.66726197064992</v>
+        <v>95.70206414313375</v>
       </c>
       <c r="W3">
-        <v>4.332738029350081</v>
+        <v>4.297935856866253</v>
       </c>
       <c r="X3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y3" t="s">
         <v>70</v>
       </c>
       <c r="Z3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AA3" t="s">
         <v>70</v>
       </c>
       <c r="AB3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AC3">
-        <v>4.332738029350081</v>
+        <v>95.70206414313375</v>
       </c>
       <c r="AD3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AE3">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -1172,49 +1178,49 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>0.9317053276388867</v>
+        <v>0.6031979407292191</v>
       </c>
       <c r="AL3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AM3">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AN3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AO3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AP3">
-        <v>0.5664</v>
+        <v>0.4869</v>
       </c>
       <c r="AQ3">
-        <v>13.28</v>
+        <v>2.620000000000005</v>
       </c>
       <c r="AR3">
-        <v>7.126009195964262</v>
+        <v>10.13162129304176</v>
       </c>
       <c r="AS3">
-        <v>4.15399080403574</v>
+        <v>6.51162129304176</v>
       </c>
       <c r="AT3">
-        <v>5.640000000000001</v>
+        <v>8.321621293041762</v>
       </c>
       <c r="AU3">
-        <v>1.41</v>
+        <v>2.08040532326044</v>
       </c>
       <c r="AV3">
-        <v>5.112371008372736</v>
+        <v>4.808352845952818</v>
       </c>
       <c r="AW3">
-        <v>4.623848774507894</v>
+        <v>4.614040001124252</v>
       </c>
       <c r="AX3">
-        <v>5.326524149844822</v>
+        <v>5.318011579654246</v>
       </c>
       <c r="AY3">
         <v>0.8436468628413508</v>
@@ -1223,22 +1229,22 @@
         <v>3</v>
       </c>
       <c r="BA3">
-        <v>2.230264441281014</v>
+        <v>2.170415722150866</v>
       </c>
       <c r="BB3">
-        <v>0.8055665595386128</v>
+        <v>0.275052926652725</v>
       </c>
       <c r="BC3">
-        <v>5.981300614496139</v>
+        <v>2.954610092474855</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>30.09640135085562</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>30.09640135085562</v>
       </c>
       <c r="BF3">
-        <v>0.9698252308898075</v>
+        <v>0.9401657373535796</v>
       </c>
     </row>
     <row r="4" spans="1:58">
@@ -1246,43 +1252,43 @@
         <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4">
-        <v>50.675</v>
+        <v>49.77500000000001</v>
       </c>
       <c r="D4">
-        <v>41.45</v>
+        <v>43.225</v>
       </c>
       <c r="E4">
-        <v>9.225</v>
+        <v>6.550000000000001</v>
       </c>
       <c r="F4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I4">
-        <v>55.0067842605156</v>
+        <v>53.52150537634409</v>
       </c>
       <c r="J4">
-        <v>44.9932157394844</v>
+        <v>46.47849462365591</v>
       </c>
       <c r="K4">
-        <v>10.0135685210312</v>
+        <v>7.043010752688183</v>
       </c>
       <c r="L4">
-        <v>-1.380307966940977</v>
+        <v>2.668898933726563</v>
       </c>
       <c r="M4">
-        <v>8.633260554090226</v>
+        <v>9.711909686414746</v>
       </c>
       <c r="N4">
-        <v>8.633260554090226</v>
+        <v>9.711909686414746</v>
       </c>
       <c r="O4">
         <v>0.25</v>
@@ -1291,49 +1297,49 @@
         <v>0.75</v>
       </c>
       <c r="Q4">
-        <v>54.48916877291273</v>
+        <v>54.52234247649155</v>
       </c>
       <c r="R4">
-        <v>45.51083122708727</v>
+        <v>45.47765752350845</v>
       </c>
       <c r="S4">
-        <v>-1.035230975205733</v>
+        <v>2.001674200294921</v>
       </c>
       <c r="T4">
-        <v>8.97833754582547</v>
+        <v>9.044684952983104</v>
       </c>
       <c r="U4">
-        <v>8.97833754582547</v>
+        <v>9.044684952983104</v>
       </c>
       <c r="V4">
-        <v>95.47518279599674</v>
+        <v>95.4133894089687</v>
       </c>
       <c r="W4">
-        <v>4.52481720400325</v>
+        <v>4.586610591031304</v>
       </c>
       <c r="X4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y4" t="s">
         <v>70</v>
       </c>
       <c r="Z4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AA4" t="s">
         <v>70</v>
       </c>
       <c r="AB4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AC4">
-        <v>95.47518279599674</v>
+        <v>4.586610591031304</v>
       </c>
       <c r="AD4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AE4">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF4">
         <v>0</v>
@@ -1348,49 +1354,49 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK4">
-        <v>0.5976908822084687</v>
+        <v>1.155667138370202</v>
       </c>
       <c r="AL4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AO4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AP4">
-        <v>0.4869</v>
+        <v>0.5664</v>
       </c>
       <c r="AQ4">
-        <v>2.620000000000005</v>
+        <v>13.28</v>
       </c>
       <c r="AR4">
-        <v>9.97833754582547</v>
+        <v>7.044684952983104</v>
       </c>
       <c r="AS4">
-        <v>6.358337545825465</v>
+        <v>4.235315047016897</v>
       </c>
       <c r="AT4">
-        <v>8.168337545825468</v>
+        <v>5.640000000000001</v>
       </c>
       <c r="AU4">
-        <v>2.042084386456367</v>
+        <v>1.41</v>
       </c>
       <c r="AV4">
-        <v>4.808352845952818</v>
+        <v>5.112371008372736</v>
       </c>
       <c r="AW4">
-        <v>4.597750331251065</v>
+        <v>4.666431817801355</v>
       </c>
       <c r="AX4">
-        <v>5.303884438586613</v>
+        <v>5.363531293798034</v>
       </c>
       <c r="AY4">
         <v>0.8436468628413508</v>
@@ -1399,22 +1405,22 @@
         <v>3</v>
       </c>
       <c r="BA4">
-        <v>2.170415722150866</v>
+        <v>2.230264441281014</v>
       </c>
       <c r="BB4">
-        <v>0.275052926652725</v>
+        <v>0.8055665595386128</v>
       </c>
       <c r="BC4">
-        <v>2.954610092474855</v>
+        <v>5.981300614496139</v>
       </c>
       <c r="BD4">
-        <v>30.09640135085562</v>
+        <v>0</v>
       </c>
       <c r="BE4">
-        <v>30.09640135085562</v>
+        <v>0</v>
       </c>
       <c r="BF4">
-        <v>0.9401657373535796</v>
+        <v>0.9698252308898075</v>
       </c>
     </row>
     <row r="5" spans="1:58">
@@ -1425,40 +1431,40 @@
         <v>70</v>
       </c>
       <c r="C5">
-        <v>48.825</v>
+        <v>48.725</v>
       </c>
       <c r="D5">
-        <v>45.275</v>
+        <v>45.05</v>
       </c>
       <c r="E5">
-        <v>3.55</v>
+        <v>3.675</v>
       </c>
       <c r="F5" t="s">
         <v>74</v>
       </c>
       <c r="G5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I5">
-        <v>51.88629117959618</v>
+        <v>51.95947747267395</v>
       </c>
       <c r="J5">
-        <v>48.11370882040383</v>
+        <v>48.04052252732605</v>
       </c>
       <c r="K5">
-        <v>3.772582359192349</v>
+        <v>3.918954945347906</v>
       </c>
       <c r="L5">
-        <v>2.784312428859241</v>
+        <v>2.590328418627033</v>
       </c>
       <c r="M5">
-        <v>6.55689478805159</v>
+        <v>6.509283363974939</v>
       </c>
       <c r="N5">
-        <v>6.55689478805159</v>
+        <v>6.509283363974939</v>
       </c>
       <c r="O5">
         <v>0.25</v>
@@ -1467,49 +1473,49 @@
         <v>0.75</v>
       </c>
       <c r="Q5">
-        <v>52.93040834041839</v>
+        <v>52.93085062965909</v>
       </c>
       <c r="R5">
-        <v>47.06959165958161</v>
+        <v>47.06914937034091</v>
       </c>
       <c r="S5">
-        <v>2.088234321644431</v>
+        <v>1.942746313970275</v>
       </c>
       <c r="T5">
-        <v>5.86081668083678</v>
+        <v>5.861701259318181</v>
       </c>
       <c r="U5">
-        <v>5.86081668083678</v>
+        <v>5.861701259318181</v>
       </c>
       <c r="V5">
-        <v>86.78566705347262</v>
+        <v>86.85847000210781</v>
       </c>
       <c r="W5">
-        <v>13.21433294652739</v>
+        <v>13.1415299978922</v>
       </c>
       <c r="X5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Y5" t="s">
         <v>70</v>
       </c>
       <c r="Z5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AA5" t="s">
         <v>70</v>
       </c>
       <c r="AB5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AC5">
-        <v>13.21433294652739</v>
+        <v>13.1415299978922</v>
       </c>
       <c r="AD5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AE5">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -1527,16 +1533,16 @@
         <v>-0</v>
       </c>
       <c r="AK5">
-        <v>1.205642647732428</v>
+        <v>1.121645107337891</v>
       </c>
       <c r="AL5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AM5">
         <v>0</v>
       </c>
       <c r="AN5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AO5" t="s">
         <v>70</v>
@@ -1548,25 +1554,25 @@
         <v>-0.2000000000000028</v>
       </c>
       <c r="AR5">
-        <v>5.86081668083678</v>
+        <v>5.861701259318181</v>
       </c>
       <c r="AS5">
-        <v>6.060816680836782</v>
+        <v>6.061701259318184</v>
       </c>
       <c r="AT5">
-        <v>5.960816680836781</v>
+        <v>5.961701259318183</v>
       </c>
       <c r="AU5">
-        <v>1.490204170209195</v>
+        <v>1.490425314829546</v>
       </c>
       <c r="AV5">
         <v>4.890566271054463</v>
       </c>
       <c r="AW5">
-        <v>4.535644811700211</v>
+        <v>4.518046915456435</v>
       </c>
       <c r="AX5">
-        <v>5.250138654099052</v>
+        <v>5.234943166800129</v>
       </c>
       <c r="AY5">
         <v>0.8436468628413508</v>
@@ -1601,40 +1607,40 @@
         <v>71</v>
       </c>
       <c r="C6">
-        <v>50.55</v>
+        <v>47.825</v>
       </c>
       <c r="D6">
-        <v>48.25</v>
+        <v>43.7</v>
       </c>
       <c r="E6">
-        <v>2.3</v>
+        <v>4.125</v>
       </c>
       <c r="F6" t="s">
         <v>75</v>
       </c>
       <c r="G6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I6">
-        <v>51.16396761133603</v>
+        <v>52.25348265501229</v>
       </c>
       <c r="J6">
-        <v>48.83603238866397</v>
+        <v>47.74651734498771</v>
       </c>
       <c r="K6">
-        <v>2.327935222672068</v>
+        <v>4.506965310024583</v>
       </c>
       <c r="L6">
-        <v>1.046950541341876</v>
+        <v>-2.638289777369295</v>
       </c>
       <c r="M6">
-        <v>3.374885764013944</v>
+        <v>1.868675532655288</v>
       </c>
       <c r="N6">
-        <v>3.374885764013944</v>
+        <v>1.868675532655288</v>
       </c>
       <c r="O6">
         <v>0.25</v>
@@ -1643,49 +1649,49 @@
         <v>0.75</v>
       </c>
       <c r="Q6">
-        <v>51.55657406433924</v>
+        <v>51.26412398849881</v>
       </c>
       <c r="R6">
-        <v>48.44342593566076</v>
+        <v>48.73587601150119</v>
       </c>
       <c r="S6">
-        <v>0.7852129060064073</v>
+        <v>-1.978717333026971</v>
       </c>
       <c r="T6">
-        <v>3.113148128678475</v>
+        <v>2.528247976997612</v>
       </c>
       <c r="U6">
-        <v>3.113148128678475</v>
+        <v>2.528247976997612</v>
       </c>
       <c r="V6">
-        <v>69.21939506969498</v>
+        <v>68.62056620003455</v>
       </c>
       <c r="W6">
-        <v>30.78060493030502</v>
+        <v>31.37943379996545</v>
       </c>
       <c r="X6" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="Y6" t="s">
         <v>70</v>
       </c>
       <c r="Z6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AA6" t="s">
         <v>70</v>
       </c>
       <c r="AB6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AC6">
-        <v>69.21939506969498</v>
+        <v>68.62056620003455</v>
       </c>
       <c r="AD6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AE6">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -1703,70 +1709,58 @@
         <v>0</v>
       </c>
       <c r="AK6">
-        <v>0.4533428826539674</v>
+        <v>1.1424129848733</v>
       </c>
       <c r="AL6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AM6">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AN6" t="s">
-        <v>105</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP6">
-        <v>0.539</v>
-      </c>
-      <c r="AQ6">
-        <v>-7.800000000000011</v>
+        <v>107</v>
       </c>
       <c r="AR6">
-        <v>9.113148128678475</v>
-      </c>
-      <c r="AS6">
-        <v>10.91314812867849</v>
+        <v>7.528247976997612</v>
       </c>
       <c r="AT6">
-        <v>10.01314812867848</v>
+        <v>7.528247976997612</v>
       </c>
       <c r="AU6">
-        <v>2.50328703216962</v>
+        <v>1.882061994249403</v>
       </c>
       <c r="AV6">
-        <v>5.898436507750732</v>
+        <v>4.567515257270437</v>
       </c>
       <c r="AW6">
-        <v>5.60843385395642</v>
+        <v>4.490926033506978</v>
       </c>
       <c r="AX6">
-        <v>6.200517101304247</v>
+        <v>5.211554342784182</v>
       </c>
       <c r="AY6">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA6">
-        <v>1.541161542643699</v>
+        <v>2.797261014127842</v>
       </c>
       <c r="BB6">
-        <v>-4.006524474852094</v>
+        <v>0.1730167113317724</v>
       </c>
       <c r="BC6">
-        <v>11.41694912221213</v>
+        <v>2.956526743070407</v>
       </c>
       <c r="BD6">
-        <v>42.06393827345702</v>
+        <v>17.4915896825486</v>
       </c>
       <c r="BE6">
-        <v>23.63541255450272</v>
+        <v>0</v>
       </c>
       <c r="BF6">
-        <v>0.6873186760847522</v>
+        <v>0.956231216651788</v>
       </c>
     </row>
     <row r="7" spans="1:58">
@@ -1777,40 +1771,40 @@
         <v>71</v>
       </c>
       <c r="C7">
-        <v>47.8</v>
+        <v>48.9</v>
       </c>
       <c r="D7">
-        <v>43.7</v>
+        <v>46.175</v>
       </c>
       <c r="E7">
-        <v>4.100000000000001</v>
+        <v>2.725</v>
       </c>
       <c r="F7" t="s">
         <v>75</v>
       </c>
       <c r="G7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I7">
-        <v>52.24043715846994</v>
+        <v>51.43307914804102</v>
       </c>
       <c r="J7">
-        <v>47.75956284153006</v>
+        <v>48.56692085195898</v>
       </c>
       <c r="K7">
-        <v>4.480874316939889</v>
+        <v>2.866158296082041</v>
       </c>
       <c r="L7">
-        <v>-2.617231028609809</v>
+        <v>-0.9522874185159853</v>
       </c>
       <c r="M7">
-        <v>1.86364328833008</v>
+        <v>1.913870877566056</v>
       </c>
       <c r="N7">
-        <v>1.86364328833008</v>
+        <v>1.913870877566056</v>
       </c>
       <c r="O7">
         <v>0.25</v>
@@ -1819,49 +1813,49 @@
         <v>0.75</v>
       </c>
       <c r="Q7">
-        <v>51.25897552274127</v>
+        <v>51.07597136609753</v>
       </c>
       <c r="R7">
-        <v>48.74102447725873</v>
+        <v>48.92402863390247</v>
       </c>
       <c r="S7">
-        <v>-1.962923271457357</v>
+        <v>-0.7142155638869889</v>
       </c>
       <c r="T7">
-        <v>2.517951045482532</v>
+        <v>2.151942732195052</v>
       </c>
       <c r="U7">
-        <v>2.517951045482532</v>
+        <v>2.151942732195052</v>
       </c>
       <c r="V7">
-        <v>68.55458229868631</v>
+        <v>66.42247604555808</v>
       </c>
       <c r="W7">
-        <v>31.44541770131368</v>
+        <v>33.57752395444192</v>
       </c>
       <c r="X7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Y7" t="s">
         <v>70</v>
       </c>
       <c r="Z7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AA7" t="s">
         <v>70</v>
       </c>
       <c r="AB7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AC7">
-        <v>68.55458229868631</v>
+        <v>66.42247604555808</v>
       </c>
       <c r="AD7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AE7">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF7">
         <v>0</v>
@@ -1879,58 +1873,70 @@
         <v>0</v>
       </c>
       <c r="AK7">
-        <v>1.133294279174486</v>
+        <v>0.4123525480695734</v>
       </c>
       <c r="AL7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AM7">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="AN7" t="s">
-        <v>106</v>
+        <v>108</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AP7">
+        <v>0.5351</v>
+      </c>
+      <c r="AQ7">
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR7">
-        <v>7.517951045482532</v>
+        <v>8.151942732195053</v>
+      </c>
+      <c r="AS7">
+        <v>9.171942732195063</v>
       </c>
       <c r="AT7">
-        <v>7.517951045482532</v>
+        <v>8.661942732195058</v>
       </c>
       <c r="AU7">
-        <v>1.879487761370633</v>
+        <v>2.165485683048765</v>
       </c>
       <c r="AV7">
-        <v>4.567515257270437</v>
+        <v>4.345503062353619</v>
       </c>
       <c r="AW7">
-        <v>4.489472846184185</v>
+        <v>4.331813166230072</v>
       </c>
       <c r="AX7">
-        <v>5.210302147283503</v>
+        <v>5.075084958548591</v>
       </c>
       <c r="AY7">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA7">
-        <v>2.797261014127842</v>
+        <v>1.930645252303767</v>
       </c>
       <c r="BB7">
-        <v>0.1730167113317724</v>
+        <v>1.354753062157686</v>
       </c>
       <c r="BC7">
-        <v>2.956526743070407</v>
+        <v>5.754964092348529</v>
       </c>
       <c r="BD7">
-        <v>17.4915896825486</v>
+        <v>0</v>
       </c>
       <c r="BE7">
         <v>0</v>
       </c>
       <c r="BF7">
-        <v>0.956231216651788</v>
+        <v>0.9442145399410329</v>
       </c>
     </row>
     <row r="8" spans="1:58">
@@ -1941,40 +1947,40 @@
         <v>71</v>
       </c>
       <c r="C8">
-        <v>48.675</v>
+        <v>49.475</v>
       </c>
       <c r="D8">
-        <v>46.1</v>
+        <v>46.775</v>
       </c>
       <c r="E8">
-        <v>2.575</v>
+        <v>2.7</v>
       </c>
       <c r="F8" t="s">
         <v>75</v>
       </c>
       <c r="G8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I8">
-        <v>51.35848061197573</v>
+        <v>51.4025974025974</v>
       </c>
       <c r="J8">
-        <v>48.64151938802426</v>
+        <v>48.5974025974026</v>
       </c>
       <c r="K8">
-        <v>2.716961223951465</v>
+        <v>2.805194805194802</v>
       </c>
       <c r="L8">
-        <v>-1.102239597745279</v>
+        <v>-0.3163895128283701</v>
       </c>
       <c r="M8">
-        <v>1.614721626206186</v>
+        <v>2.488805292366432</v>
       </c>
       <c r="N8">
-        <v>1.614721626206186</v>
+        <v>2.488805292366432</v>
       </c>
       <c r="O8">
         <v>0.25</v>
@@ -1983,49 +1989,49 @@
         <v>0.75</v>
       </c>
       <c r="Q8">
-        <v>50.94514076282125</v>
+        <v>51.28395133528676</v>
       </c>
       <c r="R8">
-        <v>49.05485923717875</v>
+        <v>48.71604866471324</v>
       </c>
       <c r="S8">
-        <v>-0.8266796983089593</v>
+        <v>-0.2372921346212777</v>
       </c>
       <c r="T8">
-        <v>1.890281525642506</v>
+        <v>2.567902670573524</v>
       </c>
       <c r="U8">
-        <v>1.890281525642506</v>
+        <v>2.567902670573524</v>
       </c>
       <c r="V8">
-        <v>64.5725196739622</v>
+        <v>66.19625489789294</v>
       </c>
       <c r="W8">
-        <v>35.4274803260378</v>
+        <v>33.80374510210705</v>
       </c>
       <c r="X8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Y8" t="s">
         <v>70</v>
       </c>
       <c r="Z8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AA8" t="s">
         <v>70</v>
       </c>
       <c r="AB8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AC8">
-        <v>64.5725196739622</v>
+        <v>66.19625489789294</v>
       </c>
       <c r="AD8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AE8">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF8">
         <v>0</v>
@@ -2043,46 +2049,46 @@
         <v>0</v>
       </c>
       <c r="AK8">
-        <v>0.4772837463522762</v>
+        <v>0.1370006778001755</v>
       </c>
       <c r="AL8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AM8">
         <v>-6</v>
       </c>
       <c r="AN8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AO8" t="s">
         <v>71</v>
       </c>
       <c r="AP8">
-        <v>0.5351</v>
+        <v>0.539</v>
       </c>
       <c r="AQ8">
-        <v>-7.02000000000001</v>
+        <v>-7.800000000000011</v>
       </c>
       <c r="AR8">
-        <v>7.890281525642505</v>
+        <v>8.567902670573524</v>
       </c>
       <c r="AS8">
-        <v>8.910281525642516</v>
+        <v>10.36790267057354</v>
       </c>
       <c r="AT8">
-        <v>8.400281525642511</v>
+        <v>9.46790267057353</v>
       </c>
       <c r="AU8">
-        <v>2.100070381410628</v>
+        <v>2.366975667643382</v>
       </c>
       <c r="AV8">
-        <v>4.345503062353619</v>
+        <v>5.898436507750732</v>
       </c>
       <c r="AW8">
-        <v>4.310457345837744</v>
+        <v>5.547966090444774</v>
       </c>
       <c r="AX8">
-        <v>5.056869047112899</v>
+        <v>6.145877461362781</v>
       </c>
       <c r="AY8">
         <v>0.8436468628413508</v>
@@ -2091,22 +2097,22 @@
         <v>3</v>
       </c>
       <c r="BA8">
-        <v>1.930645252303767</v>
+        <v>1.541161542643699</v>
       </c>
       <c r="BB8">
-        <v>1.354753062157686</v>
+        <v>-4.006524474852094</v>
       </c>
       <c r="BC8">
-        <v>5.754964092348529</v>
+        <v>11.41694912221213</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>42.06393827345702</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>23.63541255450272</v>
       </c>
       <c r="BF8">
-        <v>0.9442145399410329</v>
+        <v>0.6873186760847522</v>
       </c>
     </row>
     <row r="9" spans="1:58">
@@ -2117,40 +2123,40 @@
         <v>71</v>
       </c>
       <c r="C9">
-        <v>48.825</v>
+        <v>48.85</v>
       </c>
       <c r="D9">
-        <v>47.5</v>
+        <v>47.55</v>
       </c>
       <c r="E9">
-        <v>1.325</v>
+        <v>1.3</v>
       </c>
       <c r="F9" t="s">
         <v>75</v>
       </c>
       <c r="G9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I9">
-        <v>50.68777575914871</v>
+        <v>50.67427385892116</v>
       </c>
       <c r="J9">
-        <v>49.31222424085129</v>
+        <v>49.32572614107884</v>
       </c>
       <c r="K9">
-        <v>1.375551518297428</v>
+        <v>1.348547717842322</v>
       </c>
       <c r="L9">
-        <v>-0.4670255429338032</v>
+        <v>-0.4691798583288631</v>
       </c>
       <c r="M9">
-        <v>0.9085259753636247</v>
+        <v>0.8793678595134593</v>
       </c>
       <c r="N9">
-        <v>0.9085259753636247</v>
+        <v>0.8793678595134593</v>
       </c>
       <c r="O9">
         <v>0.25</v>
@@ -2159,49 +2165,49 @@
         <v>0.75</v>
       </c>
       <c r="Q9">
-        <v>50.51264118054853</v>
+        <v>50.49833141204784</v>
       </c>
       <c r="R9">
-        <v>49.48735881945147</v>
+        <v>49.50166858795216</v>
       </c>
       <c r="S9">
-        <v>-0.3502691572003522</v>
+        <v>-0.3518848937466473</v>
       </c>
       <c r="T9">
-        <v>1.025282361097076</v>
+        <v>0.9966628240956751</v>
       </c>
       <c r="U9">
-        <v>1.025282361097076</v>
+        <v>0.9966628240956751</v>
       </c>
       <c r="V9">
-        <v>56.86396059822987</v>
+        <v>56.67502366776529</v>
       </c>
       <c r="W9">
-        <v>43.13603940177013</v>
+        <v>43.32497633223471</v>
       </c>
       <c r="X9" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="Y9" t="s">
         <v>70</v>
       </c>
       <c r="Z9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AA9" t="s">
         <v>70</v>
       </c>
       <c r="AB9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AC9">
-        <v>56.86396059822987</v>
+        <v>56.67502366776529</v>
       </c>
       <c r="AD9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AE9">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF9">
         <v>0</v>
@@ -2219,16 +2225,16 @@
         <v>0</v>
       </c>
       <c r="AK9">
-        <v>0.2022279921984468</v>
+        <v>0.2031608381283897</v>
       </c>
       <c r="AL9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AM9">
         <v>4</v>
       </c>
       <c r="AN9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AO9" t="s">
         <v>71</v>
@@ -2240,10 +2246,10 @@
         <v>-1.95999999999998</v>
       </c>
       <c r="AR9">
-        <v>2.974717638902924</v>
+        <v>3.003337175904325</v>
       </c>
       <c r="AS9">
-        <v>2.985282361097055</v>
+        <v>2.956662824095655</v>
       </c>
       <c r="AT9">
         <v>2.97999999999999</v>
@@ -2255,10 +2261,10 @@
         <v>6.166256775636249</v>
       </c>
       <c r="AW9">
-        <v>5.307280945654573</v>
+        <v>5.306440474313349</v>
       </c>
       <c r="AX9">
-        <v>5.929512042779748</v>
+        <v>5.92875978066179</v>
       </c>
       <c r="AY9">
         <v>0.8436468628413508</v>
@@ -2293,40 +2299,40 @@
         <v>71</v>
       </c>
       <c r="C10">
-        <v>47.025</v>
+        <v>47.125</v>
       </c>
       <c r="D10">
-        <v>46.55</v>
+        <v>46.6</v>
       </c>
       <c r="E10">
-        <v>0.475</v>
+        <v>0.525</v>
       </c>
       <c r="F10" t="s">
         <v>76</v>
       </c>
       <c r="G10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I10">
-        <v>50.25380710659898</v>
+        <v>50.28007468658309</v>
       </c>
       <c r="J10">
-        <v>49.74619289340102</v>
+        <v>49.71992531341692</v>
       </c>
       <c r="K10">
-        <v>0.507614213197968</v>
+        <v>0.5601493731661762</v>
       </c>
       <c r="L10">
-        <v>-2.118496098593954</v>
+        <v>-2.066588514966667</v>
       </c>
       <c r="M10">
-        <v>-1.610881885395986</v>
+        <v>-1.506439141800491</v>
       </c>
       <c r="N10">
-        <v>-1.610881885395986</v>
+        <v>-1.506439141800491</v>
       </c>
       <c r="O10">
         <v>0.25</v>
@@ -2335,49 +2341,49 @@
         <v>0.75</v>
       </c>
       <c r="Q10">
-        <v>49.45937106962625</v>
+        <v>49.50510399347059</v>
       </c>
       <c r="R10">
-        <v>50.54062893037375</v>
+        <v>50.49489600652941</v>
       </c>
       <c r="S10">
-        <v>-1.588872073945465</v>
+        <v>-1.549941386225</v>
       </c>
       <c r="T10">
-        <v>-1.081257860747497</v>
+        <v>-0.989792013058824</v>
       </c>
       <c r="U10">
-        <v>-1.081257860747497</v>
+        <v>-0.989792013058824</v>
       </c>
       <c r="V10">
-        <v>42.55353044592097</v>
+        <v>43.17452577301096</v>
       </c>
       <c r="W10">
-        <v>57.44646955407903</v>
+        <v>56.82547422698904</v>
       </c>
       <c r="X10" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="Y10" t="s">
         <v>71</v>
       </c>
       <c r="Z10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AA10" t="s">
         <v>70</v>
       </c>
       <c r="AB10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AC10">
-        <v>42.55353044592097</v>
+        <v>43.17452577301096</v>
       </c>
       <c r="AD10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AE10">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF10">
         <v>0</v>
@@ -2395,16 +2401,16 @@
         <v>0</v>
       </c>
       <c r="AK10">
-        <v>0.9173357196002934</v>
+        <v>0.8948590765651455</v>
       </c>
       <c r="AL10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AM10">
         <v>-6</v>
       </c>
       <c r="AN10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AO10" t="s">
         <v>71</v>
@@ -2416,25 +2422,25 @@
         <v>-3.47999999999999</v>
       </c>
       <c r="AR10">
-        <v>4.918742139252503</v>
+        <v>5.010207986941176</v>
       </c>
       <c r="AS10">
-        <v>2.398742139252493</v>
+        <v>2.490207986941166</v>
       </c>
       <c r="AT10">
-        <v>3.658742139252498</v>
+        <v>3.750207986941171</v>
       </c>
       <c r="AU10">
-        <v>0.9146855348131244</v>
+        <v>0.9375519967352928</v>
       </c>
       <c r="AV10">
         <v>5.775280601260435</v>
       </c>
       <c r="AW10">
-        <v>5.116017109818188</v>
+        <v>5.113664173968316</v>
       </c>
       <c r="AX10">
-        <v>5.758950694120796</v>
+        <v>5.756860543168386</v>
       </c>
       <c r="AY10">
         <v>0.8436468628413508</v>
@@ -2469,40 +2475,40 @@
         <v>71</v>
       </c>
       <c r="C11">
-        <v>46.025</v>
+        <v>45.925</v>
       </c>
       <c r="D11">
-        <v>49.52500000000001</v>
+        <v>47.09999999999999</v>
       </c>
       <c r="E11">
-        <v>-3.5</v>
+        <v>-1.175</v>
       </c>
       <c r="F11" t="s">
         <v>77</v>
       </c>
       <c r="G11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I11">
-        <v>48.16849816849816</v>
+        <v>49.36844934157485</v>
       </c>
       <c r="J11">
-        <v>51.83150183150183</v>
+        <v>50.63155065842515</v>
       </c>
       <c r="K11">
-        <v>-3.663003663003671</v>
+        <v>-1.263101316850296</v>
       </c>
       <c r="L11">
-        <v>-0.319579423669317</v>
+        <v>-2.267434889907832</v>
       </c>
       <c r="M11">
-        <v>-3.982583086672988</v>
+        <v>-3.530536206758129</v>
       </c>
       <c r="N11">
-        <v>-3.982583086672988</v>
+        <v>-3.530536206758129</v>
       </c>
       <c r="O11">
         <v>0.25</v>
@@ -2511,49 +2517,49 @@
         <v>0.75</v>
       </c>
       <c r="Q11">
-        <v>48.04865588462217</v>
+        <v>48.51816125785942</v>
       </c>
       <c r="R11">
-        <v>51.95134411537783</v>
+        <v>51.48183874214058</v>
       </c>
       <c r="S11">
-        <v>-0.2396845677519877</v>
+        <v>-1.700576167430874</v>
       </c>
       <c r="T11">
-        <v>-3.902688230755659</v>
+        <v>-2.96367748428117</v>
       </c>
       <c r="U11">
-        <v>-3.902688230755659</v>
+        <v>-2.96367748428117</v>
       </c>
       <c r="V11">
-        <v>23.15815969257593</v>
+        <v>29.4052758159271</v>
       </c>
       <c r="W11">
-        <v>76.84184030742406</v>
+        <v>70.5947241840729</v>
       </c>
       <c r="X11" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="Y11" t="s">
         <v>71</v>
       </c>
       <c r="Z11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AA11" t="s">
         <v>71</v>
       </c>
       <c r="AB11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AC11">
-        <v>23.15815969257593</v>
+        <v>29.4052758159271</v>
       </c>
       <c r="AD11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AE11">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF11">
         <v>0</v>
@@ -2571,16 +2577,16 @@
         <v>0</v>
       </c>
       <c r="AK11">
-        <v>0.1383819497122092</v>
+        <v>0.9818281080436774</v>
       </c>
       <c r="AL11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AM11">
         <v>-8</v>
       </c>
       <c r="AN11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AO11" t="s">
         <v>71</v>
@@ -2592,25 +2598,25 @@
         <v>-6.439999999999998</v>
       </c>
       <c r="AR11">
-        <v>4.097311769244341</v>
+        <v>5.03632251571883</v>
       </c>
       <c r="AS11">
-        <v>2.537311769244339</v>
+        <v>3.476322515718827</v>
       </c>
       <c r="AT11">
-        <v>3.317311769244339</v>
+        <v>4.256322515718828</v>
       </c>
       <c r="AU11">
-        <v>0.8293279423110849</v>
+        <v>1.064080628929707</v>
       </c>
       <c r="AV11">
         <v>5.314982794026658</v>
       </c>
       <c r="AW11">
-        <v>4.615828922128182</v>
+        <v>4.790990486816234</v>
       </c>
       <c r="AX11">
-        <v>5.319563766674573</v>
+        <v>5.472245597021904</v>
       </c>
       <c r="AY11">
         <v>0.8436468628413508</v>
@@ -2645,40 +2651,40 @@
         <v>71</v>
       </c>
       <c r="C12">
-        <v>46.3</v>
+        <v>46.03333333</v>
       </c>
       <c r="D12">
-        <v>51.16666667000001</v>
+        <v>51.26666667000001</v>
       </c>
       <c r="E12">
-        <v>-4.866666667</v>
+        <v>-5.233333333</v>
       </c>
       <c r="F12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I12">
-        <v>47.50341997101561</v>
+        <v>47.31072284686535</v>
       </c>
       <c r="J12">
-        <v>52.49658002898438</v>
+        <v>52.68927715313463</v>
       </c>
       <c r="K12">
-        <v>-4.993160057968772</v>
+        <v>-5.37855430626928</v>
       </c>
       <c r="L12">
-        <v>1.022628397888314</v>
+        <v>0.9757182060598102</v>
       </c>
       <c r="M12">
-        <v>-3.970531660080458</v>
+        <v>-4.40283610020947</v>
       </c>
       <c r="N12">
-        <v>-3.970531660080458</v>
+        <v>-4.40283610020947</v>
       </c>
       <c r="O12">
         <v>0.25</v>
@@ -2687,49 +2693,49 @@
         <v>0.75</v>
       </c>
       <c r="Q12">
-        <v>47.88690562022373</v>
+        <v>47.67661717413779</v>
       </c>
       <c r="R12">
-        <v>52.11309437977627</v>
+        <v>52.32338282586221</v>
       </c>
       <c r="S12">
-        <v>0.7669712984162356</v>
+        <v>0.7317886545448573</v>
       </c>
       <c r="T12">
-        <v>-4.226188759552537</v>
+        <v>-4.646765651724422</v>
       </c>
       <c r="U12">
-        <v>-4.226188759552537</v>
+        <v>-4.646765651724422</v>
       </c>
       <c r="V12">
-        <v>22.86059118815288</v>
+        <v>20.42376415676219</v>
       </c>
       <c r="W12">
-        <v>77.13940881184712</v>
+        <v>79.57623584323781</v>
       </c>
       <c r="X12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y12" t="s">
         <v>71</v>
       </c>
       <c r="Z12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AA12" t="s">
         <v>71</v>
       </c>
       <c r="AB12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AC12">
-        <v>22.86059118815288</v>
+        <v>20.42376415676219</v>
       </c>
       <c r="AD12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AE12">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF12">
         <v>0</v>
@@ -2747,16 +2753,16 @@
         <v>0</v>
       </c>
       <c r="AK12">
-        <v>0.4428110856013305</v>
+        <v>0.4224983766913874</v>
       </c>
       <c r="AL12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AM12">
         <v>-10</v>
       </c>
       <c r="AN12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AO12" t="s">
         <v>71</v>
@@ -2768,25 +2774,25 @@
         <v>-25.16000000000001</v>
       </c>
       <c r="AR12">
-        <v>5.773811240447463</v>
+        <v>5.353234348275578</v>
       </c>
       <c r="AS12">
-        <v>20.93381124044748</v>
+        <v>20.51323434827559</v>
       </c>
       <c r="AT12">
-        <v>13.35381124044747</v>
+        <v>12.93323434827558</v>
       </c>
       <c r="AU12">
-        <v>3.338452810111868</v>
+        <v>3.233308587068896</v>
       </c>
       <c r="AV12">
         <v>4.390437171606355</v>
       </c>
       <c r="AW12">
-        <v>5.032171060126636</v>
+        <v>4.960986351892614</v>
       </c>
       <c r="AX12">
-        <v>5.684595641533177</v>
+        <v>5.621678362644624</v>
       </c>
       <c r="AY12">
         <v>0.8436468628413508</v>
@@ -2824,37 +2830,37 @@
         <v>17.05</v>
       </c>
       <c r="D13">
-        <v>45.25</v>
+        <v>45.275</v>
       </c>
       <c r="E13">
-        <v>-28.2</v>
+        <v>-28.225</v>
       </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I13">
-        <v>27.36757624398074</v>
+        <v>27.35659847573205</v>
       </c>
       <c r="J13">
-        <v>72.63242375601926</v>
+        <v>72.64340152426794</v>
       </c>
       <c r="K13">
-        <v>-45.26484751203853</v>
+        <v>-45.28680304853589</v>
       </c>
       <c r="L13">
-        <v>-9.55808334289528</v>
+        <v>-9.578587311345132</v>
       </c>
       <c r="M13">
-        <v>-54.82293085493381</v>
+        <v>-54.86539035988103</v>
       </c>
       <c r="N13">
-        <v>-54.82293085493381</v>
+        <v>-54.86539035988103</v>
       </c>
       <c r="O13">
         <v>0.25</v>
@@ -2863,19 +2869,19 @@
         <v>0.75</v>
       </c>
       <c r="Q13">
-        <v>23.78329499039501</v>
+        <v>23.76462823397763</v>
       </c>
       <c r="R13">
-        <v>76.21670500960499</v>
+        <v>76.23537176602237</v>
       </c>
       <c r="S13">
-        <v>-7.168562507171458</v>
+        <v>-7.183940483508849</v>
       </c>
       <c r="T13">
-        <v>-52.43341001920999</v>
+        <v>-52.47074353204474</v>
       </c>
       <c r="U13">
-        <v>-52.43341001920999</v>
+        <v>-52.47074353204474</v>
       </c>
       <c r="V13">
         <v>0.1</v>
@@ -2884,28 +2890,28 @@
         <v>99.90000000000001</v>
       </c>
       <c r="X13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Y13" t="s">
         <v>71</v>
       </c>
       <c r="Z13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AA13" t="s">
         <v>71</v>
       </c>
       <c r="AB13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AC13">
         <v>0.1</v>
       </c>
       <c r="AD13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AE13">
-        <v>8.719769247836687</v>
+        <v>8.452880158905305</v>
       </c>
       <c r="AF13">
         <v>0</v>
@@ -2923,16 +2929,16 @@
         <v>0</v>
       </c>
       <c r="AK13">
-        <v>4.138771493218101</v>
+        <v>4.147649971996084</v>
       </c>
       <c r="AL13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AM13">
         <v>-10</v>
       </c>
       <c r="AN13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AO13" t="s">
         <v>71</v>
@@ -2944,13 +2950,13 @@
         <v>-10.02000000000001</v>
       </c>
       <c r="AR13">
-        <v>42.43341001920999</v>
+        <v>42.47074353204474</v>
       </c>
       <c r="AS13">
-        <v>42.41341001920998</v>
+        <v>42.45074353204473</v>
       </c>
       <c r="AT13">
-        <v>42.42341001920998</v>
+        <v>42.46074353204474</v>
       </c>
       <c r="AU13">
         <v>6</v>
@@ -2959,10 +2965,10 @@
         <v>4.808765205332268</v>
       </c>
       <c r="AW13">
-        <v>8.264248554060883</v>
+        <v>8.266271311478688</v>
       </c>
       <c r="AX13">
-        <v>8.676962959046175</v>
+        <v>8.678889527142141</v>
       </c>
       <c r="AY13">
         <v>0.8436468628413508</v>

--- a/outputs/Block5B_Senate_Race_Attribution.xlsx
+++ b/outputs/Block5B_Senate_Race_Attribution.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="113">
   <si>
     <t>STATE</t>
   </si>
@@ -205,21 +205,21 @@
     <t>Ohio</t>
   </si>
   <si>
+    <t>Alaska</t>
+  </si>
+  <si>
     <t>Texas</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
     <t>Maine</t>
   </si>
   <si>
+    <t>Kansas</t>
+  </si>
+  <si>
     <t>Iowa</t>
   </si>
   <si>
-    <t>Kansas</t>
-  </si>
-  <si>
     <t>Nebraska</t>
   </si>
   <si>
@@ -250,9 +250,6 @@
     <t>RSenLeanPollH (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>RSenLikPollH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
     <t>RSenSafPollH (&gt;10%)</t>
   </si>
   <si>
@@ -268,9 +265,6 @@
     <t>R Lean</t>
   </si>
   <si>
-    <t>R Likely</t>
-  </si>
-  <si>
     <t>R Safe</t>
   </si>
   <si>
@@ -340,19 +334,19 @@
     <t>Appointed (2025)[p]</t>
   </si>
   <si>
+    <t>53.90% R</t>
+  </si>
+  <si>
     <t>53.51% R</t>
   </si>
   <si>
-    <t>53.90% R</t>
-  </si>
-  <si>
     <t>50.98% R</t>
   </si>
   <si>
+    <t>53.22% R</t>
+  </si>
+  <si>
     <t>51.74% R</t>
-  </si>
-  <si>
-    <t>53.22% R</t>
   </si>
   <si>
     <t>62.58% R (2024 sp.)[o]</t>
@@ -915,10 +909,10 @@
         <v>72</v>
       </c>
       <c r="G2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I2">
         <v>54.57846952010376</v>
@@ -930,13 +924,13 @@
         <v>9.156939040207519</v>
       </c>
       <c r="L2">
-        <v>4.865057489990605</v>
+        <v>4.959486511901973</v>
       </c>
       <c r="M2">
-        <v>14.02199653019812</v>
+        <v>14.11642555210949</v>
       </c>
       <c r="N2">
-        <v>14.02199653019812</v>
+        <v>14.11642555210949</v>
       </c>
       <c r="O2">
         <v>0.25</v>
@@ -945,49 +939,49 @@
         <v>0.75</v>
       </c>
       <c r="Q2">
-        <v>56.40286607885024</v>
+        <v>56.438276962067</v>
       </c>
       <c r="R2">
-        <v>43.59713392114976</v>
+        <v>43.561723037933</v>
       </c>
       <c r="S2">
-        <v>3.648793117492954</v>
+        <v>3.71961488392648</v>
       </c>
       <c r="T2">
-        <v>12.80573215770047</v>
+        <v>12.876553924134</v>
       </c>
       <c r="U2">
-        <v>12.80573215770047</v>
+        <v>12.876553924134</v>
       </c>
       <c r="V2">
-        <v>97.54891845534584</v>
+        <v>97.57944163470155</v>
       </c>
       <c r="W2">
-        <v>2.451081544654166</v>
+        <v>2.420558365298442</v>
       </c>
       <c r="X2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y2" t="s">
         <v>70</v>
       </c>
       <c r="Z2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AA2" t="s">
         <v>70</v>
       </c>
       <c r="AB2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AC2">
-        <v>2.451081544654166</v>
+        <v>2.420558365298442</v>
       </c>
       <c r="AD2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AE2">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -1005,16 +999,16 @@
         <v>-0</v>
       </c>
       <c r="AK2">
-        <v>2.10663168860181</v>
+        <v>2.147520654516692</v>
       </c>
       <c r="AL2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AM2">
         <v>-1</v>
       </c>
       <c r="AN2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AO2" t="s">
         <v>70</v>
@@ -1026,25 +1020,25 @@
         <v>1.239999999999995</v>
       </c>
       <c r="AR2">
-        <v>13.80573215770047</v>
+        <v>13.876553924134</v>
       </c>
       <c r="AS2">
-        <v>11.56573215770048</v>
+        <v>11.636553924134</v>
       </c>
       <c r="AT2">
-        <v>12.68573215770047</v>
+        <v>12.756553924134</v>
       </c>
       <c r="AU2">
-        <v>3.171433039425119</v>
+        <v>3.1891384810335</v>
       </c>
       <c r="AV2">
         <v>5.482188815058572</v>
       </c>
       <c r="AW2">
-        <v>5.944032352845992</v>
+        <v>5.964042785182579</v>
       </c>
       <c r="AX2">
-        <v>6.505643906719904</v>
+        <v>6.523931971813496</v>
       </c>
       <c r="AY2">
         <v>0.8436468628413508</v>
@@ -1079,40 +1073,40 @@
         <v>71</v>
       </c>
       <c r="C3">
-        <v>50.74999999999999</v>
+        <v>50.64999999999999</v>
       </c>
       <c r="D3">
-        <v>41.375</v>
+        <v>40.84999999999999</v>
       </c>
       <c r="E3">
-        <v>9.375</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F3" t="s">
         <v>73</v>
       </c>
       <c r="G3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I3">
-        <v>55.08819538670284</v>
+        <v>55.3551912568306</v>
       </c>
       <c r="J3">
-        <v>44.91180461329715</v>
+        <v>44.6448087431694</v>
       </c>
       <c r="K3">
-        <v>10.17639077340569</v>
+        <v>10.7103825136612</v>
       </c>
       <c r="L3">
-        <v>-1.39302597381857</v>
+        <v>-1.555845774894018</v>
       </c>
       <c r="M3">
-        <v>8.783364799587122</v>
+        <v>9.154536738767183</v>
       </c>
       <c r="N3">
-        <v>8.783364799587122</v>
+        <v>9.154536738767183</v>
       </c>
       <c r="O3">
         <v>0.25</v>
@@ -1121,49 +1115,49 @@
         <v>0.75</v>
       </c>
       <c r="Q3">
-        <v>54.56581064652088</v>
+        <v>54.77174909124534</v>
       </c>
       <c r="R3">
-        <v>45.43418935347912</v>
+        <v>45.22825090875466</v>
       </c>
       <c r="S3">
-        <v>-1.044769480363929</v>
+        <v>-1.166884331170515</v>
       </c>
       <c r="T3">
-        <v>9.131621293041764</v>
+        <v>9.543498182490687</v>
       </c>
       <c r="U3">
-        <v>9.131621293041764</v>
+        <v>9.543498182490687</v>
       </c>
       <c r="V3">
-        <v>95.70206414313375</v>
+        <v>96.22844716481518</v>
       </c>
       <c r="W3">
-        <v>4.297935856866253</v>
+        <v>3.771552835184822</v>
       </c>
       <c r="X3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y3" t="s">
         <v>70</v>
       </c>
       <c r="Z3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AA3" t="s">
         <v>70</v>
       </c>
       <c r="AB3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC3">
+        <v>96.22844716481518</v>
+      </c>
+      <c r="AD3" t="s">
         <v>92</v>
       </c>
-      <c r="AC3">
-        <v>95.70206414313375</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>94</v>
-      </c>
       <c r="AE3">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -1181,16 +1175,16 @@
         <v>0</v>
       </c>
       <c r="AK3">
-        <v>0.6031979407292191</v>
+        <v>0.6737009827144528</v>
       </c>
       <c r="AL3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AM3">
         <v>-1</v>
       </c>
       <c r="AN3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AO3" t="s">
         <v>71</v>
@@ -1202,25 +1196,25 @@
         <v>2.620000000000005</v>
       </c>
       <c r="AR3">
-        <v>10.13162129304176</v>
+        <v>10.54349818249069</v>
       </c>
       <c r="AS3">
-        <v>6.51162129304176</v>
+        <v>6.923498182490682</v>
       </c>
       <c r="AT3">
-        <v>8.321621293041762</v>
+        <v>8.733498182490685</v>
       </c>
       <c r="AU3">
-        <v>2.08040532326044</v>
+        <v>2.183374545622671</v>
       </c>
       <c r="AV3">
         <v>4.808352845952818</v>
       </c>
       <c r="AW3">
-        <v>4.614040001124252</v>
+        <v>4.671621122213203</v>
       </c>
       <c r="AX3">
-        <v>5.318011579654246</v>
+        <v>5.368046752671822</v>
       </c>
       <c r="AY3">
         <v>0.8436468628413508</v>
@@ -1255,40 +1249,40 @@
         <v>70</v>
       </c>
       <c r="C4">
-        <v>49.77500000000001</v>
+        <v>49.675</v>
       </c>
       <c r="D4">
-        <v>43.225</v>
+        <v>43.02500000000001</v>
       </c>
       <c r="E4">
-        <v>6.550000000000001</v>
+        <v>6.65</v>
       </c>
       <c r="F4" t="s">
         <v>72</v>
       </c>
       <c r="G4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I4">
-        <v>53.52150537634409</v>
+        <v>53.58683926645091</v>
       </c>
       <c r="J4">
-        <v>46.47849462365591</v>
+        <v>46.41316073354908</v>
       </c>
       <c r="K4">
-        <v>7.043010752688183</v>
+        <v>7.173678532901825</v>
       </c>
       <c r="L4">
-        <v>2.668898933726563</v>
+        <v>2.619558306178332</v>
       </c>
       <c r="M4">
-        <v>9.711909686414746</v>
+        <v>9.793236839080157</v>
       </c>
       <c r="N4">
-        <v>9.711909686414746</v>
+        <v>9.793236839080157</v>
       </c>
       <c r="O4">
         <v>0.25</v>
@@ -1297,49 +1291,49 @@
         <v>0.75</v>
       </c>
       <c r="Q4">
-        <v>54.52234247649155</v>
+        <v>54.56917363126779</v>
       </c>
       <c r="R4">
-        <v>45.47765752350845</v>
+        <v>45.43082636873221</v>
       </c>
       <c r="S4">
-        <v>2.001674200294921</v>
+        <v>1.964668729633749</v>
       </c>
       <c r="T4">
-        <v>9.044684952983104</v>
+        <v>9.138347262535573</v>
       </c>
       <c r="U4">
-        <v>9.044684952983104</v>
+        <v>9.138347262535573</v>
       </c>
       <c r="V4">
-        <v>95.4133894089687</v>
+        <v>95.59246363352291</v>
       </c>
       <c r="W4">
-        <v>4.586610591031304</v>
+        <v>4.407536366477094</v>
       </c>
       <c r="X4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y4" t="s">
         <v>70</v>
       </c>
       <c r="Z4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AA4" t="s">
         <v>70</v>
       </c>
       <c r="AB4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AC4">
-        <v>4.586610591031304</v>
+        <v>4.407536366477094</v>
       </c>
       <c r="AD4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AE4">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF4">
         <v>0</v>
@@ -1357,16 +1351,16 @@
         <v>-0</v>
       </c>
       <c r="AK4">
-        <v>1.155667138370202</v>
+        <v>1.134302019922485</v>
       </c>
       <c r="AL4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AM4">
         <v>2</v>
       </c>
       <c r="AN4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AO4" t="s">
         <v>70</v>
@@ -1378,10 +1372,10 @@
         <v>13.28</v>
       </c>
       <c r="AR4">
-        <v>7.044684952983104</v>
+        <v>7.138347262535573</v>
       </c>
       <c r="AS4">
-        <v>4.235315047016897</v>
+        <v>4.141652737464428</v>
       </c>
       <c r="AT4">
         <v>5.640000000000001</v>
@@ -1393,10 +1387,10 @@
         <v>5.112371008372736</v>
       </c>
       <c r="AW4">
-        <v>4.666431817801355</v>
+        <v>4.661220490838894</v>
       </c>
       <c r="AX4">
-        <v>5.363531293798034</v>
+        <v>5.358997900128189</v>
       </c>
       <c r="AY4">
         <v>0.8436468628413508</v>
@@ -1431,40 +1425,40 @@
         <v>70</v>
       </c>
       <c r="C5">
-        <v>48.725</v>
+        <v>48.15</v>
       </c>
       <c r="D5">
-        <v>45.05</v>
+        <v>45.325</v>
       </c>
       <c r="E5">
-        <v>3.675</v>
+        <v>2.825</v>
       </c>
       <c r="F5" t="s">
         <v>74</v>
       </c>
       <c r="G5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I5">
-        <v>51.95947747267395</v>
+        <v>51.51109922439155</v>
       </c>
       <c r="J5">
-        <v>48.04052252732605</v>
+        <v>48.48890077560846</v>
       </c>
       <c r="K5">
-        <v>3.918954945347906</v>
+        <v>3.022198448783094</v>
       </c>
       <c r="L5">
-        <v>2.590328418627033</v>
+        <v>2.375074950791695</v>
       </c>
       <c r="M5">
-        <v>6.509283363974939</v>
+        <v>5.397273399574789</v>
       </c>
       <c r="N5">
-        <v>6.509283363974939</v>
+        <v>5.397273399574789</v>
       </c>
       <c r="O5">
         <v>0.25</v>
@@ -1473,49 +1467,49 @@
         <v>0.75</v>
       </c>
       <c r="Q5">
-        <v>52.93085062965909</v>
+        <v>52.40175233093844</v>
       </c>
       <c r="R5">
-        <v>47.06914937034091</v>
+        <v>47.59824766906156</v>
       </c>
       <c r="S5">
-        <v>1.942746313970275</v>
+        <v>1.781306213093772</v>
       </c>
       <c r="T5">
-        <v>5.861701259318181</v>
+        <v>4.803504661876866</v>
       </c>
       <c r="U5">
-        <v>5.861701259318181</v>
+        <v>4.803504661876866</v>
       </c>
       <c r="V5">
-        <v>86.85847000210781</v>
+        <v>82.43962590954837</v>
       </c>
       <c r="W5">
-        <v>13.1415299978922</v>
+        <v>17.56037409045163</v>
       </c>
       <c r="X5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Y5" t="s">
         <v>70</v>
       </c>
       <c r="Z5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AA5" t="s">
         <v>70</v>
       </c>
       <c r="AB5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AC5">
-        <v>13.1415299978922</v>
+        <v>17.56037409045163</v>
       </c>
       <c r="AD5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AE5">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -1533,16 +1527,16 @@
         <v>-0</v>
       </c>
       <c r="AK5">
-        <v>1.121645107337891</v>
+        <v>1.028437621638842</v>
       </c>
       <c r="AL5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AM5">
         <v>0</v>
       </c>
       <c r="AN5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AO5" t="s">
         <v>70</v>
@@ -1554,25 +1548,25 @@
         <v>-0.2000000000000028</v>
       </c>
       <c r="AR5">
-        <v>5.861701259318181</v>
+        <v>4.803504661876866</v>
       </c>
       <c r="AS5">
-        <v>6.061701259318184</v>
+        <v>5.003504661876868</v>
       </c>
       <c r="AT5">
-        <v>5.961701259318183</v>
+        <v>4.903504661876867</v>
       </c>
       <c r="AU5">
-        <v>1.490425314829546</v>
+        <v>1.225876165469217</v>
       </c>
       <c r="AV5">
         <v>4.890566271054463</v>
       </c>
       <c r="AW5">
-        <v>4.518046915456435</v>
+        <v>4.422368858589397</v>
       </c>
       <c r="AX5">
-        <v>5.234943166800129</v>
+        <v>5.152594332060622</v>
       </c>
       <c r="AY5">
         <v>0.8436468628413508</v>
@@ -1607,40 +1601,40 @@
         <v>71</v>
       </c>
       <c r="C6">
-        <v>47.825</v>
+        <v>47.675</v>
       </c>
       <c r="D6">
         <v>43.7</v>
       </c>
       <c r="E6">
-        <v>4.125</v>
+        <v>3.975</v>
       </c>
       <c r="F6" t="s">
         <v>75</v>
       </c>
       <c r="G6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I6">
-        <v>52.25348265501229</v>
+        <v>52.1751025991792</v>
       </c>
       <c r="J6">
-        <v>47.74651734498771</v>
+        <v>47.8248974008208</v>
       </c>
       <c r="K6">
-        <v>4.506965310024583</v>
+        <v>4.35020519835841</v>
       </c>
       <c r="L6">
-        <v>-2.638289777369295</v>
+        <v>-2.651610263822058</v>
       </c>
       <c r="M6">
-        <v>1.868675532655288</v>
+        <v>1.698594934536351</v>
       </c>
       <c r="N6">
-        <v>1.868675532655288</v>
+        <v>1.698594934536351</v>
       </c>
       <c r="O6">
         <v>0.25</v>
@@ -1649,49 +1643,49 @@
         <v>0.75</v>
       </c>
       <c r="Q6">
-        <v>51.26412398849881</v>
+        <v>51.18074875024593</v>
       </c>
       <c r="R6">
-        <v>48.73587601150119</v>
+        <v>48.81925124975407</v>
       </c>
       <c r="S6">
-        <v>-1.978717333026971</v>
+        <v>-1.988707697866544</v>
       </c>
       <c r="T6">
-        <v>2.528247976997612</v>
+        <v>2.361497500491866</v>
       </c>
       <c r="U6">
-        <v>2.528247976997612</v>
+        <v>2.361497500491866</v>
       </c>
       <c r="V6">
-        <v>68.62056620003455</v>
+        <v>67.5043909927755</v>
       </c>
       <c r="W6">
-        <v>31.37943379996545</v>
+        <v>32.4956090072245</v>
       </c>
       <c r="X6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="Y6" t="s">
         <v>70</v>
       </c>
       <c r="Z6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AA6" t="s">
         <v>70</v>
       </c>
       <c r="AB6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC6">
+        <v>67.5043909927755</v>
+      </c>
+      <c r="AD6" t="s">
         <v>92</v>
       </c>
-      <c r="AC6">
-        <v>68.62056620003455</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>94</v>
-      </c>
       <c r="AE6">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -1709,34 +1703,34 @@
         <v>0</v>
       </c>
       <c r="AK6">
-        <v>1.1424129848733</v>
+        <v>1.14818092470273</v>
       </c>
       <c r="AL6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AM6">
         <v>-5</v>
       </c>
       <c r="AN6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AR6">
-        <v>7.528247976997612</v>
+        <v>7.361497500491866</v>
       </c>
       <c r="AT6">
-        <v>7.528247976997612</v>
+        <v>7.361497500491866</v>
       </c>
       <c r="AU6">
-        <v>1.882061994249403</v>
+        <v>1.840374375122966</v>
       </c>
       <c r="AV6">
         <v>4.567515257270437</v>
       </c>
       <c r="AW6">
-        <v>4.490926033506978</v>
+        <v>4.480837687014714</v>
       </c>
       <c r="AX6">
-        <v>5.211554342784182</v>
+        <v>5.202863481462234</v>
       </c>
       <c r="AY6">
         <v>0.8436468628413508</v>
@@ -1771,40 +1765,40 @@
         <v>71</v>
       </c>
       <c r="C7">
-        <v>48.9</v>
+        <v>49.225</v>
       </c>
       <c r="D7">
-        <v>46.175</v>
+        <v>47.025</v>
       </c>
       <c r="E7">
-        <v>2.725</v>
+        <v>2.2</v>
       </c>
       <c r="F7" t="s">
         <v>75</v>
       </c>
       <c r="G7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I7">
-        <v>51.43307914804102</v>
+        <v>51.14285714285715</v>
       </c>
       <c r="J7">
-        <v>48.56692085195898</v>
+        <v>48.85714285714285</v>
       </c>
       <c r="K7">
-        <v>2.866158296082041</v>
+        <v>2.285714285714292</v>
       </c>
       <c r="L7">
-        <v>-0.9522874185159853</v>
+        <v>-0.3058484137633198</v>
       </c>
       <c r="M7">
-        <v>1.913870877566056</v>
+        <v>1.979865871950972</v>
       </c>
       <c r="N7">
-        <v>1.913870877566056</v>
+        <v>1.979865871950972</v>
       </c>
       <c r="O7">
         <v>0.25</v>
@@ -1813,49 +1807,49 @@
         <v>0.75</v>
       </c>
       <c r="Q7">
-        <v>51.07597136609753</v>
+        <v>51.0281639876959</v>
       </c>
       <c r="R7">
-        <v>48.92402863390247</v>
+        <v>48.9718360123041</v>
       </c>
       <c r="S7">
-        <v>-0.7142155638869889</v>
+        <v>-0.2293863103224898</v>
       </c>
       <c r="T7">
-        <v>2.151942732195052</v>
+        <v>2.056327975391802</v>
       </c>
       <c r="U7">
-        <v>2.151942732195052</v>
+        <v>2.056327975391802</v>
       </c>
       <c r="V7">
-        <v>66.42247604555808</v>
+        <v>63.19398747980172</v>
       </c>
       <c r="W7">
-        <v>33.57752395444192</v>
+        <v>36.80601252019828</v>
       </c>
       <c r="X7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="Y7" t="s">
         <v>70</v>
       </c>
       <c r="Z7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AA7" t="s">
         <v>70</v>
       </c>
       <c r="AB7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC7">
+        <v>63.19398747980172</v>
+      </c>
+      <c r="AD7" t="s">
         <v>92</v>
       </c>
-      <c r="AC7">
-        <v>66.42247604555808</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>94</v>
-      </c>
       <c r="AE7">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF7">
         <v>0</v>
@@ -1873,46 +1867,46 @@
         <v>0</v>
       </c>
       <c r="AK7">
-        <v>0.4123525480695734</v>
+        <v>0.1324362480131045</v>
       </c>
       <c r="AL7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AM7">
         <v>-6</v>
       </c>
       <c r="AN7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AO7" t="s">
         <v>71</v>
       </c>
       <c r="AP7">
-        <v>0.5351</v>
+        <v>0.539</v>
       </c>
       <c r="AQ7">
-        <v>-7.02000000000001</v>
+        <v>-7.800000000000011</v>
       </c>
       <c r="AR7">
-        <v>8.151942732195053</v>
+        <v>8.056327975391802</v>
       </c>
       <c r="AS7">
-        <v>9.171942732195063</v>
+        <v>9.856327975391814</v>
       </c>
       <c r="AT7">
-        <v>8.661942732195058</v>
+        <v>8.956327975391808</v>
       </c>
       <c r="AU7">
-        <v>2.165485683048765</v>
+        <v>2.239081993847952</v>
       </c>
       <c r="AV7">
-        <v>4.345503062353619</v>
+        <v>5.898436507750732</v>
       </c>
       <c r="AW7">
-        <v>4.331813166230072</v>
+        <v>5.499257889098187</v>
       </c>
       <c r="AX7">
-        <v>5.075084958548591</v>
+        <v>6.101943900116634</v>
       </c>
       <c r="AY7">
         <v>0.8436468628413508</v>
@@ -1921,22 +1915,22 @@
         <v>3</v>
       </c>
       <c r="BA7">
-        <v>1.930645252303767</v>
+        <v>1.541161542643699</v>
       </c>
       <c r="BB7">
-        <v>1.354753062157686</v>
+        <v>-4.006524474852094</v>
       </c>
       <c r="BC7">
-        <v>5.754964092348529</v>
+        <v>11.41694912221213</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>42.06393827345702</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>23.63541255450272</v>
       </c>
       <c r="BF7">
-        <v>0.9442145399410329</v>
+        <v>0.6873186760847522</v>
       </c>
     </row>
     <row r="8" spans="1:58">
@@ -1947,40 +1941,40 @@
         <v>71</v>
       </c>
       <c r="C8">
-        <v>49.475</v>
+        <v>48.575</v>
       </c>
       <c r="D8">
-        <v>46.775</v>
+        <v>46.3</v>
       </c>
       <c r="E8">
-        <v>2.7</v>
+        <v>2.275</v>
       </c>
       <c r="F8" t="s">
         <v>75</v>
       </c>
       <c r="G8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I8">
-        <v>51.4025974025974</v>
+        <v>51.19894598155468</v>
       </c>
       <c r="J8">
-        <v>48.5974025974026</v>
+        <v>48.80105401844532</v>
       </c>
       <c r="K8">
-        <v>2.805194805194802</v>
+        <v>2.397891963109359</v>
       </c>
       <c r="L8">
-        <v>-0.3163895128283701</v>
+        <v>-1.043389660304166</v>
       </c>
       <c r="M8">
-        <v>2.488805292366432</v>
+        <v>1.354502302805193</v>
       </c>
       <c r="N8">
-        <v>2.488805292366432</v>
+        <v>1.354502302805193</v>
       </c>
       <c r="O8">
         <v>0.25</v>
@@ -1989,49 +1983,49 @@
         <v>0.75</v>
       </c>
       <c r="Q8">
-        <v>51.28395133528676</v>
+        <v>50.80767485894062</v>
       </c>
       <c r="R8">
-        <v>48.71604866471324</v>
+        <v>49.19232514105938</v>
       </c>
       <c r="S8">
-        <v>-0.2372921346212777</v>
+        <v>-0.7825422452281245</v>
       </c>
       <c r="T8">
-        <v>2.567902670573524</v>
+        <v>1.615349717881234</v>
       </c>
       <c r="U8">
-        <v>2.567902670573524</v>
+        <v>1.615349717881234</v>
       </c>
       <c r="V8">
-        <v>66.19625489789294</v>
+        <v>62.59604325003473</v>
       </c>
       <c r="W8">
-        <v>33.80374510210705</v>
+        <v>37.40395674996527</v>
       </c>
       <c r="X8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="Y8" t="s">
         <v>70</v>
       </c>
       <c r="Z8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AA8" t="s">
         <v>70</v>
       </c>
       <c r="AB8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC8">
+        <v>62.59604325003473</v>
+      </c>
+      <c r="AD8" t="s">
         <v>92</v>
       </c>
-      <c r="AC8">
-        <v>66.19625489789294</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>94</v>
-      </c>
       <c r="AE8">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF8">
         <v>0</v>
@@ -2049,46 +2043,46 @@
         <v>0</v>
       </c>
       <c r="AK8">
-        <v>0.1370006778001755</v>
+        <v>0.4518009759347119</v>
       </c>
       <c r="AL8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AM8">
         <v>-6</v>
       </c>
       <c r="AN8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AO8" t="s">
         <v>71</v>
       </c>
       <c r="AP8">
-        <v>0.539</v>
+        <v>0.5351</v>
       </c>
       <c r="AQ8">
-        <v>-7.800000000000011</v>
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR8">
-        <v>8.567902670573524</v>
+        <v>7.615349717881235</v>
       </c>
       <c r="AS8">
-        <v>10.36790267057354</v>
+        <v>8.635349717881244</v>
       </c>
       <c r="AT8">
-        <v>9.46790267057353</v>
+        <v>8.125349717881239</v>
       </c>
       <c r="AU8">
-        <v>2.366975667643382</v>
+        <v>2.03133742947031</v>
       </c>
       <c r="AV8">
-        <v>5.898436507750732</v>
+        <v>4.345503062353619</v>
       </c>
       <c r="AW8">
-        <v>5.547966090444774</v>
+        <v>4.278349256582922</v>
       </c>
       <c r="AX8">
-        <v>6.145877461362781</v>
+        <v>5.029528247327535</v>
       </c>
       <c r="AY8">
         <v>0.8436468628413508</v>
@@ -2097,22 +2091,22 @@
         <v>3</v>
       </c>
       <c r="BA8">
-        <v>1.541161542643699</v>
+        <v>1.930645252303767</v>
       </c>
       <c r="BB8">
-        <v>-4.006524474852094</v>
+        <v>1.354753062157686</v>
       </c>
       <c r="BC8">
-        <v>11.41694912221213</v>
+        <v>5.754964092348529</v>
       </c>
       <c r="BD8">
-        <v>42.06393827345702</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>23.63541255450272</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>0.6873186760847522</v>
+        <v>0.9442145399410329</v>
       </c>
     </row>
     <row r="9" spans="1:58">
@@ -2123,40 +2117,40 @@
         <v>71</v>
       </c>
       <c r="C9">
-        <v>48.85</v>
+        <v>49.125</v>
       </c>
       <c r="D9">
-        <v>47.55</v>
+        <v>47.175</v>
       </c>
       <c r="E9">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="F9" t="s">
         <v>75</v>
       </c>
       <c r="G9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I9">
-        <v>50.67427385892116</v>
+        <v>51.01246105919003</v>
       </c>
       <c r="J9">
-        <v>49.32572614107884</v>
+        <v>48.98753894080997</v>
       </c>
       <c r="K9">
-        <v>1.348547717842322</v>
+        <v>2.024922118380061</v>
       </c>
       <c r="L9">
-        <v>-0.4691798583288631</v>
+        <v>-0.3204838353402772</v>
       </c>
       <c r="M9">
-        <v>0.8793678595134593</v>
+        <v>1.704438283039784</v>
       </c>
       <c r="N9">
-        <v>0.8793678595134593</v>
+        <v>1.704438283039784</v>
       </c>
       <c r="O9">
         <v>0.25</v>
@@ -2165,49 +2159,49 @@
         <v>0.75</v>
       </c>
       <c r="Q9">
-        <v>50.49833141204784</v>
+        <v>50.89227962093743</v>
       </c>
       <c r="R9">
-        <v>49.50166858795216</v>
+        <v>49.10772037906257</v>
       </c>
       <c r="S9">
-        <v>-0.3518848937466473</v>
+        <v>-0.2403628765052079</v>
       </c>
       <c r="T9">
-        <v>0.9966628240956751</v>
+        <v>1.784559241874853</v>
       </c>
       <c r="U9">
-        <v>0.9966628240956751</v>
+        <v>1.784559241874853</v>
       </c>
       <c r="V9">
-        <v>56.67502366776529</v>
+        <v>61.83849093383414</v>
       </c>
       <c r="W9">
-        <v>43.32497633223471</v>
+        <v>38.16150906616586</v>
       </c>
       <c r="X9" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="Y9" t="s">
         <v>70</v>
       </c>
       <c r="Z9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AA9" t="s">
         <v>70</v>
       </c>
       <c r="AB9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC9">
+        <v>61.83849093383414</v>
+      </c>
+      <c r="AD9" t="s">
         <v>92</v>
       </c>
-      <c r="AC9">
-        <v>56.67502366776529</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>94</v>
-      </c>
       <c r="AE9">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF9">
         <v>0</v>
@@ -2225,16 +2219,16 @@
         <v>0</v>
       </c>
       <c r="AK9">
-        <v>0.2031608381283897</v>
+        <v>0.1387735714534746</v>
       </c>
       <c r="AL9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AM9">
         <v>4</v>
       </c>
       <c r="AN9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO9" t="s">
         <v>71</v>
@@ -2246,10 +2240,10 @@
         <v>-1.95999999999998</v>
       </c>
       <c r="AR9">
-        <v>3.003337175904325</v>
+        <v>2.215440758125147</v>
       </c>
       <c r="AS9">
-        <v>2.956662824095655</v>
+        <v>3.744559241874833</v>
       </c>
       <c r="AT9">
         <v>2.97999999999999</v>
@@ -2261,10 +2255,10 @@
         <v>6.166256775636249</v>
       </c>
       <c r="AW9">
-        <v>5.306440474313349</v>
+        <v>5.301134249610259</v>
       </c>
       <c r="AX9">
-        <v>5.92875978066179</v>
+        <v>5.924011002838607</v>
       </c>
       <c r="AY9">
         <v>0.8436468628413508</v>
@@ -2299,40 +2293,40 @@
         <v>71</v>
       </c>
       <c r="C10">
-        <v>47.125</v>
+        <v>46.25</v>
       </c>
       <c r="D10">
-        <v>46.6</v>
+        <v>45.775</v>
       </c>
       <c r="E10">
-        <v>0.525</v>
+        <v>0.475</v>
       </c>
       <c r="F10" t="s">
         <v>76</v>
       </c>
       <c r="G10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I10">
-        <v>50.28007468658309</v>
+        <v>50.25808204292311</v>
       </c>
       <c r="J10">
-        <v>49.71992531341692</v>
+        <v>49.74191795707688</v>
       </c>
       <c r="K10">
-        <v>0.5601493731661762</v>
+        <v>0.5161640858462349</v>
       </c>
       <c r="L10">
-        <v>-2.066588514966667</v>
+        <v>-2.913528240380083</v>
       </c>
       <c r="M10">
-        <v>-1.506439141800491</v>
+        <v>-2.397364154533848</v>
       </c>
       <c r="N10">
-        <v>-1.506439141800491</v>
+        <v>-2.397364154533848</v>
       </c>
       <c r="O10">
         <v>0.25</v>
@@ -2341,49 +2335,49 @@
         <v>0.75</v>
       </c>
       <c r="Q10">
-        <v>49.50510399347059</v>
+        <v>49.16550895278058</v>
       </c>
       <c r="R10">
-        <v>50.49489600652941</v>
+        <v>50.83449104721942</v>
       </c>
       <c r="S10">
-        <v>-1.549941386225</v>
+        <v>-2.185146180285062</v>
       </c>
       <c r="T10">
-        <v>-0.989792013058824</v>
+        <v>-1.668982094438827</v>
       </c>
       <c r="U10">
-        <v>-0.989792013058824</v>
+        <v>-1.668982094438827</v>
       </c>
       <c r="V10">
-        <v>43.17452577301096</v>
+        <v>38.30178365229862</v>
       </c>
       <c r="W10">
-        <v>56.82547422698904</v>
+        <v>61.69821634770138</v>
       </c>
       <c r="X10" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="Y10" t="s">
         <v>71</v>
       </c>
       <c r="Z10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AA10" t="s">
         <v>70</v>
       </c>
       <c r="AB10" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC10">
+        <v>38.30178365229862</v>
+      </c>
+      <c r="AD10" t="s">
         <v>92</v>
       </c>
-      <c r="AC10">
-        <v>43.17452577301096</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>94</v>
-      </c>
       <c r="AE10">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF10">
         <v>0</v>
@@ -2401,70 +2395,70 @@
         <v>0</v>
       </c>
       <c r="AK10">
-        <v>0.8948590765651455</v>
+        <v>1.261594735406263</v>
       </c>
       <c r="AL10" t="s">
         <v>99</v>
       </c>
       <c r="AM10">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AN10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AO10" t="s">
         <v>71</v>
       </c>
       <c r="AP10">
-        <v>0.5174</v>
+        <v>0.5322</v>
       </c>
       <c r="AQ10">
-        <v>-3.47999999999999</v>
+        <v>-6.439999999999998</v>
       </c>
       <c r="AR10">
-        <v>5.010207986941176</v>
+        <v>6.331017905561173</v>
       </c>
       <c r="AS10">
-        <v>2.490207986941166</v>
+        <v>4.771017905561171</v>
       </c>
       <c r="AT10">
-        <v>3.750207986941171</v>
+        <v>5.551017905561172</v>
       </c>
       <c r="AU10">
-        <v>0.9375519967352928</v>
+        <v>1.387754476390293</v>
       </c>
       <c r="AV10">
-        <v>5.775280601260435</v>
+        <v>5.314982794026658</v>
       </c>
       <c r="AW10">
-        <v>5.113664173968316</v>
+        <v>4.946399794780316</v>
       </c>
       <c r="AX10">
-        <v>5.756860543168386</v>
+        <v>5.608810298019065</v>
       </c>
       <c r="AY10">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA10">
-        <v>2.193175026846863</v>
+        <v>0</v>
       </c>
       <c r="BB10">
-        <v>-2.886112316484782</v>
+        <v>-0.3706239798868902</v>
       </c>
       <c r="BC10">
-        <v>6.837360120673064</v>
+        <v>5.000892084631056</v>
       </c>
       <c r="BD10">
-        <v>30.49114883433812</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>8.823529411764707</v>
       </c>
       <c r="BF10">
-        <v>0.9513390040572299</v>
+        <v>0.9238036867710117</v>
       </c>
     </row>
     <row r="11" spans="1:58">
@@ -2475,40 +2469,40 @@
         <v>71</v>
       </c>
       <c r="C11">
-        <v>45.925</v>
+        <v>45.975</v>
       </c>
       <c r="D11">
-        <v>47.09999999999999</v>
+        <v>46.425</v>
       </c>
       <c r="E11">
-        <v>-1.175</v>
+        <v>-0.45</v>
       </c>
       <c r="F11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="I11">
-        <v>49.36844934157485</v>
+        <v>49.75649350649351</v>
       </c>
       <c r="J11">
-        <v>50.63155065842515</v>
+        <v>50.24350649350649</v>
       </c>
       <c r="K11">
-        <v>-1.263101316850296</v>
+        <v>-0.4870129870129816</v>
       </c>
       <c r="L11">
-        <v>-2.267434889907832</v>
+        <v>-2.685028376207439</v>
       </c>
       <c r="M11">
-        <v>-3.530536206758129</v>
+        <v>-3.172041363220421</v>
       </c>
       <c r="N11">
-        <v>-3.530536206758129</v>
+        <v>-3.172041363220421</v>
       </c>
       <c r="O11">
         <v>0.25</v>
@@ -2517,49 +2511,49 @@
         <v>0.75</v>
       </c>
       <c r="Q11">
-        <v>48.51816125785942</v>
+        <v>48.74960786541572</v>
       </c>
       <c r="R11">
-        <v>51.48183874214058</v>
+        <v>51.25039213458428</v>
       </c>
       <c r="S11">
-        <v>-1.700576167430874</v>
+        <v>-2.01377128215558</v>
       </c>
       <c r="T11">
-        <v>-2.96367748428117</v>
+        <v>-2.500784269168561</v>
       </c>
       <c r="U11">
-        <v>-2.96367748428117</v>
+        <v>-2.500784269168561</v>
       </c>
       <c r="V11">
-        <v>29.4052758159271</v>
+        <v>33.22591425492713</v>
       </c>
       <c r="W11">
-        <v>70.5947241840729</v>
+        <v>66.77408574507287</v>
       </c>
       <c r="X11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Y11" t="s">
         <v>71</v>
       </c>
       <c r="Z11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AA11" t="s">
         <v>71</v>
       </c>
       <c r="AB11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AC11">
-        <v>29.4052758159271</v>
+        <v>33.22591425492713</v>
       </c>
       <c r="AD11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AE11">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF11">
         <v>0</v>
@@ -2577,70 +2571,70 @@
         <v>0</v>
       </c>
       <c r="AK11">
-        <v>0.9818281080436774</v>
+        <v>1.162651391838862</v>
       </c>
       <c r="AL11" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="AM11">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AN11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AO11" t="s">
         <v>71</v>
       </c>
       <c r="AP11">
-        <v>0.5322</v>
+        <v>0.5174</v>
       </c>
       <c r="AQ11">
-        <v>-6.439999999999998</v>
+        <v>-3.47999999999999</v>
       </c>
       <c r="AR11">
-        <v>5.03632251571883</v>
+        <v>3.499215730831439</v>
       </c>
       <c r="AS11">
-        <v>3.476322515718827</v>
+        <v>0.9792157308314287</v>
       </c>
       <c r="AT11">
-        <v>4.256322515718828</v>
+        <v>2.239215730831434</v>
       </c>
       <c r="AU11">
-        <v>1.064080628929707</v>
+        <v>0.5598039327078584</v>
       </c>
       <c r="AV11">
-        <v>5.314982794026658</v>
+        <v>5.775280601260435</v>
       </c>
       <c r="AW11">
-        <v>4.790990486816234</v>
+        <v>5.12437958111547</v>
       </c>
       <c r="AX11">
-        <v>5.472245597021904</v>
+        <v>5.766380851167837</v>
       </c>
       <c r="AY11">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>2.193175026846863</v>
       </c>
       <c r="BB11">
-        <v>-0.3706239798868902</v>
+        <v>-2.886112316484782</v>
       </c>
       <c r="BC11">
-        <v>5.000892084631056</v>
+        <v>6.837360120673064</v>
       </c>
       <c r="BD11">
-        <v>17.64705882352941</v>
+        <v>30.49114883433812</v>
       </c>
       <c r="BE11">
-        <v>8.823529411764707</v>
+        <v>0</v>
       </c>
       <c r="BF11">
-        <v>0.9238036867710117</v>
+        <v>0.9513390040572299</v>
       </c>
     </row>
     <row r="12" spans="1:58">
@@ -2651,40 +2645,40 @@
         <v>71</v>
       </c>
       <c r="C12">
-        <v>46.03333333</v>
+        <v>46.1</v>
       </c>
       <c r="D12">
-        <v>51.26666667000001</v>
+        <v>48.7</v>
       </c>
       <c r="E12">
-        <v>-5.233333333</v>
+        <v>-2.6</v>
       </c>
       <c r="F12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I12">
-        <v>47.31072284686535</v>
+        <v>48.62869198312237</v>
       </c>
       <c r="J12">
-        <v>52.68927715313463</v>
+        <v>51.37130801687764</v>
       </c>
       <c r="K12">
-        <v>-5.37855430626928</v>
+        <v>-2.742616033755276</v>
       </c>
       <c r="L12">
-        <v>0.9757182060598102</v>
+        <v>-0.8762175158523855</v>
       </c>
       <c r="M12">
-        <v>-4.40283610020947</v>
+        <v>-3.618833549607661</v>
       </c>
       <c r="N12">
-        <v>-4.40283610020947</v>
+        <v>-3.618833549607661</v>
       </c>
       <c r="O12">
         <v>0.25</v>
@@ -2693,49 +2687,49 @@
         <v>0.75</v>
       </c>
       <c r="Q12">
-        <v>47.67661717413779</v>
+        <v>48.30011041467772</v>
       </c>
       <c r="R12">
-        <v>52.32338282586221</v>
+        <v>51.69988958532228</v>
       </c>
       <c r="S12">
-        <v>0.7317886545448573</v>
+        <v>-0.657163136889289</v>
       </c>
       <c r="T12">
-        <v>-4.646765651724422</v>
+        <v>-3.399779170644565</v>
       </c>
       <c r="U12">
-        <v>-4.646765651724422</v>
+        <v>-3.399779170644565</v>
       </c>
       <c r="V12">
-        <v>20.42376415676219</v>
+        <v>28.00039720000291</v>
       </c>
       <c r="W12">
-        <v>79.57623584323781</v>
+        <v>71.99960279999709</v>
       </c>
       <c r="X12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y12" t="s">
         <v>71</v>
       </c>
       <c r="Z12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AA12" t="s">
         <v>71</v>
       </c>
       <c r="AB12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AC12">
-        <v>20.42376415676219</v>
+        <v>28.00039720000291</v>
       </c>
       <c r="AD12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AE12">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF12">
         <v>0</v>
@@ -2753,16 +2747,16 @@
         <v>0</v>
       </c>
       <c r="AK12">
-        <v>0.4224983766913874</v>
+        <v>0.3794133139845298</v>
       </c>
       <c r="AL12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AM12">
         <v>-10</v>
       </c>
       <c r="AN12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AO12" t="s">
         <v>71</v>
@@ -2774,25 +2768,25 @@
         <v>-25.16000000000001</v>
       </c>
       <c r="AR12">
-        <v>5.353234348275578</v>
+        <v>6.600220829355435</v>
       </c>
       <c r="AS12">
-        <v>20.51323434827559</v>
+        <v>21.76022082935545</v>
       </c>
       <c r="AT12">
-        <v>12.93323434827558</v>
+        <v>14.18022082935544</v>
       </c>
       <c r="AU12">
-        <v>3.233308587068896</v>
+        <v>3.54505520733886</v>
       </c>
       <c r="AV12">
         <v>4.390437171606355</v>
       </c>
       <c r="AW12">
-        <v>4.960986351892614</v>
+        <v>5.199488328800901</v>
       </c>
       <c r="AX12">
-        <v>5.621678362644624</v>
+        <v>5.833229029508334</v>
       </c>
       <c r="AY12">
         <v>0.8436468628413508</v>
@@ -2827,40 +2821,40 @@
         <v>71</v>
       </c>
       <c r="C13">
-        <v>17.05</v>
+        <v>16.375</v>
       </c>
       <c r="D13">
-        <v>45.275</v>
+        <v>44.85</v>
       </c>
       <c r="E13">
-        <v>-28.225</v>
+        <v>-28.475</v>
       </c>
       <c r="F13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I13">
-        <v>27.35659847573205</v>
+        <v>26.74561045324622</v>
       </c>
       <c r="J13">
-        <v>72.64340152426794</v>
+        <v>73.25438954675377</v>
       </c>
       <c r="K13">
-        <v>-45.28680304853589</v>
+        <v>-46.50877909350755</v>
       </c>
       <c r="L13">
-        <v>-9.578587311345132</v>
+        <v>-9.823307752572713</v>
       </c>
       <c r="M13">
-        <v>-54.86539035988103</v>
+        <v>-56.33208684608026</v>
       </c>
       <c r="N13">
-        <v>-54.86539035988103</v>
+        <v>-56.33208684608026</v>
       </c>
       <c r="O13">
         <v>0.25</v>
@@ -2869,19 +2863,19 @@
         <v>0.75</v>
       </c>
       <c r="Q13">
-        <v>23.76462823397763</v>
+        <v>23.06187004603146</v>
       </c>
       <c r="R13">
-        <v>76.23537176602237</v>
+        <v>76.93812995396854</v>
       </c>
       <c r="S13">
-        <v>-7.183940483508849</v>
+        <v>-7.367480814429534</v>
       </c>
       <c r="T13">
-        <v>-52.47074353204474</v>
+        <v>-53.87625990793708</v>
       </c>
       <c r="U13">
-        <v>-52.47074353204474</v>
+        <v>-53.87625990793708</v>
       </c>
       <c r="V13">
         <v>0.1</v>
@@ -2890,28 +2884,28 @@
         <v>99.90000000000001</v>
       </c>
       <c r="X13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Y13" t="s">
         <v>71</v>
       </c>
       <c r="Z13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AA13" t="s">
         <v>71</v>
       </c>
       <c r="AB13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AC13">
         <v>0.1</v>
       </c>
       <c r="AD13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AE13">
-        <v>8.452880158905305</v>
+        <v>9.098901098901106</v>
       </c>
       <c r="AF13">
         <v>0</v>
@@ -2929,16 +2923,16 @@
         <v>0</v>
       </c>
       <c r="AK13">
-        <v>4.147649971996084</v>
+        <v>4.253617031460293</v>
       </c>
       <c r="AL13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AM13">
         <v>-10</v>
       </c>
       <c r="AN13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AO13" t="s">
         <v>71</v>
@@ -2950,13 +2944,13 @@
         <v>-10.02000000000001</v>
       </c>
       <c r="AR13">
-        <v>42.47074353204474</v>
+        <v>43.87625990793708</v>
       </c>
       <c r="AS13">
-        <v>42.45074353204473</v>
+        <v>43.85625990793707</v>
       </c>
       <c r="AT13">
-        <v>42.46074353204474</v>
+        <v>43.86625990793708</v>
       </c>
       <c r="AU13">
         <v>6</v>
@@ -2965,10 +2959,10 @@
         <v>4.808765205332268</v>
       </c>
       <c r="AW13">
-        <v>8.266271311478688</v>
+        <v>8.318140067872987</v>
       </c>
       <c r="AX13">
-        <v>8.678889527142141</v>
+        <v>8.72830660655983</v>
       </c>
       <c r="AY13">
         <v>0.8436468628413508</v>

--- a/outputs/Block5B_Senate_Race_Attribution.xlsx
+++ b/outputs/Block5B_Senate_Race_Attribution.xlsx
@@ -897,13 +897,13 @@
         <v>70</v>
       </c>
       <c r="C2">
-        <v>52.6</v>
+        <v>52.34999999999999</v>
       </c>
       <c r="D2">
-        <v>43.775</v>
+        <v>43.45</v>
       </c>
       <c r="E2">
-        <v>8.824999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="F2" t="s">
         <v>72</v>
@@ -915,22 +915,22 @@
         <v>84</v>
       </c>
       <c r="I2">
-        <v>54.57846952010376</v>
+        <v>54.64509394572024</v>
       </c>
       <c r="J2">
-        <v>45.42153047989624</v>
+        <v>45.35490605427975</v>
       </c>
       <c r="K2">
-        <v>9.156939040207519</v>
+        <v>9.290187891440489</v>
       </c>
       <c r="L2">
-        <v>4.959486511901973</v>
+        <v>4.665002429802401</v>
       </c>
       <c r="M2">
-        <v>14.11642555210949</v>
+        <v>13.95519032124289</v>
       </c>
       <c r="N2">
-        <v>14.11642555210949</v>
+        <v>13.95519032124289</v>
       </c>
       <c r="O2">
         <v>0.25</v>
@@ -939,25 +939,25 @@
         <v>0.75</v>
       </c>
       <c r="Q2">
-        <v>56.438276962067</v>
+        <v>56.39446985689614</v>
       </c>
       <c r="R2">
-        <v>43.561723037933</v>
+        <v>43.60553014310386</v>
       </c>
       <c r="S2">
-        <v>3.71961488392648</v>
+        <v>3.498751822351801</v>
       </c>
       <c r="T2">
-        <v>12.876553924134</v>
+        <v>12.78893971379229</v>
       </c>
       <c r="U2">
-        <v>12.876553924134</v>
+        <v>12.78893971379229</v>
       </c>
       <c r="V2">
-        <v>97.57944163470155</v>
+        <v>97.58286304790226</v>
       </c>
       <c r="W2">
-        <v>2.420558365298442</v>
+        <v>2.417136952097731</v>
       </c>
       <c r="X2" t="s">
         <v>79</v>
@@ -975,7 +975,7 @@
         <v>89</v>
       </c>
       <c r="AC2">
-        <v>2.420558365298442</v>
+        <v>2.417136952097731</v>
       </c>
       <c r="AD2" t="s">
         <v>92</v>
@@ -999,7 +999,7 @@
         <v>-0</v>
       </c>
       <c r="AK2">
-        <v>2.147520654516692</v>
+        <v>2.020005306462506</v>
       </c>
       <c r="AL2" t="s">
         <v>93</v>
@@ -1020,25 +1020,25 @@
         <v>1.239999999999995</v>
       </c>
       <c r="AR2">
-        <v>13.876553924134</v>
+        <v>13.78893971379229</v>
       </c>
       <c r="AS2">
-        <v>11.636553924134</v>
+        <v>11.5489397137923</v>
       </c>
       <c r="AT2">
-        <v>12.756553924134</v>
+        <v>12.66893971379229</v>
       </c>
       <c r="AU2">
-        <v>3.1891384810335</v>
+        <v>3.167234928448073</v>
       </c>
       <c r="AV2">
         <v>5.482188815058572</v>
       </c>
       <c r="AW2">
-        <v>5.964042785182579</v>
+        <v>5.913289326156208</v>
       </c>
       <c r="AX2">
-        <v>6.523931971813496</v>
+        <v>6.477566879947662</v>
       </c>
       <c r="AY2">
         <v>0.8436468628413508</v>
@@ -2469,13 +2469,13 @@
         <v>71</v>
       </c>
       <c r="C11">
-        <v>45.975</v>
+        <v>46.225</v>
       </c>
       <c r="D11">
-        <v>46.425</v>
+        <v>46.125</v>
       </c>
       <c r="E11">
-        <v>-0.45</v>
+        <v>0.1</v>
       </c>
       <c r="F11" t="s">
         <v>76</v>
@@ -2487,22 +2487,22 @@
         <v>81</v>
       </c>
       <c r="I11">
-        <v>49.75649350649351</v>
+        <v>50.05414185165133</v>
       </c>
       <c r="J11">
-        <v>50.24350649350649</v>
+        <v>49.94585814834868</v>
       </c>
       <c r="K11">
-        <v>-0.4870129870129816</v>
+        <v>0.1082837033026536</v>
       </c>
       <c r="L11">
-        <v>-2.685028376207439</v>
+        <v>-2.800784857330001</v>
       </c>
       <c r="M11">
-        <v>-3.172041363220421</v>
+        <v>-2.692501154027347</v>
       </c>
       <c r="N11">
-        <v>-3.172041363220421</v>
+        <v>-2.692501154027347</v>
       </c>
       <c r="O11">
         <v>0.25</v>
@@ -2511,25 +2511,25 @@
         <v>0.75</v>
       </c>
       <c r="Q11">
-        <v>48.74960786541572</v>
+        <v>49.00384753015258</v>
       </c>
       <c r="R11">
-        <v>51.25039213458428</v>
+        <v>50.99615246984742</v>
       </c>
       <c r="S11">
-        <v>-2.01377128215558</v>
+        <v>-2.100588642997501</v>
       </c>
       <c r="T11">
-        <v>-2.500784269168561</v>
+        <v>-1.992304939694847</v>
       </c>
       <c r="U11">
-        <v>-2.500784269168561</v>
+        <v>-1.992304939694847</v>
       </c>
       <c r="V11">
-        <v>33.22591425492713</v>
+        <v>36.54288608991354</v>
       </c>
       <c r="W11">
-        <v>66.77408574507287</v>
+        <v>63.45711391008646</v>
       </c>
       <c r="X11" t="s">
         <v>88</v>
@@ -2541,13 +2541,13 @@
         <v>91</v>
       </c>
       <c r="AA11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AB11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AC11">
-        <v>33.22591425492713</v>
+        <v>36.54288608991354</v>
       </c>
       <c r="AD11" t="s">
         <v>92</v>
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="AK11">
-        <v>1.162651391838862</v>
+        <v>1.212775418491278</v>
       </c>
       <c r="AL11" t="s">
         <v>97</v>
@@ -2592,25 +2592,25 @@
         <v>-3.47999999999999</v>
       </c>
       <c r="AR11">
-        <v>3.499215730831439</v>
+        <v>4.007695060305153</v>
       </c>
       <c r="AS11">
-        <v>0.9792157308314287</v>
+        <v>1.487695060305143</v>
       </c>
       <c r="AT11">
-        <v>2.239215730831434</v>
+        <v>2.747695060305148</v>
       </c>
       <c r="AU11">
-        <v>0.5598039327078584</v>
+        <v>0.6869237650762869</v>
       </c>
       <c r="AV11">
         <v>5.775280601260435</v>
       </c>
       <c r="AW11">
-        <v>5.12437958111547</v>
+        <v>5.153011767448446</v>
       </c>
       <c r="AX11">
-        <v>5.766380851167837</v>
+        <v>5.791840148417783</v>
       </c>
       <c r="AY11">
         <v>0.8436468628413508</v>
@@ -2645,13 +2645,13 @@
         <v>71</v>
       </c>
       <c r="C12">
-        <v>46.1</v>
+        <v>45.6</v>
       </c>
       <c r="D12">
-        <v>48.7</v>
+        <v>46.93333333</v>
       </c>
       <c r="E12">
-        <v>-2.6</v>
+        <v>-1.333333333</v>
       </c>
       <c r="F12" t="s">
         <v>77</v>
@@ -2663,22 +2663,22 @@
         <v>85</v>
       </c>
       <c r="I12">
-        <v>48.62869198312237</v>
+        <v>49.27953890667433</v>
       </c>
       <c r="J12">
-        <v>51.37130801687764</v>
+        <v>50.72046109332566</v>
       </c>
       <c r="K12">
-        <v>-2.742616033755276</v>
+        <v>-1.440922186651328</v>
       </c>
       <c r="L12">
-        <v>-0.8762175158523855</v>
+        <v>-2.404592995100077</v>
       </c>
       <c r="M12">
-        <v>-3.618833549607661</v>
+        <v>-3.845515181751405</v>
       </c>
       <c r="N12">
-        <v>-3.618833549607661</v>
+        <v>-3.845515181751405</v>
       </c>
       <c r="O12">
         <v>0.25</v>
@@ -2687,25 +2687,25 @@
         <v>0.75</v>
       </c>
       <c r="Q12">
-        <v>48.30011041467772</v>
+        <v>48.3778165335118</v>
       </c>
       <c r="R12">
-        <v>51.69988958532228</v>
+        <v>51.6221834664882</v>
       </c>
       <c r="S12">
-        <v>-0.657163136889289</v>
+        <v>-1.803444746325058</v>
       </c>
       <c r="T12">
-        <v>-3.399779170644565</v>
+        <v>-3.244366932976385</v>
       </c>
       <c r="U12">
-        <v>-3.399779170644565</v>
+        <v>-3.244366932976385</v>
       </c>
       <c r="V12">
-        <v>28.00039720000291</v>
+        <v>29.28823179916958</v>
       </c>
       <c r="W12">
-        <v>71.99960279999709</v>
+        <v>70.71176820083042</v>
       </c>
       <c r="X12" t="s">
         <v>82</v>
@@ -2723,7 +2723,7 @@
         <v>91</v>
       </c>
       <c r="AC12">
-        <v>28.00039720000291</v>
+        <v>29.28823179916958</v>
       </c>
       <c r="AD12" t="s">
         <v>92</v>
@@ -2747,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="AK12">
-        <v>0.3794133139845298</v>
+        <v>1.041219309759388</v>
       </c>
       <c r="AL12" t="s">
         <v>100</v>
@@ -2768,25 +2768,25 @@
         <v>-25.16000000000001</v>
       </c>
       <c r="AR12">
-        <v>6.600220829355435</v>
+        <v>6.755633067023615</v>
       </c>
       <c r="AS12">
-        <v>21.76022082935545</v>
+        <v>21.91563306702363</v>
       </c>
       <c r="AT12">
-        <v>14.18022082935544</v>
+        <v>14.33563306702362</v>
       </c>
       <c r="AU12">
-        <v>3.54505520733886</v>
+        <v>3.583908266755905</v>
       </c>
       <c r="AV12">
         <v>4.390437171606355</v>
       </c>
       <c r="AW12">
-        <v>5.199488328800901</v>
+        <v>5.33366990827579</v>
       </c>
       <c r="AX12">
-        <v>5.833229029508334</v>
+        <v>5.95314343181891</v>
       </c>
       <c r="AY12">
         <v>0.8436468628413508</v>

--- a/outputs/Block5B_Senate_Race_Attribution.xlsx
+++ b/outputs/Block5B_Senate_Race_Attribution.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="123">
   <si>
     <t>STATE</t>
   </si>
@@ -190,18 +190,21 @@
     <t>Mean Comparability Weight</t>
   </si>
   <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
     <t>Georgia</t>
   </si>
   <si>
-    <t>North Carolina</t>
-  </si>
-  <si>
     <t>New Hampshire</t>
   </si>
   <si>
     <t>Michigan</t>
   </si>
   <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
     <t>Ohio</t>
   </si>
   <si>
@@ -223,21 +226,27 @@
     <t>Nebraska</t>
   </si>
   <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>R</t>
+  </si>
+  <si>
     <t>D</t>
   </si>
   <si>
-    <t>R</t>
+    <t>RSenSafPollLD (&gt;10%)</t>
   </si>
   <si>
     <t>DSenLikPollH (&gt;5%&lt;=10%)</t>
   </si>
   <si>
-    <t>RSenLikPollLD (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
     <t>DSenLeanPollH (&gt;1&lt;=5%)</t>
   </si>
   <si>
@@ -250,9 +259,15 @@
     <t>RSenLeanPollH (&gt;1&lt;=5%)</t>
   </si>
   <si>
+    <t>RSenLikPollH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
     <t>RSenSafPollH (&gt;10%)</t>
   </si>
   <si>
+    <t>D Safe</t>
+  </si>
+  <si>
     <t>D Likely</t>
   </si>
   <si>
@@ -265,30 +280,33 @@
     <t>R Lean</t>
   </si>
   <si>
+    <t>R Likely</t>
+  </si>
+  <si>
     <t>R Safe</t>
   </si>
   <si>
+    <t>Safe</t>
+  </si>
+  <si>
     <t>Likely</t>
   </si>
   <si>
     <t>Lean</t>
   </si>
   <si>
-    <t>Safe</t>
-  </si>
-  <si>
     <t>D Tilt</t>
   </si>
   <si>
     <t>R Tilt</t>
   </si>
   <si>
+    <t>Democratic Flip</t>
+  </si>
+  <si>
     <t>Democratic Hold</t>
   </si>
   <si>
-    <t>Democratic Flip</t>
-  </si>
-  <si>
     <t>Republican Hold</t>
   </si>
   <si>
@@ -304,6 +322,9 @@
     <t>EVEN</t>
   </si>
   <si>
+    <t>D+3</t>
+  </si>
+  <si>
     <t>R+5</t>
   </si>
   <si>
@@ -319,18 +340,21 @@
     <t>R+10</t>
   </si>
   <si>
+    <t>48.69% R</t>
+  </si>
+  <si>
     <t>50.62% D</t>
   </si>
   <si>
-    <t>48.69% R</t>
-  </si>
-  <si>
     <t>56.64% D</t>
   </si>
   <si>
     <t>49.90% D</t>
   </si>
   <si>
+    <t>48.74% D</t>
+  </si>
+  <si>
     <t>Appointed (2025)[p]</t>
   </si>
   <si>
@@ -350,6 +374,12 @@
   </si>
   <si>
     <t>62.58% R (2024 sp.)[o]</t>
+  </si>
+  <si>
+    <t>Appointed (2026)[r]</t>
+  </si>
+  <si>
+    <t>Appointed (2025)[n]</t>
   </si>
   <si>
     <t>55.01% R</t>
@@ -710,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BF13"/>
+  <dimension ref="A1:BF16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:58">
@@ -894,43 +924,43 @@
         <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C2">
-        <v>52.34999999999999</v>
+        <v>51.1</v>
       </c>
       <c r="D2">
-        <v>43.45</v>
+        <v>40.725</v>
       </c>
       <c r="E2">
-        <v>8.9</v>
+        <v>10.375</v>
       </c>
       <c r="F2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I2">
-        <v>54.64509394572024</v>
+        <v>55.64933297032398</v>
       </c>
       <c r="J2">
-        <v>45.35490605427975</v>
+        <v>44.35066702967601</v>
       </c>
       <c r="K2">
-        <v>9.290187891440489</v>
+        <v>11.29866594064797</v>
       </c>
       <c r="L2">
-        <v>4.665002429802401</v>
+        <v>-1.328018485761584</v>
       </c>
       <c r="M2">
-        <v>13.95519032124289</v>
+        <v>9.970647454886388</v>
       </c>
       <c r="N2">
-        <v>13.95519032124289</v>
+        <v>9.970647454886388</v>
       </c>
       <c r="O2">
         <v>0.25</v>
@@ -939,49 +969,49 @@
         <v>0.75</v>
       </c>
       <c r="Q2">
-        <v>56.39446985689614</v>
+        <v>55.15132603816339</v>
       </c>
       <c r="R2">
-        <v>43.60553014310386</v>
+        <v>44.84867396183661</v>
       </c>
       <c r="S2">
-        <v>3.498751822351801</v>
+        <v>-0.9960138643211884</v>
       </c>
       <c r="T2">
-        <v>12.78893971379229</v>
+        <v>10.30265207632678</v>
       </c>
       <c r="U2">
-        <v>12.78893971379229</v>
+        <v>10.30265207632678</v>
       </c>
       <c r="V2">
-        <v>97.58286304790226</v>
+        <v>97.10292526103559</v>
       </c>
       <c r="W2">
-        <v>2.417136952097731</v>
+        <v>2.8970747389644</v>
       </c>
       <c r="X2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="Y2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Z2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AA2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AB2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AC2">
-        <v>2.417136952097731</v>
+        <v>97.10292526103559</v>
       </c>
       <c r="AD2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AE2">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -996,49 +1026,49 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>2.020005306462506</v>
+        <v>0.5750488726824372</v>
       </c>
       <c r="AL2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="AM2">
         <v>-1</v>
       </c>
       <c r="AN2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="AO2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AP2">
-        <v>0.5062</v>
+        <v>0.4869</v>
       </c>
       <c r="AQ2">
-        <v>1.239999999999995</v>
+        <v>2.620000000000005</v>
       </c>
       <c r="AR2">
-        <v>13.78893971379229</v>
+        <v>11.30265207632678</v>
       </c>
       <c r="AS2">
-        <v>11.5489397137923</v>
+        <v>7.682652076326779</v>
       </c>
       <c r="AT2">
-        <v>12.66893971379229</v>
+        <v>9.492652076326781</v>
       </c>
       <c r="AU2">
-        <v>3.167234928448073</v>
+        <v>2.373163019081695</v>
       </c>
       <c r="AV2">
-        <v>5.482188815058572</v>
+        <v>4.808352845952818</v>
       </c>
       <c r="AW2">
-        <v>5.913289326156208</v>
+        <v>4.746671443331257</v>
       </c>
       <c r="AX2">
-        <v>6.477566879947662</v>
+        <v>5.433486157182918</v>
       </c>
       <c r="AY2">
         <v>0.8436468628413508</v>
@@ -1047,22 +1077,22 @@
         <v>3</v>
       </c>
       <c r="BA2">
-        <v>2.211929341045432</v>
+        <v>2.170415722150866</v>
       </c>
       <c r="BB2">
-        <v>0.7423884751670249</v>
+        <v>0.275052926652725</v>
       </c>
       <c r="BC2">
-        <v>5.209225288644337</v>
+        <v>2.954610092474855</v>
       </c>
       <c r="BD2">
-        <v>0</v>
+        <v>30.09640135085562</v>
       </c>
       <c r="BE2">
-        <v>44.3421030056761</v>
+        <v>30.09640135085562</v>
       </c>
       <c r="BF2">
-        <v>0.9584693849829202</v>
+        <v>0.9401657373535796</v>
       </c>
     </row>
     <row r="3" spans="1:58">
@@ -1070,43 +1100,43 @@
         <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C3">
-        <v>50.64999999999999</v>
+        <v>51.7</v>
       </c>
       <c r="D3">
-        <v>40.84999999999999</v>
+        <v>43.3</v>
       </c>
       <c r="E3">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="F3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I3">
-        <v>55.3551912568306</v>
+        <v>54.42105263157895</v>
       </c>
       <c r="J3">
-        <v>44.6448087431694</v>
+        <v>45.57894736842105</v>
       </c>
       <c r="K3">
-        <v>10.7103825136612</v>
+        <v>8.84210526315789</v>
       </c>
       <c r="L3">
-        <v>-1.555845774894018</v>
+        <v>4.107208779216789</v>
       </c>
       <c r="M3">
-        <v>9.154536738767183</v>
+        <v>12.94931404237468</v>
       </c>
       <c r="N3">
-        <v>9.154536738767183</v>
+        <v>12.94931404237468</v>
       </c>
       <c r="O3">
         <v>0.25</v>
@@ -1115,49 +1145,49 @@
         <v>0.75</v>
       </c>
       <c r="Q3">
-        <v>54.77174909124534</v>
+        <v>55.96125592378524</v>
       </c>
       <c r="R3">
-        <v>45.22825090875466</v>
+        <v>44.03874407621476</v>
       </c>
       <c r="S3">
-        <v>-1.166884331170515</v>
+        <v>3.080406584412591</v>
       </c>
       <c r="T3">
-        <v>9.543498182490687</v>
+        <v>11.92251184757048</v>
       </c>
       <c r="U3">
-        <v>9.543498182490687</v>
+        <v>11.92251184757048</v>
       </c>
       <c r="V3">
-        <v>96.22844716481518</v>
+        <v>97.05519973121267</v>
       </c>
       <c r="W3">
-        <v>3.771552835184822</v>
+        <v>2.94480026878734</v>
       </c>
       <c r="X3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="Y3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Z3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AA3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AB3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AC3">
-        <v>96.22844716481518</v>
+        <v>2.94480026878734</v>
       </c>
       <c r="AD3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AE3">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -1172,49 +1202,49 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3">
-        <v>0.6737009827144528</v>
+        <v>1.778473570724105</v>
       </c>
       <c r="AL3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="AM3">
         <v>-1</v>
       </c>
       <c r="AN3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="AO3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AP3">
-        <v>0.4869</v>
+        <v>0.5062</v>
       </c>
       <c r="AQ3">
-        <v>2.620000000000005</v>
+        <v>1.239999999999995</v>
       </c>
       <c r="AR3">
-        <v>10.54349818249069</v>
+        <v>12.92251184757048</v>
       </c>
       <c r="AS3">
-        <v>6.923498182490682</v>
+        <v>10.68251184757049</v>
       </c>
       <c r="AT3">
-        <v>8.733498182490685</v>
+        <v>11.80251184757048</v>
       </c>
       <c r="AU3">
-        <v>2.183374545622671</v>
+        <v>2.950627961892621</v>
       </c>
       <c r="AV3">
-        <v>4.808352845952818</v>
+        <v>5.482188815058572</v>
       </c>
       <c r="AW3">
-        <v>4.671621122213203</v>
+        <v>5.731060568511756</v>
       </c>
       <c r="AX3">
-        <v>5.368046752671822</v>
+        <v>6.311650914722094</v>
       </c>
       <c r="AY3">
         <v>0.8436468628413508</v>
@@ -1223,22 +1253,22 @@
         <v>3</v>
       </c>
       <c r="BA3">
-        <v>2.170415722150866</v>
+        <v>2.211929341045432</v>
       </c>
       <c r="BB3">
-        <v>0.275052926652725</v>
+        <v>0.7423884751670249</v>
       </c>
       <c r="BC3">
-        <v>2.954610092474855</v>
+        <v>5.209225288644337</v>
       </c>
       <c r="BD3">
-        <v>30.09640135085562</v>
+        <v>0</v>
       </c>
       <c r="BE3">
-        <v>30.09640135085562</v>
+        <v>44.3421030056761</v>
       </c>
       <c r="BF3">
-        <v>0.9401657373535796</v>
+        <v>0.9584693849829202</v>
       </c>
     </row>
     <row r="4" spans="1:58">
@@ -1246,43 +1276,43 @@
         <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C4">
-        <v>49.675</v>
+        <v>49.725</v>
       </c>
       <c r="D4">
-        <v>43.02500000000001</v>
+        <v>43.05</v>
       </c>
       <c r="E4">
-        <v>6.65</v>
+        <v>6.675000000000001</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I4">
-        <v>53.58683926645091</v>
+        <v>53.59741309620048</v>
       </c>
       <c r="J4">
-        <v>46.41316073354908</v>
+        <v>46.40258690379951</v>
       </c>
       <c r="K4">
-        <v>7.173678532901825</v>
+        <v>7.194826192400974</v>
       </c>
       <c r="L4">
-        <v>2.619558306178332</v>
+        <v>2.618410068627739</v>
       </c>
       <c r="M4">
-        <v>9.793236839080157</v>
+        <v>9.813236261028713</v>
       </c>
       <c r="N4">
-        <v>9.793236839080157</v>
+        <v>9.813236261028713</v>
       </c>
       <c r="O4">
         <v>0.25</v>
@@ -1291,49 +1321,49 @@
         <v>0.75</v>
       </c>
       <c r="Q4">
-        <v>54.56917363126779</v>
+        <v>54.57931687193589</v>
       </c>
       <c r="R4">
-        <v>45.43082636873221</v>
+        <v>45.42068312806411</v>
       </c>
       <c r="S4">
-        <v>1.964668729633749</v>
+        <v>1.963807551470804</v>
       </c>
       <c r="T4">
-        <v>9.138347262535573</v>
+        <v>9.158633743871778</v>
       </c>
       <c r="U4">
-        <v>9.138347262535573</v>
+        <v>9.158633743871778</v>
       </c>
       <c r="V4">
-        <v>95.59246363352291</v>
+        <v>95.62712810470497</v>
       </c>
       <c r="W4">
-        <v>4.407536366477094</v>
+        <v>4.372871895295038</v>
       </c>
       <c r="X4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="Y4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Z4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="AA4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AB4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="AC4">
-        <v>4.407536366477094</v>
+        <v>4.372871895295038</v>
       </c>
       <c r="AD4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AE4">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF4">
         <v>0</v>
@@ -1351,19 +1381,19 @@
         <v>-0</v>
       </c>
       <c r="AK4">
-        <v>1.134302019922485</v>
+        <v>1.133804818478289</v>
       </c>
       <c r="AL4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="AM4">
         <v>2</v>
       </c>
       <c r="AN4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="AO4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AP4">
         <v>0.5664</v>
@@ -1372,10 +1402,10 @@
         <v>13.28</v>
       </c>
       <c r="AR4">
-        <v>7.138347262535573</v>
+        <v>7.158633743871778</v>
       </c>
       <c r="AS4">
-        <v>4.141652737464428</v>
+        <v>4.121366256128223</v>
       </c>
       <c r="AT4">
         <v>5.640000000000001</v>
@@ -1387,10 +1417,10 @@
         <v>5.112371008372736</v>
       </c>
       <c r="AW4">
-        <v>4.661220490838894</v>
+        <v>4.661418305708279</v>
       </c>
       <c r="AX4">
-        <v>5.358997900128189</v>
+        <v>5.359169959065881</v>
       </c>
       <c r="AY4">
         <v>0.8436468628413508</v>
@@ -1422,43 +1452,43 @@
         <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C5">
-        <v>48.15</v>
+        <v>47.95</v>
       </c>
       <c r="D5">
-        <v>45.325</v>
+        <v>45.7</v>
       </c>
       <c r="E5">
-        <v>2.825</v>
+        <v>2.25</v>
       </c>
       <c r="F5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I5">
-        <v>51.51109922439155</v>
+        <v>51.20128136679124</v>
       </c>
       <c r="J5">
-        <v>48.48890077560846</v>
+        <v>48.79871863320875</v>
       </c>
       <c r="K5">
-        <v>3.022198448783094</v>
+        <v>2.402562733582492</v>
       </c>
       <c r="L5">
-        <v>2.375074950791695</v>
+        <v>2.325407102330715</v>
       </c>
       <c r="M5">
-        <v>5.397273399574789</v>
+        <v>4.727969835913207</v>
       </c>
       <c r="N5">
-        <v>5.397273399574789</v>
+        <v>4.727969835913207</v>
       </c>
       <c r="O5">
         <v>0.25</v>
@@ -1467,49 +1497,49 @@
         <v>0.75</v>
       </c>
       <c r="Q5">
-        <v>52.40175233093844</v>
+        <v>52.07330903016526</v>
       </c>
       <c r="R5">
-        <v>47.59824766906156</v>
+        <v>47.92669096983474</v>
       </c>
       <c r="S5">
-        <v>1.781306213093772</v>
+        <v>1.744055326748036</v>
       </c>
       <c r="T5">
-        <v>4.803504661876866</v>
+        <v>4.146618060330528</v>
       </c>
       <c r="U5">
-        <v>4.803504661876866</v>
+        <v>4.146618060330528</v>
       </c>
       <c r="V5">
-        <v>82.43962590954837</v>
+        <v>79.12552443815213</v>
       </c>
       <c r="W5">
-        <v>17.56037409045163</v>
+        <v>20.87447556184787</v>
       </c>
       <c r="X5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Y5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Z5" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="AA5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AB5" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="AC5">
-        <v>17.56037409045163</v>
+        <v>20.87447556184787</v>
       </c>
       <c r="AD5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AE5">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -1527,19 +1557,19 @@
         <v>-0</v>
       </c>
       <c r="AK5">
-        <v>1.028437621638842</v>
+        <v>1.006930812379579</v>
       </c>
       <c r="AL5" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AM5">
         <v>0</v>
       </c>
       <c r="AN5" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="AO5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AP5">
         <v>0.499</v>
@@ -1548,25 +1578,25 @@
         <v>-0.2000000000000028</v>
       </c>
       <c r="AR5">
-        <v>4.803504661876866</v>
+        <v>4.146618060330528</v>
       </c>
       <c r="AS5">
-        <v>5.003504661876868</v>
+        <v>4.346618060330531</v>
       </c>
       <c r="AT5">
-        <v>4.903504661876867</v>
+        <v>4.24661806033053</v>
       </c>
       <c r="AU5">
-        <v>1.225876165469217</v>
+        <v>1.061654515082632</v>
       </c>
       <c r="AV5">
         <v>4.890566271054463</v>
       </c>
       <c r="AW5">
-        <v>4.422368858589397</v>
+        <v>4.377725388203625</v>
       </c>
       <c r="AX5">
-        <v>5.152594332060622</v>
+        <v>5.114329047283185</v>
       </c>
       <c r="AY5">
         <v>0.8436468628413508</v>
@@ -1598,43 +1628,43 @@
         <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C6">
-        <v>47.675</v>
+        <v>46.575</v>
       </c>
       <c r="D6">
-        <v>43.7</v>
+        <v>43.27500000000001</v>
       </c>
       <c r="E6">
-        <v>3.975</v>
+        <v>3.3</v>
       </c>
       <c r="F6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I6">
-        <v>52.1751025991792</v>
+        <v>51.8363939899833</v>
       </c>
       <c r="J6">
-        <v>47.8248974008208</v>
+        <v>48.1636060100167</v>
       </c>
       <c r="K6">
-        <v>4.35020519835841</v>
+        <v>3.6727879799666</v>
       </c>
       <c r="L6">
-        <v>-2.651610263822058</v>
+        <v>0.4421695923481876</v>
       </c>
       <c r="M6">
-        <v>1.698594934536351</v>
+        <v>4.114957572314788</v>
       </c>
       <c r="N6">
-        <v>1.698594934536351</v>
+        <v>4.114957572314788</v>
       </c>
       <c r="O6">
         <v>0.25</v>
@@ -1643,49 +1673,49 @@
         <v>0.75</v>
       </c>
       <c r="Q6">
-        <v>51.18074875024593</v>
+        <v>52.00220758711387</v>
       </c>
       <c r="R6">
-        <v>48.81925124975407</v>
+        <v>47.99779241288613</v>
       </c>
       <c r="S6">
-        <v>-1.988707697866544</v>
+        <v>0.3316271942611415</v>
       </c>
       <c r="T6">
-        <v>2.361497500491866</v>
+        <v>4.004415174227741</v>
       </c>
       <c r="U6">
-        <v>2.361497500491866</v>
+        <v>4.004415174227741</v>
       </c>
       <c r="V6">
-        <v>67.5043909927755</v>
+        <v>77.42997567231396</v>
       </c>
       <c r="W6">
-        <v>32.4956090072245</v>
+        <v>22.57002432768605</v>
       </c>
       <c r="X6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="Y6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Z6" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AA6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AB6" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AC6">
-        <v>67.5043909927755</v>
+        <v>22.57002432768605</v>
       </c>
       <c r="AD6" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AE6">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -1700,61 +1730,73 @@
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK6">
-        <v>1.14818092470273</v>
+        <v>0.1914650498772701</v>
       </c>
       <c r="AL6" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="AM6">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="AN6" t="s">
-        <v>105</v>
+        <v>112</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP6">
+        <v>0.4874</v>
+      </c>
+      <c r="AQ6">
+        <v>-2.519999999999996</v>
       </c>
       <c r="AR6">
-        <v>7.361497500491866</v>
+        <v>1.004415174227741</v>
+      </c>
+      <c r="AS6">
+        <v>6.524415174227737</v>
       </c>
       <c r="AT6">
-        <v>7.361497500491866</v>
+        <v>3.764415174227739</v>
       </c>
       <c r="AU6">
-        <v>1.840374375122966</v>
+        <v>0.9411037935569349</v>
       </c>
       <c r="AV6">
-        <v>4.567515257270437</v>
+        <v>5.314982794026658</v>
       </c>
       <c r="AW6">
-        <v>4.480837687014714</v>
+        <v>4.613297734483568</v>
       </c>
       <c r="AX6">
-        <v>5.202863481462234</v>
+        <v>5.317367583339822</v>
       </c>
       <c r="AY6">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA6">
-        <v>2.797261014127842</v>
+        <v>0</v>
       </c>
       <c r="BB6">
-        <v>0.1730167113317724</v>
+        <v>-0.3706239798868902</v>
       </c>
       <c r="BC6">
-        <v>2.956526743070407</v>
+        <v>5.000892084631056</v>
       </c>
       <c r="BD6">
-        <v>17.4915896825486</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>8.823529411764707</v>
       </c>
       <c r="BF6">
-        <v>0.956231216651788</v>
+        <v>0.9238036867710117</v>
       </c>
     </row>
     <row r="7" spans="1:58">
@@ -1762,43 +1804,43 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7">
-        <v>49.225</v>
+        <v>48.125</v>
       </c>
       <c r="D7">
-        <v>47.025</v>
+        <v>43.7</v>
       </c>
       <c r="E7">
-        <v>2.2</v>
+        <v>4.425</v>
       </c>
       <c r="F7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I7">
-        <v>51.14285714285715</v>
+        <v>52.40947454396951</v>
       </c>
       <c r="J7">
-        <v>48.85714285714285</v>
+        <v>47.59052545603049</v>
       </c>
       <c r="K7">
-        <v>2.285714285714292</v>
+        <v>4.818949087939018</v>
       </c>
       <c r="L7">
-        <v>-0.3058484137633198</v>
+        <v>-2.374390711518226</v>
       </c>
       <c r="M7">
-        <v>1.979865871950972</v>
+        <v>2.444558376420792</v>
       </c>
       <c r="N7">
-        <v>1.979865871950972</v>
+        <v>2.444558376420792</v>
       </c>
       <c r="O7">
         <v>0.25</v>
@@ -1807,49 +1849,49 @@
         <v>0.75</v>
       </c>
       <c r="Q7">
-        <v>51.0281639876959</v>
+        <v>51.51907802715017</v>
       </c>
       <c r="R7">
-        <v>48.9718360123041</v>
+        <v>48.48092197284983</v>
       </c>
       <c r="S7">
-        <v>-0.2293863103224898</v>
+        <v>-1.78079303363867</v>
       </c>
       <c r="T7">
-        <v>2.056327975391802</v>
+        <v>3.038156054300348</v>
       </c>
       <c r="U7">
-        <v>2.056327975391802</v>
+        <v>3.038156054300348</v>
       </c>
       <c r="V7">
-        <v>63.19398747980172</v>
+        <v>71.91900153246786</v>
       </c>
       <c r="W7">
-        <v>36.80601252019828</v>
+        <v>28.08099846753214</v>
       </c>
       <c r="X7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="Y7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Z7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AA7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AB7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AC7">
-        <v>63.19398747980172</v>
+        <v>71.91900153246786</v>
       </c>
       <c r="AD7" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AE7">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF7">
         <v>0</v>
@@ -1867,70 +1909,58 @@
         <v>0</v>
       </c>
       <c r="AK7">
-        <v>0.1324362480131045</v>
+        <v>1.028141337342296</v>
       </c>
       <c r="AL7" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="AM7">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AN7" t="s">
-        <v>106</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP7">
-        <v>0.539</v>
-      </c>
-      <c r="AQ7">
-        <v>-7.800000000000011</v>
+        <v>113</v>
       </c>
       <c r="AR7">
-        <v>8.056327975391802</v>
-      </c>
-      <c r="AS7">
-        <v>9.856327975391814</v>
+        <v>8.038156054300348</v>
       </c>
       <c r="AT7">
-        <v>8.956327975391808</v>
+        <v>8.038156054300348</v>
       </c>
       <c r="AU7">
-        <v>2.239081993847952</v>
+        <v>2.009539013575087</v>
       </c>
       <c r="AV7">
-        <v>5.898436507750732</v>
+        <v>4.567515257270437</v>
       </c>
       <c r="AW7">
-        <v>5.499257889098187</v>
+        <v>4.517251250195202</v>
       </c>
       <c r="AX7">
-        <v>6.101943900116634</v>
+        <v>5.234256478885237</v>
       </c>
       <c r="AY7">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA7">
-        <v>1.541161542643699</v>
+        <v>2.797261014127842</v>
       </c>
       <c r="BB7">
-        <v>-4.006524474852094</v>
+        <v>0.1730167113317724</v>
       </c>
       <c r="BC7">
-        <v>11.41694912221213</v>
+        <v>2.956526743070407</v>
       </c>
       <c r="BD7">
-        <v>42.06393827345702</v>
+        <v>17.4915896825486</v>
       </c>
       <c r="BE7">
-        <v>23.63541255450272</v>
+        <v>0</v>
       </c>
       <c r="BF7">
-        <v>0.6873186760847522</v>
+        <v>0.956231216651788</v>
       </c>
     </row>
     <row r="8" spans="1:58">
@@ -1938,43 +1968,43 @@
         <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8">
-        <v>48.575</v>
+        <v>49.45</v>
       </c>
       <c r="D8">
-        <v>46.3</v>
+        <v>47.625</v>
       </c>
       <c r="E8">
-        <v>2.275</v>
+        <v>1.825</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I8">
-        <v>51.19894598155468</v>
+        <v>50.93999484934329</v>
       </c>
       <c r="J8">
-        <v>48.80105401844532</v>
+        <v>49.06000515065671</v>
       </c>
       <c r="K8">
-        <v>2.397891963109359</v>
+        <v>1.879989698686586</v>
       </c>
       <c r="L8">
-        <v>-1.043389660304166</v>
+        <v>0.03624629882810737</v>
       </c>
       <c r="M8">
-        <v>1.354502302805193</v>
+        <v>1.916235997514693</v>
       </c>
       <c r="N8">
-        <v>1.354502302805193</v>
+        <v>1.916235997514693</v>
       </c>
       <c r="O8">
         <v>0.25</v>
@@ -1983,49 +2013,49 @@
         <v>0.75</v>
       </c>
       <c r="Q8">
-        <v>50.80767485894062</v>
+        <v>50.95358721140384</v>
       </c>
       <c r="R8">
-        <v>49.19232514105938</v>
+        <v>49.04641278859616</v>
       </c>
       <c r="S8">
-        <v>-0.7825422452281245</v>
+        <v>0.02718472412108053</v>
       </c>
       <c r="T8">
-        <v>1.615349717881234</v>
+        <v>1.907174422807667</v>
       </c>
       <c r="U8">
-        <v>1.615349717881234</v>
+        <v>1.907174422807667</v>
       </c>
       <c r="V8">
-        <v>62.59604325003473</v>
+        <v>62.30433719532572</v>
       </c>
       <c r="W8">
-        <v>37.40395674996527</v>
+        <v>37.69566280467428</v>
       </c>
       <c r="X8" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="Y8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Z8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AA8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AB8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AC8">
-        <v>62.59604325003473</v>
+        <v>62.30433719532572</v>
       </c>
       <c r="AD8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AE8">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF8">
         <v>0</v>
@@ -2043,46 +2073,46 @@
         <v>0</v>
       </c>
       <c r="AK8">
-        <v>0.4518009759347119</v>
+        <v>0.01569510778915155</v>
       </c>
       <c r="AL8" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="AM8">
         <v>-6</v>
       </c>
       <c r="AN8" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AO8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AP8">
-        <v>0.5351</v>
+        <v>0.539</v>
       </c>
       <c r="AQ8">
-        <v>-7.02000000000001</v>
+        <v>-7.800000000000011</v>
       </c>
       <c r="AR8">
-        <v>7.615349717881235</v>
+        <v>7.907174422807667</v>
       </c>
       <c r="AS8">
-        <v>8.635349717881244</v>
+        <v>9.707174422807679</v>
       </c>
       <c r="AT8">
-        <v>8.125349717881239</v>
+        <v>8.807174422807673</v>
       </c>
       <c r="AU8">
-        <v>2.03133742947031</v>
+        <v>2.201793605701918</v>
       </c>
       <c r="AV8">
-        <v>4.345503062353619</v>
+        <v>5.898436507750732</v>
       </c>
       <c r="AW8">
-        <v>4.278349256582922</v>
+        <v>5.479128204442785</v>
       </c>
       <c r="AX8">
-        <v>5.029528247327535</v>
+        <v>6.083808668102767</v>
       </c>
       <c r="AY8">
         <v>0.8436468628413508</v>
@@ -2091,22 +2121,22 @@
         <v>3</v>
       </c>
       <c r="BA8">
-        <v>1.930645252303767</v>
+        <v>1.541161542643699</v>
       </c>
       <c r="BB8">
-        <v>1.354753062157686</v>
+        <v>-4.006524474852094</v>
       </c>
       <c r="BC8">
-        <v>5.754964092348529</v>
+        <v>11.41694912221213</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>42.06393827345702</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>23.63541255450272</v>
       </c>
       <c r="BF8">
-        <v>0.9442145399410329</v>
+        <v>0.6873186760847522</v>
       </c>
     </row>
     <row r="9" spans="1:58">
@@ -2114,43 +2144,43 @@
         <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C9">
-        <v>49.125</v>
+        <v>48.525</v>
       </c>
       <c r="D9">
-        <v>47.175</v>
+        <v>46.225</v>
       </c>
       <c r="E9">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="F9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I9">
-        <v>51.01246105919003</v>
+        <v>51.21372031662269</v>
       </c>
       <c r="J9">
-        <v>48.98753894080997</v>
+        <v>48.78627968337731</v>
       </c>
       <c r="K9">
-        <v>2.024922118380061</v>
+        <v>2.427440633245382</v>
       </c>
       <c r="L9">
-        <v>-0.3204838353402772</v>
+        <v>-1.153094892366958</v>
       </c>
       <c r="M9">
-        <v>1.704438283039784</v>
+        <v>1.274345740878424</v>
       </c>
       <c r="N9">
-        <v>1.704438283039784</v>
+        <v>1.274345740878424</v>
       </c>
       <c r="O9">
         <v>0.25</v>
@@ -2159,49 +2189,49 @@
         <v>0.75</v>
       </c>
       <c r="Q9">
-        <v>50.89227962093743</v>
+        <v>50.78130973198508</v>
       </c>
       <c r="R9">
-        <v>49.10772037906257</v>
+        <v>49.21869026801492</v>
       </c>
       <c r="S9">
-        <v>-0.2403628765052079</v>
+        <v>-0.8648211692752186</v>
       </c>
       <c r="T9">
-        <v>1.784559241874853</v>
+        <v>1.562619463970164</v>
       </c>
       <c r="U9">
-        <v>1.784559241874853</v>
+        <v>1.562619463970164</v>
       </c>
       <c r="V9">
-        <v>61.83849093383414</v>
+        <v>62.20127145762546</v>
       </c>
       <c r="W9">
-        <v>38.16150906616586</v>
+        <v>37.79872854237454</v>
       </c>
       <c r="X9" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="Y9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Z9" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AA9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AB9" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AC9">
-        <v>61.83849093383414</v>
+        <v>62.20127145762546</v>
       </c>
       <c r="AD9" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AE9">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF9">
         <v>0</v>
@@ -2219,46 +2249,46 @@
         <v>0</v>
       </c>
       <c r="AK9">
-        <v>0.1387735714534746</v>
+        <v>0.4993047348819343</v>
       </c>
       <c r="AL9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AM9">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="AN9" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="AO9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AP9">
-        <v>0.5097999999999999</v>
+        <v>0.5351</v>
       </c>
       <c r="AQ9">
-        <v>-1.95999999999998</v>
+        <v>-7.02000000000001</v>
       </c>
       <c r="AR9">
-        <v>2.215440758125147</v>
+        <v>7.562619463970163</v>
       </c>
       <c r="AS9">
-        <v>3.744559241874833</v>
+        <v>8.582619463970174</v>
       </c>
       <c r="AT9">
-        <v>2.97999999999999</v>
+        <v>8.072619463970168</v>
       </c>
       <c r="AU9">
-        <v>0.7449999999999974</v>
+        <v>2.018154865992542</v>
       </c>
       <c r="AV9">
-        <v>6.166256775636249</v>
+        <v>4.345503062353619</v>
       </c>
       <c r="AW9">
-        <v>5.301134249610259</v>
+        <v>4.276786783839438</v>
       </c>
       <c r="AX9">
-        <v>5.924011002838607</v>
+        <v>5.02819920287429</v>
       </c>
       <c r="AY9">
         <v>0.8436468628413508</v>
@@ -2267,13 +2297,13 @@
         <v>3</v>
       </c>
       <c r="BA9">
-        <v>1.878161728442779</v>
+        <v>1.930645252303767</v>
       </c>
       <c r="BB9">
-        <v>1.021885173756878</v>
+        <v>1.354753062157686</v>
       </c>
       <c r="BC9">
-        <v>7.445671083211828</v>
+        <v>5.754964092348529</v>
       </c>
       <c r="BD9">
         <v>0</v>
@@ -2282,7 +2312,7 @@
         <v>0</v>
       </c>
       <c r="BF9">
-        <v>0.9207631564477893</v>
+        <v>0.9442145399410329</v>
       </c>
     </row>
     <row r="10" spans="1:58">
@@ -2290,43 +2320,43 @@
         <v>66</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C10">
-        <v>46.25</v>
+        <v>49.075</v>
       </c>
       <c r="D10">
-        <v>45.775</v>
+        <v>47.525</v>
       </c>
       <c r="E10">
-        <v>0.475</v>
+        <v>1.55</v>
       </c>
       <c r="F10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H10" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I10">
-        <v>50.25808204292311</v>
+        <v>50.80227743271222</v>
       </c>
       <c r="J10">
-        <v>49.74191795707688</v>
+        <v>49.19772256728779</v>
       </c>
       <c r="K10">
-        <v>0.5161640858462349</v>
+        <v>1.604554865424426</v>
       </c>
       <c r="L10">
-        <v>-2.913528240380083</v>
+        <v>-0.2692769494406259</v>
       </c>
       <c r="M10">
-        <v>-2.397364154533848</v>
+        <v>1.3352779159838</v>
       </c>
       <c r="N10">
-        <v>-2.397364154533848</v>
+        <v>1.3352779159838</v>
       </c>
       <c r="O10">
         <v>0.25</v>
@@ -2335,49 +2365,49 @@
         <v>0.75</v>
       </c>
       <c r="Q10">
-        <v>49.16550895278058</v>
+        <v>50.70129857667198</v>
       </c>
       <c r="R10">
-        <v>50.83449104721942</v>
+        <v>49.29870142332802</v>
       </c>
       <c r="S10">
-        <v>-2.185146180285062</v>
+        <v>-0.2019577120804694</v>
       </c>
       <c r="T10">
-        <v>-1.668982094438827</v>
+        <v>1.402597153343956</v>
       </c>
       <c r="U10">
-        <v>-1.668982094438827</v>
+        <v>1.402597153343956</v>
       </c>
       <c r="V10">
-        <v>38.30178365229862</v>
+        <v>59.35812758782153</v>
       </c>
       <c r="W10">
-        <v>61.69821634770138</v>
+        <v>40.64187241217847</v>
       </c>
       <c r="X10" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="Y10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Z10" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AA10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AB10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AC10">
-        <v>38.30178365229862</v>
+        <v>59.35812758782153</v>
       </c>
       <c r="AD10" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AE10">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF10">
         <v>0</v>
@@ -2395,70 +2425,70 @@
         <v>0</v>
       </c>
       <c r="AK10">
-        <v>1.261594735406263</v>
+        <v>0.11660033943458</v>
       </c>
       <c r="AL10" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="AM10">
-        <v>-8</v>
+        <v>4</v>
       </c>
       <c r="AN10" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="AO10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AP10">
-        <v>0.5322</v>
+        <v>0.5097999999999999</v>
       </c>
       <c r="AQ10">
-        <v>-6.439999999999998</v>
+        <v>-1.95999999999998</v>
       </c>
       <c r="AR10">
-        <v>6.331017905561173</v>
+        <v>2.597402846656044</v>
       </c>
       <c r="AS10">
-        <v>4.771017905561171</v>
+        <v>3.362597153343936</v>
       </c>
       <c r="AT10">
-        <v>5.551017905561172</v>
+        <v>2.97999999999999</v>
       </c>
       <c r="AU10">
-        <v>1.387754476390293</v>
+        <v>0.7449999999999974</v>
       </c>
       <c r="AV10">
-        <v>5.314982794026658</v>
+        <v>6.166256775636249</v>
       </c>
       <c r="AW10">
-        <v>4.946399794780316</v>
+        <v>5.30106833087324</v>
       </c>
       <c r="AX10">
-        <v>5.608810298019065</v>
+        <v>5.923952015162611</v>
       </c>
       <c r="AY10">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>1.878161728442779</v>
       </c>
       <c r="BB10">
-        <v>-0.3706239798868902</v>
+        <v>1.021885173756878</v>
       </c>
       <c r="BC10">
-        <v>5.000892084631056</v>
+        <v>7.445671083211828</v>
       </c>
       <c r="BD10">
-        <v>17.64705882352941</v>
+        <v>0</v>
       </c>
       <c r="BE10">
-        <v>8.823529411764707</v>
+        <v>0</v>
       </c>
       <c r="BF10">
-        <v>0.9238036867710117</v>
+        <v>0.9207631564477893</v>
       </c>
     </row>
     <row r="11" spans="1:58">
@@ -2466,43 +2496,43 @@
         <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C11">
-        <v>46.225</v>
+        <v>46.075</v>
       </c>
       <c r="D11">
-        <v>46.125</v>
+        <v>45.625</v>
       </c>
       <c r="E11">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="F11" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H11" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I11">
-        <v>50.05414185165133</v>
+        <v>50.2453653217012</v>
       </c>
       <c r="J11">
-        <v>49.94585814834868</v>
+        <v>49.7546346782988</v>
       </c>
       <c r="K11">
-        <v>0.1082837033026536</v>
+        <v>0.4907306434024008</v>
       </c>
       <c r="L11">
-        <v>-2.800784857330001</v>
+        <v>-3.142025843164147</v>
       </c>
       <c r="M11">
-        <v>-2.692501154027347</v>
+        <v>-2.651295199761746</v>
       </c>
       <c r="N11">
-        <v>-2.692501154027347</v>
+        <v>-2.651295199761746</v>
       </c>
       <c r="O11">
         <v>0.25</v>
@@ -2511,49 +2541,49 @@
         <v>0.75</v>
       </c>
       <c r="Q11">
-        <v>49.00384753015258</v>
+        <v>49.06710563051465</v>
       </c>
       <c r="R11">
-        <v>50.99615246984742</v>
+        <v>50.93289436948535</v>
       </c>
       <c r="S11">
-        <v>-2.100588642997501</v>
+        <v>-2.35651938237311</v>
       </c>
       <c r="T11">
-        <v>-1.992304939694847</v>
+        <v>-1.865788738970709</v>
       </c>
       <c r="U11">
-        <v>-1.992304939694847</v>
+        <v>-1.865788738970709</v>
       </c>
       <c r="V11">
-        <v>36.54288608991354</v>
+        <v>36.99320565632153</v>
       </c>
       <c r="W11">
-        <v>63.45711391008646</v>
+        <v>63.00679434367846</v>
       </c>
       <c r="X11" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Y11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Z11" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="AA11" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AB11" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AC11">
-        <v>36.54288608991354</v>
+        <v>36.99320565632153</v>
       </c>
       <c r="AD11" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AE11">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF11">
         <v>0</v>
@@ -2571,70 +2601,70 @@
         <v>0</v>
       </c>
       <c r="AK11">
-        <v>1.212775418491278</v>
+        <v>1.360537099763686</v>
       </c>
       <c r="AL11" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="AM11">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AN11" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="AO11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AP11">
-        <v>0.5174</v>
+        <v>0.5322</v>
       </c>
       <c r="AQ11">
-        <v>-3.47999999999999</v>
+        <v>-6.439999999999998</v>
       </c>
       <c r="AR11">
-        <v>4.007695060305153</v>
+        <v>6.134211261029291</v>
       </c>
       <c r="AS11">
-        <v>1.487695060305143</v>
+        <v>4.574211261029289</v>
       </c>
       <c r="AT11">
-        <v>2.747695060305148</v>
+        <v>5.35421126102929</v>
       </c>
       <c r="AU11">
-        <v>0.6869237650762869</v>
+        <v>1.338552815257323</v>
       </c>
       <c r="AV11">
-        <v>5.775280601260435</v>
+        <v>5.314982794026658</v>
       </c>
       <c r="AW11">
-        <v>5.153011767448446</v>
+        <v>4.958270629623712</v>
       </c>
       <c r="AX11">
-        <v>5.791840148417783</v>
+        <v>5.619281952878951</v>
       </c>
       <c r="AY11">
         <v>0.8436468628413508</v>
       </c>
       <c r="AZ11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA11">
-        <v>2.193175026846863</v>
+        <v>0</v>
       </c>
       <c r="BB11">
-        <v>-2.886112316484782</v>
+        <v>-0.3706239798868902</v>
       </c>
       <c r="BC11">
-        <v>6.837360120673064</v>
+        <v>5.000892084631056</v>
       </c>
       <c r="BD11">
-        <v>30.49114883433812</v>
+        <v>17.64705882352941</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>8.823529411764707</v>
       </c>
       <c r="BF11">
-        <v>0.9513390040572299</v>
+        <v>0.9238036867710117</v>
       </c>
     </row>
     <row r="12" spans="1:58">
@@ -2642,43 +2672,43 @@
         <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C12">
-        <v>45.6</v>
+        <v>45.85</v>
       </c>
       <c r="D12">
-        <v>46.93333333</v>
+        <v>46.15000000000001</v>
       </c>
       <c r="E12">
-        <v>-1.333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="F12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I12">
-        <v>49.27953890667433</v>
+        <v>49.83695652173913</v>
       </c>
       <c r="J12">
-        <v>50.72046109332566</v>
+        <v>50.16304347826088</v>
       </c>
       <c r="K12">
-        <v>-1.440922186651328</v>
+        <v>-0.326086956521749</v>
       </c>
       <c r="L12">
-        <v>-2.404592995100077</v>
+        <v>-2.985584654428823</v>
       </c>
       <c r="M12">
-        <v>-3.845515181751405</v>
+        <v>-3.311671610950572</v>
       </c>
       <c r="N12">
-        <v>-3.845515181751405</v>
+        <v>-3.311671610950572</v>
       </c>
       <c r="O12">
         <v>0.25</v>
@@ -2687,49 +2717,49 @@
         <v>0.75</v>
       </c>
       <c r="Q12">
-        <v>48.3778165335118</v>
+        <v>48.71736227632832</v>
       </c>
       <c r="R12">
-        <v>51.6221834664882</v>
+        <v>51.28263772367168</v>
       </c>
       <c r="S12">
-        <v>-1.803444746325058</v>
+        <v>-2.239188490821618</v>
       </c>
       <c r="T12">
-        <v>-3.244366932976385</v>
+        <v>-2.565275447343367</v>
       </c>
       <c r="U12">
-        <v>-3.244366932976385</v>
+        <v>-2.565275447343367</v>
       </c>
       <c r="V12">
-        <v>29.28823179916958</v>
+        <v>32.89408151901587</v>
       </c>
       <c r="W12">
-        <v>70.71176820083042</v>
+        <v>67.10591848098413</v>
       </c>
       <c r="X12" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="Y12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Z12" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="AA12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AB12" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="AC12">
-        <v>29.28823179916958</v>
+        <v>32.89408151901587</v>
       </c>
       <c r="AD12" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AE12">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF12">
         <v>0</v>
@@ -2747,46 +2777,46 @@
         <v>0</v>
       </c>
       <c r="AK12">
-        <v>1.041219309759388</v>
+        <v>1.292796077942173</v>
       </c>
       <c r="AL12" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AM12">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="AN12" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="AO12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AP12">
-        <v>0.6258</v>
+        <v>0.5174</v>
       </c>
       <c r="AQ12">
-        <v>-25.16000000000001</v>
+        <v>-3.47999999999999</v>
       </c>
       <c r="AR12">
-        <v>6.755633067023615</v>
+        <v>3.434724552656633</v>
       </c>
       <c r="AS12">
-        <v>21.91563306702363</v>
+        <v>0.9147245526566232</v>
       </c>
       <c r="AT12">
-        <v>14.33563306702362</v>
+        <v>2.174724552656628</v>
       </c>
       <c r="AU12">
-        <v>3.583908266755905</v>
+        <v>0.5436811381641571</v>
       </c>
       <c r="AV12">
-        <v>4.390437171606355</v>
+        <v>5.775280601260435</v>
       </c>
       <c r="AW12">
-        <v>5.33366990827579</v>
+        <v>5.154073308979592</v>
       </c>
       <c r="AX12">
-        <v>5.95314343181891</v>
+        <v>5.792784624314786</v>
       </c>
       <c r="AY12">
         <v>0.8436468628413508</v>
@@ -2795,22 +2825,22 @@
         <v>3</v>
       </c>
       <c r="BA12">
-        <v>1.906296723190152</v>
+        <v>2.193175026846863</v>
       </c>
       <c r="BB12">
-        <v>-1.372324784465838</v>
+        <v>-2.886112316484782</v>
       </c>
       <c r="BC12">
-        <v>5.414780435479317</v>
+        <v>6.837360120673064</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>30.49114883433812</v>
       </c>
       <c r="BE12">
         <v>0</v>
       </c>
       <c r="BF12">
-        <v>0.9325238981752073</v>
+        <v>0.9513390040572299</v>
       </c>
     </row>
     <row r="13" spans="1:58">
@@ -2818,43 +2848,43 @@
         <v>69</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C13">
-        <v>16.375</v>
+        <v>45.7</v>
       </c>
       <c r="D13">
-        <v>44.85</v>
+        <v>47.3</v>
       </c>
       <c r="E13">
-        <v>-28.475</v>
+        <v>-1.6</v>
       </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I13">
-        <v>26.74561045324622</v>
+        <v>49.13978494623656</v>
       </c>
       <c r="J13">
-        <v>73.25438954675377</v>
+        <v>50.86021505376344</v>
       </c>
       <c r="K13">
-        <v>-46.50877909350755</v>
+        <v>-1.72043010752688</v>
       </c>
       <c r="L13">
-        <v>-9.823307752572713</v>
+        <v>-2.133208235829057</v>
       </c>
       <c r="M13">
-        <v>-56.33208684608026</v>
+        <v>-3.853638343355938</v>
       </c>
       <c r="N13">
-        <v>-56.33208684608026</v>
+        <v>-3.853638343355938</v>
       </c>
       <c r="O13">
         <v>0.25</v>
@@ -2863,49 +2893,49 @@
         <v>0.75</v>
       </c>
       <c r="Q13">
-        <v>23.06187004603146</v>
+        <v>48.33983185780066</v>
       </c>
       <c r="R13">
-        <v>76.93812995396854</v>
+        <v>51.66016814219934</v>
       </c>
       <c r="S13">
-        <v>-7.367480814429534</v>
+        <v>-1.599906176871793</v>
       </c>
       <c r="T13">
-        <v>-53.87625990793708</v>
+        <v>-3.320336284398673</v>
       </c>
       <c r="U13">
-        <v>-53.87625990793708</v>
+        <v>-3.320336284398673</v>
       </c>
       <c r="V13">
-        <v>0.1</v>
+        <v>28.73738453916303</v>
       </c>
       <c r="W13">
-        <v>99.90000000000001</v>
+        <v>71.26261546083697</v>
       </c>
       <c r="X13" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="Y13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Z13" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="AA13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AB13" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="AC13">
-        <v>0.1</v>
+        <v>28.73738453916303</v>
       </c>
       <c r="AD13" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AE13">
-        <v>9.098901098901106</v>
+        <v>8.785698713756254</v>
       </c>
       <c r="AF13">
         <v>0</v>
@@ -2923,46 +2953,46 @@
         <v>0</v>
       </c>
       <c r="AK13">
-        <v>4.253617031460293</v>
+        <v>0.9237062618950747</v>
       </c>
       <c r="AL13" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="AM13">
         <v>-10</v>
       </c>
       <c r="AN13" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="AO13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AP13">
-        <v>0.5501</v>
+        <v>0.6258</v>
       </c>
       <c r="AQ13">
-        <v>-10.02000000000001</v>
+        <v>-25.16000000000001</v>
       </c>
       <c r="AR13">
-        <v>43.87625990793708</v>
+        <v>6.679663715601327</v>
       </c>
       <c r="AS13">
-        <v>43.85625990793707</v>
+        <v>21.83966371560134</v>
       </c>
       <c r="AT13">
-        <v>43.86625990793708</v>
+        <v>14.25966371560133</v>
       </c>
       <c r="AU13">
-        <v>6</v>
+        <v>3.564915928900333</v>
       </c>
       <c r="AV13">
-        <v>4.808765205332268</v>
+        <v>4.390437171606355</v>
       </c>
       <c r="AW13">
-        <v>8.318140067872987</v>
+        <v>5.294227952408996</v>
       </c>
       <c r="AX13">
-        <v>8.72830660655983</v>
+        <v>5.917831667209765</v>
       </c>
       <c r="AY13">
         <v>0.8436468628413508</v>
@@ -2971,21 +3001,525 @@
         <v>3</v>
       </c>
       <c r="BA13">
+        <v>1.906296723190152</v>
+      </c>
+      <c r="BB13">
+        <v>-1.372324784465838</v>
+      </c>
+      <c r="BC13">
+        <v>5.414780435479317</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0.9325238981752073</v>
+      </c>
+    </row>
+    <row r="14" spans="1:58">
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14">
+        <v>44.975</v>
+      </c>
+      <c r="D14">
+        <v>46.1</v>
+      </c>
+      <c r="E14">
+        <v>-1.125</v>
+      </c>
+      <c r="F14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" t="s">
+        <v>92</v>
+      </c>
+      <c r="I14">
+        <v>49.38237716167993</v>
+      </c>
+      <c r="J14">
+        <v>50.61762283832007</v>
+      </c>
+      <c r="K14">
+        <v>-1.235245676640133</v>
+      </c>
+      <c r="L14">
+        <v>-3.296493962154622</v>
+      </c>
+      <c r="M14">
+        <v>-4.531739638794756</v>
+      </c>
+      <c r="N14">
+        <v>-4.531739638794756</v>
+      </c>
+      <c r="O14">
+        <v>0.25</v>
+      </c>
+      <c r="P14">
+        <v>0.75</v>
+      </c>
+      <c r="Q14">
+        <v>48.14619192587195</v>
+      </c>
+      <c r="R14">
+        <v>51.85380807412805</v>
+      </c>
+      <c r="S14">
+        <v>-2.472370471615967</v>
+      </c>
+      <c r="T14">
+        <v>-3.7076161482561</v>
+      </c>
+      <c r="U14">
+        <v>-3.7076161482561</v>
+      </c>
+      <c r="V14">
+        <v>25.3176033774056</v>
+      </c>
+      <c r="W14">
+        <v>74.6823966225944</v>
+      </c>
+      <c r="X14" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC14">
+        <v>25.3176033774056</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE14">
+        <v>8.785698713756254</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>1.42742375732396</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>106</v>
+      </c>
+      <c r="AM14">
+        <v>-8</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>120</v>
+      </c>
+      <c r="AR14">
+        <v>4.292383851743899</v>
+      </c>
+      <c r="AT14">
+        <v>4.292383851743899</v>
+      </c>
+      <c r="AU14">
+        <v>1.073095962935975</v>
+      </c>
+      <c r="AV14">
+        <v>5.314982794026658</v>
+      </c>
+      <c r="AW14">
+        <v>4.912932521054522</v>
+      </c>
+      <c r="AX14">
+        <v>5.579317878181624</v>
+      </c>
+      <c r="AY14">
+        <v>0.8436468628413508</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>-0.3706239798868902</v>
+      </c>
+      <c r="BC14">
+        <v>5.000892084631056</v>
+      </c>
+      <c r="BD14">
+        <v>17.64705882352941</v>
+      </c>
+      <c r="BE14">
+        <v>8.823529411764707</v>
+      </c>
+      <c r="BF14">
+        <v>0.9238036867710117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:58">
+      <c r="A15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15">
+        <v>42.575</v>
+      </c>
+      <c r="D15">
+        <v>49.325</v>
+      </c>
+      <c r="E15">
+        <v>-6.75</v>
+      </c>
+      <c r="F15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15">
+        <v>46.32752992383025</v>
+      </c>
+      <c r="J15">
+        <v>53.67247007616974</v>
+      </c>
+      <c r="K15">
+        <v>-7.344940152339497</v>
+      </c>
+      <c r="L15">
+        <v>-1.516263212717702</v>
+      </c>
+      <c r="M15">
+        <v>-8.861203365057198</v>
+      </c>
+      <c r="N15">
+        <v>-8.861203365057198</v>
+      </c>
+      <c r="O15">
+        <v>0.25</v>
+      </c>
+      <c r="P15">
+        <v>0.75</v>
+      </c>
+      <c r="Q15">
+        <v>45.75893121906111</v>
+      </c>
+      <c r="R15">
+        <v>54.24106878093889</v>
+      </c>
+      <c r="S15">
+        <v>-1.137197409538276</v>
+      </c>
+      <c r="T15">
+        <v>-8.482137561877773</v>
+      </c>
+      <c r="U15">
+        <v>-8.482137561877773</v>
+      </c>
+      <c r="V15">
+        <v>5.710239091428177</v>
+      </c>
+      <c r="W15">
+        <v>94.28976090857182</v>
+      </c>
+      <c r="X15" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC15">
+        <v>5.710239091428177</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE15">
+        <v>8.785698713756254</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0.6565612305186688</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM15">
+        <v>-5</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AR15">
+        <v>3.482137561877773</v>
+      </c>
+      <c r="AT15">
+        <v>3.482137561877773</v>
+      </c>
+      <c r="AU15">
+        <v>0.8705343904694431</v>
+      </c>
+      <c r="AV15">
+        <v>5.314982794026658</v>
+      </c>
+      <c r="AW15">
+        <v>4.673743791644873</v>
+      </c>
+      <c r="AX15">
+        <v>5.369894138556267</v>
+      </c>
+      <c r="AY15">
+        <v>0.8436468628413508</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <v>-0.3706239798868902</v>
+      </c>
+      <c r="BC15">
+        <v>5.000892084631056</v>
+      </c>
+      <c r="BD15">
+        <v>17.64705882352941</v>
+      </c>
+      <c r="BE15">
+        <v>8.823529411764707</v>
+      </c>
+      <c r="BF15">
+        <v>0.9238036867710117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:58">
+      <c r="A16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16">
+        <v>16.525</v>
+      </c>
+      <c r="D16">
+        <v>45.1</v>
+      </c>
+      <c r="E16">
+        <v>-28.575</v>
+      </c>
+      <c r="F16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" t="s">
+        <v>90</v>
+      </c>
+      <c r="I16">
+        <v>26.81541582150102</v>
+      </c>
+      <c r="J16">
+        <v>73.18458417849898</v>
+      </c>
+      <c r="K16">
+        <v>-46.36916835699796</v>
+      </c>
+      <c r="L16">
+        <v>-9.679580505200811</v>
+      </c>
+      <c r="M16">
+        <v>-56.04874886219877</v>
+      </c>
+      <c r="N16">
+        <v>-56.04874886219877</v>
+      </c>
+      <c r="O16">
+        <v>0.25</v>
+      </c>
+      <c r="P16">
+        <v>0.75</v>
+      </c>
+      <c r="Q16">
+        <v>23.18557313205072</v>
+      </c>
+      <c r="R16">
+        <v>76.81442686794928</v>
+      </c>
+      <c r="S16">
+        <v>-7.259685378900606</v>
+      </c>
+      <c r="T16">
+        <v>-53.62885373589857</v>
+      </c>
+      <c r="U16">
+        <v>-53.62885373589857</v>
+      </c>
+      <c r="V16">
+        <v>0.1</v>
+      </c>
+      <c r="W16">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="X16" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC16">
+        <v>0.1</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE16">
+        <v>8.785698713756254</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>4.191381307740256</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AM16">
+        <v>-10</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>73</v>
+      </c>
+      <c r="AP16">
+        <v>0.5501</v>
+      </c>
+      <c r="AQ16">
+        <v>-10.02000000000001</v>
+      </c>
+      <c r="AR16">
+        <v>43.62885373589857</v>
+      </c>
+      <c r="AS16">
+        <v>43.60885373589856</v>
+      </c>
+      <c r="AT16">
+        <v>43.61885373589856</v>
+      </c>
+      <c r="AU16">
+        <v>6</v>
+      </c>
+      <c r="AV16">
+        <v>4.808765205332268</v>
+      </c>
+      <c r="AW16">
+        <v>8.287592123022948</v>
+      </c>
+      <c r="AX16">
+        <v>8.699199114111252</v>
+      </c>
+      <c r="AY16">
+        <v>0.8436468628413508</v>
+      </c>
+      <c r="AZ16">
+        <v>3</v>
+      </c>
+      <c r="BA16">
         <v>1.939183370917788</v>
       </c>
-      <c r="BB13">
+      <c r="BB16">
         <v>0.1011860990595696</v>
       </c>
-      <c r="BC13">
+      <c r="BC16">
         <v>1.960814204790223</v>
       </c>
-      <c r="BD13">
+      <c r="BD16">
         <v>58.22371654759336</v>
       </c>
-      <c r="BE13">
-        <v>0</v>
-      </c>
-      <c r="BF13">
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
         <v>0.9487813321503221</v>
       </c>
     </row>
